--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G35" t="n">

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.8</v>
+        <v>2.65</v>
       </c>
       <c r="M16" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>1.6</v>
+        <v>2.75</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N24" t="n">
-        <v>3.45</v>
+        <v>1.92</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="M25" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>1.92</v>
+        <v>3.45</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G35" t="n">

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.8</v>
+        <v>2.65</v>
       </c>
       <c r="M15" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>1.6</v>
+        <v>2.75</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.65</v>
+        <v>5.8</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>1.6</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.8</v>
+        <v>2.65</v>
       </c>
       <c r="M16" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>1.6</v>
+        <v>2.75</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G35" t="n">

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5.8</v>
+        <v>4.05</v>
       </c>
       <c r="M17" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="M24" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>1.92</v>
+        <v>3.45</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N25" t="n">
-        <v>3.45</v>
+        <v>1.92</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G31" t="n">

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.65</v>
+        <v>4.05</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>1.77</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="AB16" t="n">
         <v>1.7</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.05</v>
+        <v>2.65</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>1.77</v>
+        <v>2.75</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,7 +2489,7 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AB17" t="n">
         <v>1.7</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4280,10 +4280,10 @@
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="M8" t="n">
         <v>4.7</v>
@@ -1418,10 +1418,10 @@
         <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.8</v>
+        <v>2.65</v>
       </c>
       <c r="M15" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>1.6</v>
+        <v>2.75</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.05</v>
+        <v>5.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.35</v>
+        <v>3.77</v>
       </c>
       <c r="N16" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.65</v>
+        <v>4.05</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>2.75</v>
+        <v>1.77</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,7 +2489,7 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="AB17" t="n">
         <v>1.7</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="M26" t="n">
-        <v>3.8</v>
+        <v>3.47</v>
       </c>
       <c r="N26" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.15</v>
+        <v>3.23</v>
       </c>
       <c r="M28" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N28" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G35" t="n">

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.6</v>
+        <v>4.05</v>
       </c>
       <c r="M16" t="n">
-        <v>3.77</v>
+        <v>3.35</v>
       </c>
       <c r="N16" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.05</v>
+        <v>5.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>3.77</v>
       </c>
       <c r="N17" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="M21" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N24" t="n">
-        <v>3.45</v>
+        <v>1.92</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="M25" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>1.92</v>
+        <v>3.45</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.05</v>
+        <v>5.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.35</v>
+        <v>3.77</v>
       </c>
       <c r="N16" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5.6</v>
+        <v>4.05</v>
       </c>
       <c r="M17" t="n">
-        <v>3.77</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="M20" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N21" t="n">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC32" t="n">
         <v>2.08</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G35" t="n">

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.6</v>
+        <v>4.05</v>
       </c>
       <c r="M16" t="n">
-        <v>3.77</v>
+        <v>3.35</v>
       </c>
       <c r="N16" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.05</v>
+        <v>5.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>3.77</v>
       </c>
       <c r="N17" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G35" t="n">

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="M24" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>1.92</v>
+        <v>3.45</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N25" t="n">
-        <v>3.45</v>
+        <v>1.92</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G31" t="n">

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.05</v>
+        <v>5.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.35</v>
+        <v>3.77</v>
       </c>
       <c r="N16" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5.6</v>
+        <v>4.05</v>
       </c>
       <c r="M17" t="n">
-        <v>3.77</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.6</v>
+        <v>4.05</v>
       </c>
       <c r="M16" t="n">
-        <v>3.77</v>
+        <v>3.35</v>
       </c>
       <c r="N16" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.05</v>
+        <v>5.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>3.77</v>
       </c>
       <c r="N17" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="M21" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI35"/>
+  <dimension ref="A1:AI32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.65</v>
+        <v>4.05</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>2.75</v>
+        <v>1.77</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="AB15" t="n">
         <v>1.7</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.05</v>
+        <v>2.65</v>
       </c>
       <c r="M16" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>1.77</v>
+        <v>2.75</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AB16" t="n">
         <v>1.7</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="M20" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N21" t="n">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N24" t="n">
-        <v>3.45</v>
+        <v>1.92</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="M25" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>1.92</v>
+        <v>3.45</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -4299,363 +4299,6 @@
       </c>
       <c r="AI32" s="3" t="n">
         <v>46019.72916666666</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>46019</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>MC Oran</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>CR Belouizdad</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" s="3" t="n">
-        <v>46019.875</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>46019</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>MC Alger</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>ES Sétif</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI34" s="3" t="n">
-        <v>46019.875</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>46019</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>ES Mostaganem</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Ben Aknoun</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI35" s="3" t="n">
-        <v>46019.875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="M21" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="M24" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>1.92</v>
+        <v>3.45</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N25" t="n">
-        <v>3.45</v>
+        <v>1.92</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G31" t="n">

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.05</v>
+        <v>5.6</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>3.77</v>
       </c>
       <c r="N15" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.65</v>
+        <v>4.05</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>1.77</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="AB16" t="n">
         <v>1.7</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5.6</v>
+        <v>2.65</v>
       </c>
       <c r="M17" t="n">
-        <v>3.77</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>1.6</v>
+        <v>2.75</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.6</v>
+        <v>4.05</v>
       </c>
       <c r="M15" t="n">
-        <v>3.77</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.05</v>
+        <v>5.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.35</v>
+        <v>3.77</v>
       </c>
       <c r="N16" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G31" t="n">

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.05</v>
+        <v>5.6</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>3.77</v>
       </c>
       <c r="N15" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.6</v>
+        <v>4.05</v>
       </c>
       <c r="M16" t="n">
-        <v>3.77</v>
+        <v>3.35</v>
       </c>
       <c r="N16" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N24" t="n">
-        <v>3.45</v>
+        <v>1.92</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="M25" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>1.92</v>
+        <v>3.45</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G30" t="n">

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.6</v>
+        <v>2.65</v>
       </c>
       <c r="M15" t="n">
-        <v>3.77</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>1.6</v>
+        <v>2.75</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.65</v>
+        <v>5.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>3.77</v>
       </c>
       <c r="N17" t="n">
-        <v>2.75</v>
+        <v>1.6</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="M20" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N21" t="n">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="M24" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>1.92</v>
+        <v>3.45</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N25" t="n">
-        <v>3.45</v>
+        <v>1.92</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G31" t="n">

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.65</v>
+        <v>4.05</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>2.75</v>
+        <v>1.77</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="AB15" t="n">
         <v>1.7</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.05</v>
+        <v>2.65</v>
       </c>
       <c r="M16" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>1.77</v>
+        <v>2.75</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AB16" t="n">
         <v>1.7</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="M21" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N24" t="n">
-        <v>3.45</v>
+        <v>1.92</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="M25" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>1.92</v>
+        <v>3.45</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G30" t="n">

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.65</v>
+        <v>5.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>3.77</v>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>1.6</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5.6</v>
+        <v>2.65</v>
       </c>
       <c r="M17" t="n">
-        <v>3.77</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>1.6</v>
+        <v>2.75</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="M24" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>1.92</v>
+        <v>3.45</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N25" t="n">
-        <v>3.45</v>
+        <v>1.92</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G31" t="n">

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.05</v>
+        <v>2.65</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>1.77</v>
+        <v>2.75</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AB15" t="n">
         <v>1.7</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.6</v>
+        <v>4.05</v>
       </c>
       <c r="M16" t="n">
-        <v>3.77</v>
+        <v>3.35</v>
       </c>
       <c r="N16" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.65</v>
+        <v>5.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>3.77</v>
       </c>
       <c r="N17" t="n">
-        <v>2.75</v>
+        <v>1.6</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="M20" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N21" t="n">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N24" t="n">
-        <v>3.45</v>
+        <v>1.92</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="M25" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>1.92</v>
+        <v>3.45</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G31" t="n">

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.65</v>
+        <v>4.05</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>2.75</v>
+        <v>1.77</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="AB15" t="n">
         <v>1.7</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.05</v>
+        <v>5.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.35</v>
+        <v>3.77</v>
       </c>
       <c r="N16" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5.6</v>
+        <v>2.65</v>
       </c>
       <c r="M17" t="n">
-        <v>3.77</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>1.6</v>
+        <v>2.75</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="M21" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="M24" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>1.92</v>
+        <v>3.45</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N25" t="n">
-        <v>3.45</v>
+        <v>1.92</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G31" t="n">

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46019.14583333334</v>
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="M3" t="n">
-        <v>4.3</v>
+        <v>4.04</v>
       </c>
       <c r="N3" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.58</v>
+        <v>1.87</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46019.20833333334</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46019.22916666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.05</v>
+        <v>5.6</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>3.77</v>
       </c>
       <c r="N15" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.6</v>
+        <v>4.05</v>
       </c>
       <c r="M16" t="n">
-        <v>3.77</v>
+        <v>3.35</v>
       </c>
       <c r="N16" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N24" t="n">
-        <v>3.45</v>
+        <v>1.92</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="M25" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>1.92</v>
+        <v>3.45</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G30" t="n">

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.6</v>
+        <v>4.05</v>
       </c>
       <c r="M15" t="n">
-        <v>3.77</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.05</v>
+        <v>2.65</v>
       </c>
       <c r="M16" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>1.77</v>
+        <v>2.75</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AB16" t="n">
         <v>1.7</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.65</v>
+        <v>5.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>3.77</v>
       </c>
       <c r="N17" t="n">
-        <v>2.75</v>
+        <v>1.6</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="M24" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>1.92</v>
+        <v>3.45</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,16 +3322,16 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N25" t="n">
-        <v>3.45</v>
+        <v>1.92</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G31" t="n">

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
-        <v>4.04</v>
+        <v>4.3</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="O3" t="n">
         <v>2.1</v>
@@ -823,10 +823,10 @@
         <v>3.83</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.87</v>
+        <v>1.58</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.99</v>
+        <v>2.25</v>
       </c>
       <c r="AC3" t="n">
         <v>2.94</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AC25" t="n">
         <v>1.82</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G31" t="n">

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -659,28 +659,28 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="M2" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N2" t="n">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="O2" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="P2" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S2" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="T2" t="n">
         <v>2.86</v>
@@ -689,7 +689,7 @@
         <v>1.35</v>
       </c>
       <c r="V2" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="W2" t="n">
         <v>1.03</v>
@@ -710,10 +710,10 @@
         <v>1.79</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE2" t="n">
         <v>1.69</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="M3" t="n">
-        <v>4.3</v>
+        <v>4.04</v>
       </c>
       <c r="N3" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="O3" t="n">
         <v>2.1</v>
@@ -805,7 +805,7 @@
         <v>2.5</v>
       </c>
       <c r="U3" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="V3" t="n">
         <v>6.5</v>
@@ -820,19 +820,19 @@
         <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.83</v>
+        <v>3.85</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.58</v>
+        <v>1.88</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE3" t="n">
         <v>1.75</v>
@@ -844,7 +844,7 @@
         <v>1.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46019.20833333334</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.02</v>
+        <v>1.86</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O4" t="n">
         <v>2.36</v>
@@ -912,7 +912,7 @@
         <v>2.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.34</v>
+        <v>4.39</v>
       </c>
       <c r="R4" t="n">
         <v>1.37</v>
@@ -921,7 +921,7 @@
         <v>2.71</v>
       </c>
       <c r="T4" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="U4" t="n">
         <v>1.33</v>
@@ -942,13 +942,13 @@
         <v>3.14</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AB4" t="n">
         <v>1.74</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="AD4" t="n">
         <v>1.29</v>
@@ -960,7 +960,7 @@
         <v>1.89</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AH4" t="n">
         <v>1.8</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>5.71</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46019.3125</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46019.3125</v>
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N7" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46019.33333333334</v>
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M8" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="N8" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46019.35416666666</v>
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46019.375</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="M13" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="N13" t="n">
-        <v>2.71</v>
+        <v>3.25</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2096,64 +2096,64 @@
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46019.41666666666</v>
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.05</v>
+        <v>3.5</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.65</v>
+        <v>6.3</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>3.88</v>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>1.57</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>6.42</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5.6</v>
+        <v>2.5</v>
       </c>
       <c r="M17" t="n">
-        <v>3.77</v>
+        <v>2.95</v>
       </c>
       <c r="N17" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46019.47916666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="M20" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46019.52083333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N21" t="n">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46019.52083333334</v>
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46019.54166666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N24" t="n">
-        <v>3.45</v>
+        <v>1.92</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.97</v>
+        <v>1.25</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.83</v>
+        <v>3.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46019.5625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="M25" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>1.92</v>
+        <v>3.45</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.25</v>
+        <v>1.97</v>
       </c>
       <c r="AB25" t="n">
-        <v>3.5</v>
+        <v>1.83</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.82</v>
+        <v>3.36</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.88</v>
+        <v>1.27</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46019.5625</v>
@@ -3524,40 +3524,40 @@
         <v>4.7</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA26" t="n">
         <v>1.98</v>
@@ -3566,22 +3566,22 @@
         <v>1.77</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46019.58333333334</v>

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
-        <v>4.04</v>
+        <v>4.3</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="O3" t="n">
         <v>2.1</v>
@@ -823,10 +823,10 @@
         <v>3.85</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.88</v>
+        <v>1.58</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="AC3" t="n">
         <v>2.99</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5.71</v>
+        <v>1.33</v>
       </c>
       <c r="M5" t="n">
-        <v>4.15</v>
+        <v>5.04</v>
       </c>
       <c r="N5" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="O5" t="n">
-        <v>5.64</v>
+        <v>1.64</v>
       </c>
       <c r="P5" t="n">
-        <v>2.21</v>
+        <v>2.49</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.12</v>
+        <v>6.6</v>
       </c>
       <c r="R5" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="S5" t="n">
-        <v>2.96</v>
+        <v>3.32</v>
       </c>
       <c r="T5" t="n">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="U5" t="n">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="V5" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.08</v>
+        <v>3.12</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46019.3125</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.33</v>
+        <v>5.71</v>
       </c>
       <c r="M6" t="n">
-        <v>5.04</v>
+        <v>4.15</v>
       </c>
       <c r="N6" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="O6" t="n">
-        <v>1.64</v>
+        <v>5.64</v>
       </c>
       <c r="P6" t="n">
-        <v>2.49</v>
+        <v>2.21</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.6</v>
+        <v>2.12</v>
       </c>
       <c r="R6" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>3.32</v>
+        <v>2.96</v>
       </c>
       <c r="T6" t="n">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="U6" t="n">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="V6" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.12</v>
+        <v>1.08</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46019.3125</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="M7" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O7" t="n">
         <v>2.37</v>
@@ -1299,10 +1299,10 @@
         <v>3.43</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
         <v>3.15</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="M13" t="n">
-        <v>3.07</v>
+        <v>3.03</v>
       </c>
       <c r="N13" t="n">
-        <v>3.25</v>
+        <v>2.71</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="M15" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O15" t="n">
         <v>3.2</v>
       </c>
-      <c r="N15" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="O15" t="n">
-        <v>4</v>
-      </c>
       <c r="P15" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.62</v>
+        <v>3.54</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="S15" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="T15" t="n">
-        <v>2.95</v>
+        <v>3.28</v>
       </c>
       <c r="U15" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="V15" t="n">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.45</v>
+        <v>2.88</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.48</v>
+        <v>4.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.29</v>
+        <v>1.47</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.5</v>
+        <v>4.05</v>
       </c>
       <c r="M17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="O17" t="n">
+        <v>4</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T17" t="n">
         <v>2.95</v>
       </c>
-      <c r="N17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.28</v>
-      </c>
       <c r="U17" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="V17" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.88</v>
+        <v>3.45</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.2</v>
+        <v>3.48</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46019.45833333334</v>

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.33</v>
+        <v>5.71</v>
       </c>
       <c r="M5" t="n">
-        <v>5.04</v>
+        <v>4.15</v>
       </c>
       <c r="N5" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.64</v>
+        <v>5.64</v>
       </c>
       <c r="P5" t="n">
-        <v>2.49</v>
+        <v>2.21</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.6</v>
+        <v>2.12</v>
       </c>
       <c r="R5" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="S5" t="n">
-        <v>3.32</v>
+        <v>2.96</v>
       </c>
       <c r="T5" t="n">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="U5" t="n">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="V5" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.12</v>
+        <v>1.08</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46019.3125</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5.71</v>
+        <v>1.33</v>
       </c>
       <c r="M6" t="n">
-        <v>4.15</v>
+        <v>5.04</v>
       </c>
       <c r="N6" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="O6" t="n">
-        <v>5.64</v>
+        <v>1.64</v>
       </c>
       <c r="P6" t="n">
-        <v>2.21</v>
+        <v>2.49</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.12</v>
+        <v>6.6</v>
       </c>
       <c r="R6" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="S6" t="n">
-        <v>2.96</v>
+        <v>3.32</v>
       </c>
       <c r="T6" t="n">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="U6" t="n">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="V6" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.08</v>
+        <v>3.12</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46019.3125</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M8" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="N8" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="O8" t="n">
         <v>1.92</v>
@@ -1391,7 +1391,7 @@
         <v>8</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
         <v>3.05</v>
@@ -1418,10 +1418,10 @@
         <v>3.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AC8" t="n">
         <v>3</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46019.41666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O14" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46019.41666666666</v>
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="M15" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="O15" t="n">
         <v>3.2</v>
@@ -2239,10 +2239,10 @@
         <v>8.699999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y15" t="n">
         <v>1.4</v>
@@ -2254,7 +2254,7 @@
         <v>2.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
         <v>4.2</v>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6.3</v>
+        <v>5.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.88</v>
+        <v>3.77</v>
       </c>
       <c r="N16" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="O16" t="n">
         <v>6.42</v>
@@ -2349,10 +2349,10 @@
         <v>2.72</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="U16" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="V16" t="n">
         <v>7.5</v>
@@ -2370,10 +2370,10 @@
         <v>3.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
         <v>3.44</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46019.47916666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46019.47916666666</v>
@@ -2828,7 +2828,7 @@
         <v>3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
         <v>8.1</v>
@@ -2935,7 +2935,7 @@
         <v>1.88</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="R21" t="n">
         <v>1.53</v>
@@ -3417,10 +3417,10 @@
         <v>1.43</v>
       </c>
       <c r="S25" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="T25" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="U25" t="n">
         <v>1.39</v>
@@ -3447,7 +3447,7 @@
         <v>1.83</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="AD25" t="n">
         <v>1.27</v>
@@ -3530,7 +3530,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.6</v>
+        <v>4.15</v>
       </c>
       <c r="R26" t="n">
         <v>1.4</v>
@@ -3572,16 +3572,16 @@
         <v>1.25</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AF26" t="n">
         <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46019.58333333334</v>
@@ -3643,40 +3643,40 @@
         <v>2.25</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA27" t="n">
         <v>2.25</v>
@@ -3685,22 +3685,22 @@
         <v>1.55</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46019.625</v>
@@ -3762,40 +3762,40 @@
         <v>2.12</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA28" t="n">
         <v>1.78</v>
@@ -3804,22 +3804,22 @@
         <v>2.03</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46019.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4238,40 +4238,40 @@
         <v>19</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>6.33</v>
       </c>
       <c r="AA32" t="n">
         <v>1.45</v>
@@ -4286,16 +4286,16 @@
         <v>1.65</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46019.72916666666</v>

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5.71</v>
+        <v>1.33</v>
       </c>
       <c r="M5" t="n">
-        <v>4.15</v>
+        <v>5.04</v>
       </c>
       <c r="N5" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="O5" t="n">
-        <v>5.64</v>
+        <v>1.64</v>
       </c>
       <c r="P5" t="n">
-        <v>2.21</v>
+        <v>2.49</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.12</v>
+        <v>6.6</v>
       </c>
       <c r="R5" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="S5" t="n">
-        <v>2.96</v>
+        <v>3.32</v>
       </c>
       <c r="T5" t="n">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="U5" t="n">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="V5" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.08</v>
+        <v>3.12</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46019.3125</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.33</v>
+        <v>5.71</v>
       </c>
       <c r="M6" t="n">
-        <v>5.04</v>
+        <v>4.15</v>
       </c>
       <c r="N6" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="O6" t="n">
-        <v>1.64</v>
+        <v>5.64</v>
       </c>
       <c r="P6" t="n">
-        <v>2.49</v>
+        <v>2.21</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.6</v>
+        <v>2.12</v>
       </c>
       <c r="R6" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>3.32</v>
+        <v>2.96</v>
       </c>
       <c r="T6" t="n">
-        <v>2.29</v>
+        <v>2.45</v>
       </c>
       <c r="U6" t="n">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="V6" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.12</v>
+        <v>1.08</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46019.3125</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O13" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46019.41666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46019.41666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.65</v>
+        <v>4.05</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>2.75</v>
+        <v>1.77</v>
       </c>
       <c r="O15" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="P15" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.54</v>
+        <v>2.62</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="T15" t="n">
-        <v>3.28</v>
+        <v>2.95</v>
       </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="V15" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.88</v>
+        <v>3.45</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="AB15" t="n">
         <v>1.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.2</v>
+        <v>3.48</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.05</v>
+        <v>2.65</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>1.77</v>
+        <v>2.75</v>
       </c>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.62</v>
+        <v>3.54</v>
       </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="S17" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="T17" t="n">
-        <v>2.95</v>
+        <v>3.28</v>
       </c>
       <c r="U17" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="V17" t="n">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X17" t="n">
         <v>1.02</v>
       </c>
-      <c r="X17" t="n">
-        <v>1</v>
-      </c>
       <c r="Y17" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.45</v>
+        <v>2.88</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AB17" t="n">
         <v>1.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.48</v>
+        <v>4.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.29</v>
+        <v>1.47</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46019.45833333334</v>

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -659,37 +659,37 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.49</v>
+        <v>2.37</v>
       </c>
       <c r="M2" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="N2" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O2" t="n">
-        <v>3.06</v>
+        <v>3.02</v>
       </c>
       <c r="P2" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="R2" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="T2" t="n">
-        <v>2.86</v>
+        <v>2.79</v>
       </c>
       <c r="U2" t="n">
         <v>1.35</v>
       </c>
       <c r="V2" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="W2" t="n">
         <v>1.03</v>
@@ -707,25 +707,25 @@
         <v>1.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AF2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AG2" t="n">
         <v>1.26</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46019.14583333334</v>
@@ -787,7 +787,7 @@
         <v>6.2</v>
       </c>
       <c r="O3" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="P3" t="n">
         <v>2.25</v>
@@ -802,7 +802,7 @@
         <v>3.04</v>
       </c>
       <c r="T3" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="U3" t="n">
         <v>1.42</v>
@@ -835,13 +835,13 @@
         <v>1.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH3" t="n">
         <v>2.32</v>
@@ -897,34 +897,34 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>3.55</v>
+        <v>3.61</v>
       </c>
       <c r="O4" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="P4" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.39</v>
+        <v>4.45</v>
       </c>
       <c r="R4" t="n">
         <v>1.37</v>
       </c>
       <c r="S4" t="n">
-        <v>2.71</v>
+        <v>2.9</v>
       </c>
       <c r="T4" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="U4" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="V4" t="n">
         <v>7.5</v>
@@ -951,19 +951,19 @@
         <v>3.42</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AG4" t="n">
         <v>1.23</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46019.22916666666</v>
@@ -1019,70 +1019,70 @@
         <v>1.33</v>
       </c>
       <c r="M5" t="n">
-        <v>5.04</v>
+        <v>4.8</v>
       </c>
       <c r="N5" t="n">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="O5" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="P5" t="n">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.6</v>
+        <v>7.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>3.32</v>
+        <v>3.18</v>
       </c>
       <c r="T5" t="n">
-        <v>2.29</v>
+        <v>2.47</v>
       </c>
       <c r="U5" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="V5" t="n">
-        <v>5.1</v>
+        <v>5.35</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.4</v>
+        <v>4.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.12</v>
+        <v>2.94</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46019.3125</v>
@@ -1135,19 +1135,19 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5.71</v>
+        <v>5.5</v>
       </c>
       <c r="M6" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="N6" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="O6" t="n">
-        <v>5.64</v>
+        <v>5.74</v>
       </c>
       <c r="P6" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
         <v>2.12</v>
@@ -1159,43 +1159,43 @@
         <v>2.96</v>
       </c>
       <c r="T6" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U6" t="n">
         <v>1.44</v>
       </c>
       <c r="V6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
         <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.8</v>
+        <v>3.78</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AC6" t="n">
         <v>2.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AE6" t="n">
         <v>1.73</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AG6" t="n">
         <v>1.18</v>
@@ -1263,13 +1263,13 @@
         <v>4.3</v>
       </c>
       <c r="O7" t="n">
-        <v>2.37</v>
+        <v>2.32</v>
       </c>
       <c r="P7" t="n">
-        <v>2.07</v>
+        <v>2.28</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.95</v>
+        <v>5.34</v>
       </c>
       <c r="R7" t="n">
         <v>1.37</v>
@@ -1293,10 +1293,10 @@
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.43</v>
+        <v>3.45</v>
       </c>
       <c r="AA7" t="n">
         <v>1.9</v>
@@ -1305,22 +1305,22 @@
         <v>1.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="AD7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.26</v>
       </c>
-      <c r="AE7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AH7" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46019.33333333334</v>
@@ -1382,13 +1382,13 @@
         <v>8.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="P8" t="n">
         <v>2.48</v>
       </c>
       <c r="Q8" t="n">
-        <v>8</v>
+        <v>5.99</v>
       </c>
       <c r="R8" t="n">
         <v>1.36</v>
@@ -1397,7 +1397,7 @@
         <v>3.05</v>
       </c>
       <c r="T8" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="U8" t="n">
         <v>1.44</v>
@@ -1415,7 +1415,7 @@
         <v>1.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.75</v>
+        <v>3.68</v>
       </c>
       <c r="AA8" t="n">
         <v>1.79</v>
@@ -1427,7 +1427,7 @@
         <v>3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AE8" t="n">
         <v>2.1</v>
@@ -1495,10 +1495,10 @@
         <v>2.11</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="O9" t="n">
         <v>2.75</v>
@@ -1540,7 +1540,7 @@
         <v>2.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AC9" t="n">
         <v>3.34</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,10 +2099,10 @@
         <v>2.87</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.81</v>
+        <v>3.88</v>
       </c>
       <c r="R14" t="n">
         <v>1.4</v>
@@ -2111,7 +2111,7 @@
         <v>2.62</v>
       </c>
       <c r="T14" t="n">
-        <v>2.96</v>
+        <v>3.06</v>
       </c>
       <c r="U14" t="n">
         <v>1.32</v>
@@ -2129,19 +2129,19 @@
         <v>1.29</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.04</v>
+        <v>3.17</v>
       </c>
       <c r="AA14" t="n">
         <v>2.03</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE14" t="n">
         <v>1.79</v>
@@ -2215,7 +2215,7 @@
         <v>1.77</v>
       </c>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P15" t="n">
         <v>2.02</v>
@@ -2224,16 +2224,16 @@
         <v>2.62</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
         <v>2.66</v>
       </c>
       <c r="T15" t="n">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="U15" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
         <v>7.8</v>
@@ -2242,13 +2242,13 @@
         <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
         <v>1.28</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.45</v>
+        <v>3.12</v>
       </c>
       <c r="AA15" t="n">
         <v>2.03</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.6</v>
+        <v>2.65</v>
       </c>
       <c r="M16" t="n">
-        <v>3.77</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>1.6</v>
+        <v>2.75</v>
       </c>
       <c r="O16" t="n">
-        <v>6.42</v>
+        <v>3.2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.27</v>
+        <v>3.54</v>
       </c>
       <c r="R16" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="S16" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="T16" t="n">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="U16" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>7.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
         <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.44</v>
+        <v>4.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.13</v>
+        <v>1.53</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.65</v>
+        <v>5.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>3.77</v>
       </c>
       <c r="N17" t="n">
-        <v>2.75</v>
+        <v>1.6</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>6.42</v>
       </c>
       <c r="P17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q17" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V17" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AF17" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.47</v>
+        <v>2.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>1.13</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2742,7 +2742,7 @@
         <v>1.51</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="AG19" t="n">
         <v>1.2</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="O20" t="n">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="P20" t="n">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.62</v>
+        <v>3.06</v>
       </c>
       <c r="R20" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="S20" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="T20" t="n">
-        <v>3</v>
+        <v>3.48</v>
       </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="V20" t="n">
-        <v>8.1</v>
+        <v>9.9</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.39</v>
       </c>
-      <c r="Z20" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AH20" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46019.52083333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="M21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="O21" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T21" t="n">
         <v>3.15</v>
       </c>
-      <c r="N21" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="O21" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.48</v>
-      </c>
       <c r="U21" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="V21" t="n">
-        <v>9.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W21" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.55</v>
+        <v>2.99</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.5</v>
+        <v>4.09</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AE21" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.39</v>
+        <v>1.84</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46019.52083333334</v>
@@ -3158,19 +3158,19 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="M23" t="n">
         <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="O23" t="n">
         <v>2.45</v>
       </c>
       <c r="P23" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="Q23" t="n">
         <v>3.8</v>
@@ -3179,7 +3179,7 @@
         <v>1.32</v>
       </c>
       <c r="S23" t="n">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="T23" t="n">
         <v>2.59</v>
@@ -3191,13 +3191,13 @@
         <v>6.45</v>
       </c>
       <c r="W23" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="Z23" t="n">
         <v>3.3</v>
@@ -3206,7 +3206,7 @@
         <v>1.9</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AC23" t="n">
         <v>3.3</v>
@@ -3215,16 +3215,16 @@
         <v>1.28</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AG23" t="n">
         <v>1.23</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46019.54166666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="M24" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>1.92</v>
+        <v>3.45</v>
       </c>
       <c r="O24" t="n">
-        <v>3.16</v>
+        <v>2.85</v>
       </c>
       <c r="P24" t="n">
-        <v>2.54</v>
+        <v>2.06</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.53</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>1.13</v>
+        <v>1.43</v>
       </c>
       <c r="S24" t="n">
-        <v>4.6</v>
+        <v>2.81</v>
       </c>
       <c r="T24" t="n">
-        <v>1.81</v>
+        <v>2.98</v>
       </c>
       <c r="U24" t="n">
-        <v>1.99</v>
+        <v>1.39</v>
       </c>
       <c r="V24" t="n">
-        <v>3.3</v>
+        <v>7.9</v>
       </c>
       <c r="W24" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.02</v>
+        <v>1.33</v>
       </c>
       <c r="Z24" t="n">
-        <v>8</v>
+        <v>3.63</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.25</v>
+        <v>1.97</v>
       </c>
       <c r="AB24" t="n">
-        <v>3.5</v>
+        <v>1.83</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.82</v>
+        <v>3.38</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.88</v>
+        <v>1.27</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.3</v>
+        <v>1.76</v>
       </c>
       <c r="AF24" t="n">
-        <v>3.5</v>
+        <v>1.98</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46019.5625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N25" t="n">
-        <v>3.45</v>
+        <v>1.92</v>
       </c>
       <c r="O25" t="n">
-        <v>2.6</v>
+        <v>3.16</v>
       </c>
       <c r="P25" t="n">
-        <v>2.06</v>
+        <v>2.54</v>
       </c>
       <c r="Q25" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF25" t="n">
         <v>3.58</v>
       </c>
-      <c r="R25" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V25" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AG25" t="n">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46019.5625</v>
@@ -3524,16 +3524,16 @@
         <v>4.7</v>
       </c>
       <c r="O26" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="P26" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.15</v>
+        <v>4.6</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
         <v>2.75</v>
@@ -3557,7 +3557,7 @@
         <v>1.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.35</v>
+        <v>3.16</v>
       </c>
       <c r="AA26" t="n">
         <v>1.98</v>
@@ -3566,10 +3566,10 @@
         <v>1.77</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.63</v>
+        <v>3.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE26" t="n">
         <v>1.85</v>
@@ -3581,7 +3581,7 @@
         <v>1.31</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46019.58333333334</v>
@@ -3652,16 +3652,16 @@
         <v>2.75</v>
       </c>
       <c r="R27" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S27" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="T27" t="n">
         <v>2.9</v>
       </c>
       <c r="U27" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V27" t="n">
         <v>7.9</v>
@@ -3673,10 +3673,10 @@
         <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z27" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AA27" t="n">
         <v>2.25</v>
@@ -3691,16 +3691,16 @@
         <v>1.25</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AG27" t="n">
         <v>1.35</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46019.625</v>
@@ -3777,10 +3777,10 @@
         <v>3.05</v>
       </c>
       <c r="T28" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="U28" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="V28" t="n">
         <v>6.55</v>
@@ -3789,7 +3789,7 @@
         <v>1.08</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y28" t="n">
         <v>1.22</v>
@@ -3804,7 +3804,7 @@
         <v>2.03</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="AD28" t="n">
         <v>1.4</v>
@@ -3813,10 +3813,10 @@
         <v>1.62</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.81</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
         <v>1.3</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4238,10 +4238,10 @@
         <v>19</v>
       </c>
       <c r="O32" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P32" t="n">
-        <v>2.85</v>
+        <v>2.99</v>
       </c>
       <c r="Q32" t="n">
         <v>10.7</v>
@@ -4271,7 +4271,7 @@
         <v>1.12</v>
       </c>
       <c r="Z32" t="n">
-        <v>6.33</v>
+        <v>5.2</v>
       </c>
       <c r="AA32" t="n">
         <v>1.45</v>
@@ -4286,7 +4286,7 @@
         <v>1.65</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="AF32" t="n">
         <v>1.65</v>

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI32"/>
+  <dimension ref="A1:AI34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.65</v>
+        <v>5.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>3.77</v>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>1.6</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2</v>
+        <v>6.42</v>
       </c>
       <c r="P16" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.54</v>
+        <v>2.1</v>
       </c>
       <c r="R16" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="S16" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="T16" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="V16" t="n">
-        <v>8.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
         <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.2</v>
+        <v>3.44</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.53</v>
+        <v>1.13</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5.6</v>
+        <v>2.65</v>
       </c>
       <c r="M17" t="n">
-        <v>3.77</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>1.6</v>
+        <v>2.75</v>
       </c>
       <c r="O17" t="n">
-        <v>6.42</v>
+        <v>3.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.1</v>
+        <v>3.54</v>
       </c>
       <c r="R17" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="S17" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="T17" t="n">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="U17" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>7.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
         <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.44</v>
+        <v>4.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.13</v>
+        <v>1.53</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="M20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T20" t="n">
         <v>3.15</v>
       </c>
-      <c r="N20" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="O20" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.48</v>
-      </c>
       <c r="U20" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="V20" t="n">
-        <v>9.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.54</v>
+        <v>2.99</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.5</v>
+        <v>4.09</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.39</v>
+        <v>1.84</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46019.52083333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N21" t="n">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="O21" t="n">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="P21" t="n">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.63</v>
+        <v>3.06</v>
       </c>
       <c r="R21" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="S21" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T21" t="n">
-        <v>3.15</v>
+        <v>3.48</v>
       </c>
       <c r="U21" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="V21" t="n">
-        <v>8.199999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="W21" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.39</v>
       </c>
-      <c r="Z21" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46019.52083333334</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4299,6 +4299,244 @@
       </c>
       <c r="AI32" s="3" t="n">
         <v>46019.72916666666</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>46019</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Spanish Town Police FC</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Treasure Beach</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" s="3" t="n">
+        <v>46019.75</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>46019</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Waterhouse</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Molynes United</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="3" t="n">
+        <v>46019.85416666666</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.05</v>
+        <v>2.65</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>1.77</v>
+        <v>2.75</v>
       </c>
       <c r="O15" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.62</v>
+        <v>3.54</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="S15" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="T15" t="n">
-        <v>2.98</v>
+        <v>3.28</v>
       </c>
       <c r="U15" t="n">
         <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AB15" t="n">
         <v>1.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.48</v>
+        <v>4.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.65</v>
+        <v>4.05</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>2.75</v>
+        <v>1.77</v>
       </c>
       <c r="O17" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="P17" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.54</v>
+        <v>2.62</v>
       </c>
       <c r="R17" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="T17" t="n">
-        <v>3.28</v>
+        <v>2.98</v>
       </c>
       <c r="U17" t="n">
         <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.88</v>
+        <v>3.12</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="AB17" t="n">
         <v>1.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.2</v>
+        <v>3.48</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46019.45833333334</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N24" t="n">
-        <v>3.45</v>
+        <v>1.92</v>
       </c>
       <c r="O24" t="n">
-        <v>2.85</v>
+        <v>3.16</v>
       </c>
       <c r="P24" t="n">
-        <v>2.06</v>
+        <v>2.54</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>2.53</v>
       </c>
       <c r="R24" t="n">
-        <v>1.43</v>
+        <v>1.13</v>
       </c>
       <c r="S24" t="n">
-        <v>2.81</v>
+        <v>4.6</v>
       </c>
       <c r="T24" t="n">
-        <v>2.98</v>
+        <v>1.81</v>
       </c>
       <c r="U24" t="n">
-        <v>1.39</v>
+        <v>1.89</v>
       </c>
       <c r="V24" t="n">
-        <v>7.9</v>
+        <v>3.3</v>
       </c>
       <c r="W24" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.63</v>
+        <v>8</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.97</v>
+        <v>1.25</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.83</v>
+        <v>3.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.38</v>
+        <v>1.82</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.27</v>
+        <v>1.88</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.76</v>
+        <v>1.3</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.98</v>
+        <v>3.58</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46019.5625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="M25" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>1.92</v>
+        <v>3.45</v>
       </c>
       <c r="O25" t="n">
-        <v>3.16</v>
+        <v>2.85</v>
       </c>
       <c r="P25" t="n">
-        <v>2.54</v>
+        <v>2.06</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.53</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>1.13</v>
+        <v>1.43</v>
       </c>
       <c r="S25" t="n">
-        <v>4.6</v>
+        <v>2.81</v>
       </c>
       <c r="T25" t="n">
-        <v>1.81</v>
+        <v>2.98</v>
       </c>
       <c r="U25" t="n">
-        <v>1.89</v>
+        <v>1.39</v>
       </c>
       <c r="V25" t="n">
-        <v>3.3</v>
+        <v>7.9</v>
       </c>
       <c r="W25" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.02</v>
+        <v>1.33</v>
       </c>
       <c r="Z25" t="n">
-        <v>8</v>
+        <v>3.63</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.25</v>
+        <v>1.97</v>
       </c>
       <c r="AB25" t="n">
-        <v>3.5</v>
+        <v>1.83</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.82</v>
+        <v>3.38</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.88</v>
+        <v>1.27</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.3</v>
+        <v>1.76</v>
       </c>
       <c r="AF25" t="n">
-        <v>3.58</v>
+        <v>1.98</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46019.5625</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G31" t="n">

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -778,28 +778,28 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="M3" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="N3" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="O3" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="P3" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="S3" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="T3" t="n">
         <v>2.65</v>
@@ -817,34 +817,34 @@
         <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.85</v>
+        <v>3.54</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.58</v>
+        <v>1.88</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AG3" t="n">
         <v>1.24</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46019.20833333334</v>
@@ -1263,13 +1263,13 @@
         <v>4.3</v>
       </c>
       <c r="O7" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="P7" t="n">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.34</v>
+        <v>5.18</v>
       </c>
       <c r="R7" t="n">
         <v>1.37</v>
@@ -1278,7 +1278,7 @@
         <v>2.69</v>
       </c>
       <c r="T7" t="n">
-        <v>2.81</v>
+        <v>2.55</v>
       </c>
       <c r="U7" t="n">
         <v>1.37</v>
@@ -1305,22 +1305,22 @@
         <v>1.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AD7" t="n">
         <v>1.27</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46019.33333333334</v>
@@ -1382,10 +1382,10 @@
         <v>8.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="P8" t="n">
-        <v>2.48</v>
+        <v>2.34</v>
       </c>
       <c r="Q8" t="n">
         <v>5.99</v>
@@ -1403,16 +1403,16 @@
         <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="W8" t="n">
         <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z8" t="n">
         <v>3.68</v>
@@ -1436,7 +1436,7 @@
         <v>1.67</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AH8" t="n">
         <v>2.9</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.65</v>
+        <v>5.6</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>3.77</v>
       </c>
       <c r="N15" t="n">
-        <v>2.75</v>
+        <v>1.6</v>
       </c>
       <c r="O15" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="P15" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.54</v>
+        <v>2.16</v>
       </c>
       <c r="R15" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="T15" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="V15" t="n">
-        <v>8.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
         <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.2</v>
+        <v>3.44</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.53</v>
+        <v>1.13</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.6</v>
+        <v>4.05</v>
       </c>
       <c r="M16" t="n">
-        <v>3.77</v>
+        <v>3.35</v>
       </c>
       <c r="N16" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="O16" t="n">
-        <v>6.42</v>
+        <v>4.31</v>
       </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.1</v>
+        <v>2.49</v>
       </c>
       <c r="R16" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="U16" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="V16" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.44</v>
+        <v>3.48</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.05</v>
+        <v>2.65</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>1.77</v>
+        <v>2.75</v>
       </c>
       <c r="O17" t="n">
-        <v>3.7</v>
+        <v>3.26</v>
       </c>
       <c r="P17" t="n">
         <v>2.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.62</v>
+        <v>3.54</v>
       </c>
       <c r="R17" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S17" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="T17" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="U17" t="n">
         <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AB17" t="n">
         <v>1.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.48</v>
+        <v>4.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46019.47916666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46019.47916666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="O20" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="P20" t="n">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.63</v>
+        <v>3.04</v>
       </c>
       <c r="R20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V20" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y20" t="n">
         <v>1.46</v>
       </c>
-      <c r="S20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V20" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
+      <c r="Z20" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.39</v>
       </c>
-      <c r="Z20" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AH20" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46019.52083333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="M21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="O21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T21" t="n">
         <v>3.15</v>
       </c>
-      <c r="N21" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="O21" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.48</v>
-      </c>
       <c r="U21" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="V21" t="n">
-        <v>9.9</v>
+        <v>8.1</v>
       </c>
       <c r="W21" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.54</v>
+        <v>2.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.5</v>
+        <v>4.09</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46019.52083333334</v>
@@ -3334,7 +3334,7 @@
         <v>1.88</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AF24" t="n">
         <v>3.58</v>
@@ -3405,7 +3405,7 @@
         <v>3.45</v>
       </c>
       <c r="O25" t="n">
-        <v>2.85</v>
+        <v>2.92</v>
       </c>
       <c r="P25" t="n">
         <v>2.06</v>
@@ -3417,16 +3417,16 @@
         <v>1.43</v>
       </c>
       <c r="S25" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="T25" t="n">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="U25" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
-        <v>7.9</v>
+        <v>7</v>
       </c>
       <c r="W25" t="n">
         <v>1.05</v>
@@ -3453,10 +3453,10 @@
         <v>1.27</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AG25" t="n">
         <v>1.33</v>
@@ -3533,19 +3533,19 @@
         <v>4.6</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S26" t="n">
         <v>2.75</v>
       </c>
       <c r="T26" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="U26" t="n">
         <v>1.39</v>
       </c>
       <c r="V26" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W26" t="n">
         <v>1.06</v>
@@ -3566,7 +3566,7 @@
         <v>1.77</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AD26" t="n">
         <v>1.28</v>
@@ -3643,13 +3643,13 @@
         <v>2.25</v>
       </c>
       <c r="O27" t="n">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="P27" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="R27" t="n">
         <v>1.43</v>
@@ -3658,10 +3658,10 @@
         <v>2.62</v>
       </c>
       <c r="T27" t="n">
-        <v>2.9</v>
+        <v>2.99</v>
       </c>
       <c r="U27" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V27" t="n">
         <v>7.9</v>
@@ -3673,10 +3673,10 @@
         <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="AA27" t="n">
         <v>2.25</v>
@@ -3691,10 +3691,10 @@
         <v>1.25</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AG27" t="n">
         <v>1.35</v>
@@ -3762,16 +3762,16 @@
         <v>2.12</v>
       </c>
       <c r="O28" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="P28" t="n">
         <v>2.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="R28" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="S28" t="n">
         <v>3.05</v>
@@ -3783,7 +3783,7 @@
         <v>1.47</v>
       </c>
       <c r="V28" t="n">
-        <v>6.55</v>
+        <v>6</v>
       </c>
       <c r="W28" t="n">
         <v>1.08</v>
@@ -3795,7 +3795,7 @@
         <v>1.22</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.1</v>
+        <v>3.86</v>
       </c>
       <c r="AA28" t="n">
         <v>1.78</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4241,7 +4241,7 @@
         <v>1.47</v>
       </c>
       <c r="P32" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="Q32" t="n">
         <v>10.7</v>
@@ -4253,7 +4253,7 @@
         <v>3.85</v>
       </c>
       <c r="T32" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U32" t="n">
         <v>1.73</v>
@@ -4289,7 +4289,7 @@
         <v>2.25</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AG32" t="n">
         <v>1.08</v>

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -662,7 +662,7 @@
         <v>2.37</v>
       </c>
       <c r="M2" t="n">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="N2" t="n">
         <v>2.66</v>
@@ -671,7 +671,7 @@
         <v>3.02</v>
       </c>
       <c r="P2" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="Q2" t="n">
         <v>3.25</v>
@@ -695,7 +695,7 @@
         <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
         <v>1.25</v>
@@ -710,7 +710,7 @@
         <v>1.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD2" t="n">
         <v>1.26</v>
@@ -897,34 +897,34 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="M4" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>3.61</v>
+        <v>4.1</v>
       </c>
       <c r="O4" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="P4" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.45</v>
+        <v>3.95</v>
       </c>
       <c r="R4" t="n">
         <v>1.37</v>
       </c>
       <c r="S4" t="n">
-        <v>2.9</v>
+        <v>2.71</v>
       </c>
       <c r="T4" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="U4" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="V4" t="n">
         <v>7.5</v>
@@ -936,34 +936,34 @@
         <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AG4" t="n">
         <v>1.23</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46019.22916666666</v>
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="M5" t="n">
         <v>4.8</v>
       </c>
       <c r="N5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="O5" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="P5" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.5</v>
+        <v>7.43</v>
       </c>
       <c r="R5" t="n">
         <v>1.28</v>
@@ -1040,7 +1040,7 @@
         <v>3.18</v>
       </c>
       <c r="T5" t="n">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="U5" t="n">
         <v>1.5</v>
@@ -1055,13 +1055,13 @@
         <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z5" t="n">
         <v>4.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB5" t="n">
         <v>2.23</v>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="M6" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="N6" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="O6" t="n">
-        <v>5.74</v>
+        <v>6.75</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="R6" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S6" t="n">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="T6" t="n">
         <v>2.5</v>
       </c>
       <c r="U6" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="V6" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="W6" t="n">
         <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.78</v>
+        <v>3.55</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AB6" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46019.3125</v>
@@ -1260,7 +1260,7 @@
         <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O7" t="n">
         <v>2.35</v>
@@ -1272,37 +1272,37 @@
         <v>5.18</v>
       </c>
       <c r="R7" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S7" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="T7" t="n">
-        <v>2.55</v>
+        <v>2.81</v>
       </c>
       <c r="U7" t="n">
         <v>1.37</v>
       </c>
       <c r="V7" t="n">
-        <v>6.95</v>
+        <v>6.9</v>
       </c>
       <c r="W7" t="n">
         <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC7" t="n">
         <v>3.14</v>
@@ -1373,25 +1373,25 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="M8" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="N8" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="P8" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.99</v>
+        <v>7.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S8" t="n">
         <v>3.05</v>
@@ -1403,31 +1403,31 @@
         <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>6.25</v>
+        <v>6.85</v>
       </c>
       <c r="W8" t="n">
         <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
         <v>1.23</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AB8" t="n">
         <v>1.95</v>
       </c>
       <c r="AC8" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AE8" t="n">
         <v>2.1</v>
@@ -1436,10 +1436,10 @@
         <v>1.67</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46019.35416666666</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.11</v>
+        <v>1.97</v>
       </c>
       <c r="M9" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="O9" t="n">
         <v>2.75</v>
@@ -1510,10 +1510,10 @@
         <v>4.24</v>
       </c>
       <c r="R9" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S9" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="T9" t="n">
         <v>2.88</v>
@@ -1537,13 +1537,13 @@
         <v>2.97</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.34</v>
+        <v>3.59</v>
       </c>
       <c r="AD9" t="n">
         <v>1.24</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.36</v>
+        <v>1.68</v>
       </c>
       <c r="M13" t="n">
-        <v>3.03</v>
+        <v>3.29</v>
       </c>
       <c r="N13" t="n">
-        <v>2.71</v>
+        <v>4.73</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O14" t="n">
         <v>2.87</v>
@@ -2114,10 +2114,10 @@
         <v>3.06</v>
       </c>
       <c r="U14" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W14" t="n">
         <v>1.02</v>
@@ -2132,10 +2132,10 @@
         <v>3.17</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AC14" t="n">
         <v>3.6</v>
@@ -2150,10 +2150,10 @@
         <v>1.9</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46019.41666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,37 +2206,37 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.6</v>
+        <v>2.33</v>
       </c>
       <c r="M15" t="n">
-        <v>3.77</v>
+        <v>2.95</v>
       </c>
       <c r="N15" t="n">
-        <v>1.6</v>
+        <v>2.87</v>
       </c>
       <c r="O15" t="n">
-        <v>6</v>
+        <v>3.26</v>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.16</v>
+        <v>3.54</v>
       </c>
       <c r="R15" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="S15" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="U15" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>7.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W15" t="n">
         <v>1.06</v>
@@ -2245,34 +2245,34 @@
         <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.05</v>
+        <v>2.29</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.44</v>
+        <v>4.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.13</v>
+        <v>1.53</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2325,16 +2325,16 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.05</v>
+        <v>3.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="O16" t="n">
-        <v>4.31</v>
+        <v>4.34</v>
       </c>
       <c r="P16" t="n">
         <v>2.02</v>
@@ -2343,16 +2343,16 @@
         <v>2.49</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
         <v>2.66</v>
       </c>
       <c r="T16" t="n">
-        <v>3.13</v>
+        <v>2.98</v>
       </c>
       <c r="U16" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
         <v>7.8</v>
@@ -2361,7 +2361,7 @@
         <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
         <v>1.28</v>
@@ -2370,10 +2370,10 @@
         <v>3.08</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AC16" t="n">
         <v>3.48</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,34 +2444,34 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.65</v>
+        <v>6.4</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="N17" t="n">
-        <v>2.75</v>
+        <v>1.43</v>
       </c>
       <c r="O17" t="n">
-        <v>3.26</v>
+        <v>4.94</v>
       </c>
       <c r="P17" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.54</v>
+        <v>2.27</v>
       </c>
       <c r="R17" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S17" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="T17" t="n">
         <v>3.05</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="V17" t="n">
         <v>7.5</v>
@@ -2483,34 +2483,34 @@
         <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.2</v>
+        <v>3.44</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.44</v>
+        <v>2.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.53</v>
+        <v>1.13</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46019.47916666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46019.47916666666</v>
@@ -2804,10 +2804,10 @@
         <v>3.1</v>
       </c>
       <c r="M20" t="n">
-        <v>3.15</v>
+        <v>2.82</v>
       </c>
       <c r="N20" t="n">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="O20" t="n">
         <v>4.1</v>
@@ -2840,16 +2840,16 @@
         <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="Z20" t="n">
         <v>2.54</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="AC20" t="n">
         <v>4.5</v>
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N21" t="n">
-        <v>1.97</v>
+        <v>1.78</v>
       </c>
       <c r="O21" t="n">
         <v>4.6</v>
@@ -2965,10 +2965,10 @@
         <v>2.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC21" t="n">
         <v>4.09</v>
@@ -2977,16 +2977,16 @@
         <v>1.23</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.35</v>
+        <v>1.84</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46019.52083333334</v>
@@ -3158,64 +3158,64 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="M23" t="n">
         <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="O23" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="P23" t="n">
         <v>2.32</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="R23" t="n">
         <v>1.32</v>
       </c>
       <c r="S23" t="n">
-        <v>3.24</v>
+        <v>2.96</v>
       </c>
       <c r="T23" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="U23" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="V23" t="n">
-        <v>6.45</v>
+        <v>6</v>
       </c>
       <c r="W23" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="AB23" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AF23" t="n">
         <v>2.1</v>
@@ -3224,7 +3224,7 @@
         <v>1.23</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46019.54166666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="M24" t="n">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="N24" t="n">
-        <v>1.92</v>
+        <v>3.22</v>
       </c>
       <c r="O24" t="n">
-        <v>3.16</v>
+        <v>2.98</v>
       </c>
       <c r="P24" t="n">
-        <v>2.54</v>
+        <v>2.06</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.53</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>4.6</v>
+        <v>2.98</v>
       </c>
       <c r="T24" t="n">
-        <v>1.81</v>
+        <v>2.93</v>
       </c>
       <c r="U24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V24" t="n">
+        <v>7</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB24" t="n">
         <v>1.89</v>
       </c>
-      <c r="V24" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AC24" t="n">
-        <v>1.82</v>
+        <v>3.38</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.88</v>
+        <v>1.27</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.24</v>
+        <v>1.67</v>
       </c>
       <c r="AF24" t="n">
-        <v>3.58</v>
+        <v>2.09</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46019.5625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.1</v>
+        <v>2.76</v>
       </c>
       <c r="M25" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="N25" t="n">
-        <v>3.45</v>
+        <v>2.07</v>
       </c>
       <c r="O25" t="n">
-        <v>2.92</v>
+        <v>3.16</v>
       </c>
       <c r="P25" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AD25" t="n">
         <v>2.06</v>
       </c>
-      <c r="Q25" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V25" t="n">
-        <v>7</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AE25" t="n">
-        <v>1.74</v>
+        <v>1.24</v>
       </c>
       <c r="AF25" t="n">
-        <v>2</v>
+        <v>3.58</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46019.5625</v>
@@ -3515,16 +3515,16 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="M26" t="n">
-        <v>3.47</v>
+        <v>3.78</v>
       </c>
       <c r="N26" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O26" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="P26" t="n">
         <v>2.15</v>
@@ -3551,7 +3551,7 @@
         <v>1.06</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y26" t="n">
         <v>1.3</v>
@@ -3560,16 +3560,16 @@
         <v>3.16</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC26" t="n">
         <v>3.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE26" t="n">
         <v>1.85</v>
@@ -3578,10 +3578,10 @@
         <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46019.58333333334</v>
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="M27" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N27" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O27" t="n">
         <v>4.05</v>
@@ -3673,16 +3673,16 @@
         <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z27" t="n">
         <v>3.08</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.25</v>
+        <v>2.09</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.55</v>
+        <v>1.79</v>
       </c>
       <c r="AC27" t="n">
         <v>3.65</v>
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.23</v>
+        <v>3.61</v>
       </c>
       <c r="M28" t="n">
-        <v>3.45</v>
+        <v>3.52</v>
       </c>
       <c r="N28" t="n">
-        <v>2.12</v>
+        <v>1.78</v>
       </c>
       <c r="O28" t="n">
         <v>3.5</v>
@@ -3780,7 +3780,7 @@
         <v>2.65</v>
       </c>
       <c r="U28" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="V28" t="n">
         <v>6</v>
@@ -3795,13 +3795,13 @@
         <v>1.22</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.86</v>
+        <v>3.9</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AC28" t="n">
         <v>2.8</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="M32" t="n">
-        <v>7.3</v>
+        <v>7.25</v>
       </c>
       <c r="N32" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O32" t="n">
         <v>1.47</v>
@@ -4259,7 +4259,7 @@
         <v>1.73</v>
       </c>
       <c r="V32" t="n">
-        <v>4.15</v>
+        <v>4.3</v>
       </c>
       <c r="W32" t="n">
         <v>1.18</v>
@@ -4268,28 +4268,28 @@
         <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z32" t="n">
         <v>5.2</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.55</v>
+        <v>2.72</v>
       </c>
       <c r="AC32" t="n">
         <v>2.08</v>
       </c>
       <c r="AD32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AF32" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.55</v>
       </c>
       <c r="AG32" t="n">
         <v>1.08</v>

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="O3" t="n">
         <v>2.12</v>
@@ -823,10 +823,10 @@
         <v>3.54</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.88</v>
+        <v>1.58</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="AC3" t="n">
         <v>2.94</v>
@@ -1260,7 +1260,7 @@
         <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O7" t="n">
         <v>2.35</v>
@@ -1299,10 +1299,10 @@
         <v>3.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
         <v>3.14</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.68</v>
+        <v>2.36</v>
       </c>
       <c r="M13" t="n">
-        <v>3.29</v>
+        <v>3.03</v>
       </c>
       <c r="N13" t="n">
-        <v>4.73</v>
+        <v>2.71</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.33</v>
+        <v>4.05</v>
       </c>
       <c r="M15" t="n">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>2.87</v>
+        <v>1.77</v>
       </c>
       <c r="O15" t="n">
-        <v>3.26</v>
+        <v>4.34</v>
       </c>
       <c r="P15" t="n">
         <v>2.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.54</v>
+        <v>2.49</v>
       </c>
       <c r="R15" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="T15" t="n">
-        <v>3.28</v>
+        <v>2.98</v>
       </c>
       <c r="U15" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.29</v>
+        <v>2.03</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.2</v>
+        <v>3.48</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.6</v>
+        <v>2.33</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>2.95</v>
       </c>
       <c r="N16" t="n">
-        <v>1.93</v>
+        <v>2.87</v>
       </c>
       <c r="O16" t="n">
-        <v>4.34</v>
+        <v>3.26</v>
       </c>
       <c r="P16" t="n">
         <v>2.02</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.49</v>
+        <v>3.54</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="S16" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="T16" t="n">
-        <v>2.98</v>
+        <v>3.28</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.02</v>
+        <v>2.29</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.48</v>
+        <v>4.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46019.45833333334</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G31" t="n">

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -1373,61 +1373,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="M8" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="N8" t="n">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="O8" t="n">
         <v>1.85</v>
       </c>
       <c r="P8" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="Q8" t="n">
         <v>7.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="U8" t="n">
         <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>6.85</v>
+        <v>6.25</v>
       </c>
       <c r="W8" t="n">
         <v>1.07</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
         <v>1.23</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AB8" t="n">
         <v>1.95</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE8" t="n">
         <v>2.1</v>
@@ -1436,10 +1436,10 @@
         <v>1.67</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46019.35416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.05</v>
+        <v>5.6</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>3.77</v>
       </c>
       <c r="N15" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="O15" t="n">
-        <v>4.34</v>
+        <v>6</v>
       </c>
       <c r="P15" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.49</v>
+        <v>2.1</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="T15" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="V15" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X15" t="n">
         <v>1.02</v>
       </c>
-      <c r="X15" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y15" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.29</v>
+        <v>2.43</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2325,34 +2325,34 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.33</v>
+        <v>2.65</v>
       </c>
       <c r="M16" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="O16" t="n">
-        <v>3.26</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.54</v>
+        <v>3.59</v>
       </c>
       <c r="R16" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="S16" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="T16" t="n">
         <v>3.28</v>
       </c>
       <c r="U16" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V16" t="n">
         <v>8.699999999999999</v>
@@ -2370,28 +2370,28 @@
         <v>2.88</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC16" t="n">
         <v>4.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AF16" t="n">
         <v>1.91</v>
       </c>
       <c r="AG16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6.4</v>
+        <v>4.05</v>
       </c>
       <c r="M17" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>1.43</v>
+        <v>1.77</v>
       </c>
       <c r="O17" t="n">
-        <v>4.94</v>
+        <v>4.34</v>
       </c>
       <c r="P17" t="n">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.27</v>
+        <v>2.49</v>
       </c>
       <c r="R17" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="S17" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="T17" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="U17" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AA17" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.44</v>
+        <v>3.48</v>
       </c>
       <c r="AD17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.13</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46019.47916666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46019.47916666666</v>
@@ -2804,28 +2804,28 @@
         <v>3.1</v>
       </c>
       <c r="M20" t="n">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="O20" t="n">
-        <v>4.1</v>
+        <v>3.66</v>
       </c>
       <c r="P20" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S20" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="T20" t="n">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="U20" t="n">
         <v>1.26</v>
@@ -2834,37 +2834,37 @@
         <v>9.9</v>
       </c>
       <c r="W20" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="AD20" t="n">
         <v>1.18</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AF20" t="n">
         <v>1.73</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="AH20" t="n">
         <v>1.35</v>
@@ -2920,22 +2920,22 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="M21" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>1.78</v>
+        <v>1.97</v>
       </c>
       <c r="O21" t="n">
-        <v>4.6</v>
+        <v>4.25</v>
       </c>
       <c r="P21" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="R21" t="n">
         <v>1.46</v>
@@ -2944,13 +2944,13 @@
         <v>2.53</v>
       </c>
       <c r="T21" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="U21" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="V21" t="n">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="W21" t="n">
         <v>1.02</v>
@@ -2959,34 +2959,34 @@
         <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.09</v>
+        <v>3.84</v>
       </c>
       <c r="AD21" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.23</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.18</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46019.52083333334</v>
@@ -3277,40 +3277,40 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="M24" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>3.22</v>
+        <v>3.45</v>
       </c>
       <c r="O24" t="n">
-        <v>2.98</v>
+        <v>2.85</v>
       </c>
       <c r="P24" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="Q24" t="n">
         <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>2.98</v>
+        <v>2.75</v>
       </c>
       <c r="T24" t="n">
-        <v>2.93</v>
+        <v>2.75</v>
       </c>
       <c r="U24" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="V24" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X24" t="n">
         <v>1</v>
@@ -3322,28 +3322,28 @@
         <v>3.63</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="AD24" t="n">
         <v>1.27</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46019.5625</v>
@@ -3396,22 +3396,22 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="N25" t="n">
-        <v>2.07</v>
+        <v>1.92</v>
       </c>
       <c r="O25" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="P25" t="n">
         <v>2.54</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="R25" t="n">
         <v>1.13</v>
@@ -3420,13 +3420,13 @@
         <v>4.6</v>
       </c>
       <c r="T25" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="U25" t="n">
         <v>1.89</v>
       </c>
       <c r="V25" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="W25" t="n">
         <v>1.22</v>
@@ -3441,16 +3441,16 @@
         <v>8</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AB25" t="n">
-        <v>3.66</v>
+        <v>3.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.06</v>
+        <v>1.88</v>
       </c>
       <c r="AE25" t="n">
         <v>1.24</v>
@@ -3459,7 +3459,7 @@
         <v>3.58</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
         <v>1.36</v>
@@ -3515,37 +3515,37 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="M26" t="n">
-        <v>3.78</v>
+        <v>3.47</v>
       </c>
       <c r="N26" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O26" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="P26" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="n">
         <v>4.6</v>
       </c>
       <c r="R26" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S26" t="n">
         <v>2.75</v>
       </c>
       <c r="T26" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="U26" t="n">
         <v>1.39</v>
       </c>
       <c r="V26" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="W26" t="n">
         <v>1.06</v>
@@ -3554,31 +3554,31 @@
         <v>1.06</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="AD26" t="n">
         <v>1.25</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AF26" t="n">
         <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AH26" t="n">
         <v>2.05</v>
@@ -3634,70 +3634,70 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="M27" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N27" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="O27" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="P27" t="n">
-        <v>2.09</v>
+        <v>1.99</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="R27" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S27" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="T27" t="n">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="U27" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V27" t="n">
-        <v>7.9</v>
+        <v>7</v>
       </c>
       <c r="W27" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X27" t="n">
         <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.79</v>
+        <v>1.55</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.65</v>
+        <v>3.54</v>
       </c>
       <c r="AD27" t="n">
         <v>1.25</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AH27" t="n">
         <v>1.34</v>
@@ -3753,43 +3753,43 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.61</v>
+        <v>3.23</v>
       </c>
       <c r="M28" t="n">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="N28" t="n">
-        <v>1.78</v>
+        <v>2.12</v>
       </c>
       <c r="O28" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="P28" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="R28" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="S28" t="n">
         <v>3.05</v>
       </c>
       <c r="T28" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="U28" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="V28" t="n">
-        <v>6</v>
+        <v>6.55</v>
       </c>
       <c r="W28" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X28" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
         <v>1.22</v>
@@ -3798,10 +3798,10 @@
         <v>3.9</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AB28" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AC28" t="n">
         <v>2.8</v>
@@ -3816,10 +3816,10 @@
         <v>2.2</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>1.83</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46019.69791666666</v>
@@ -4229,37 +4229,37 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="M32" t="n">
-        <v>7.25</v>
+        <v>7.3</v>
       </c>
       <c r="N32" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O32" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P32" t="n">
-        <v>3.02</v>
+        <v>3.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>10.7</v>
+        <v>10</v>
       </c>
       <c r="R32" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S32" t="n">
         <v>3.85</v>
       </c>
       <c r="T32" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="U32" t="n">
         <v>1.73</v>
       </c>
       <c r="V32" t="n">
-        <v>4.3</v>
+        <v>4.15</v>
       </c>
       <c r="W32" t="n">
         <v>1.18</v>
@@ -4268,28 +4268,28 @@
         <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z32" t="n">
         <v>5.2</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.72</v>
+        <v>2.55</v>
       </c>
       <c r="AC32" t="n">
         <v>2.08</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.11</v>
+        <v>2.21</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AG32" t="n">
         <v>1.08</v>

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.36</v>
+        <v>1.68</v>
       </c>
       <c r="M13" t="n">
-        <v>3.03</v>
+        <v>3.29</v>
       </c>
       <c r="N13" t="n">
-        <v>2.71</v>
+        <v>4.73</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.6</v>
+        <v>2.65</v>
       </c>
       <c r="M15" t="n">
-        <v>3.77</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>1.6</v>
+        <v>2.75</v>
       </c>
       <c r="O15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.1</v>
+        <v>3.59</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S15" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="T15" t="n">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="U15" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="V15" t="n">
-        <v>7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W15" t="n">
         <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.43</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.12</v>
+        <v>1.44</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.65</v>
+        <v>4.05</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>1.77</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>4.34</v>
       </c>
       <c r="P16" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.59</v>
+        <v>2.49</v>
       </c>
       <c r="R16" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="T16" t="n">
-        <v>3.28</v>
+        <v>2.98</v>
       </c>
       <c r="U16" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="AB16" t="n">
         <v>1.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.2</v>
+        <v>3.48</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.05</v>
+        <v>5.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>3.77</v>
       </c>
       <c r="N17" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="O17" t="n">
-        <v>4.34</v>
+        <v>6</v>
       </c>
       <c r="P17" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.49</v>
+        <v>2.1</v>
       </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="T17" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="V17" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="W17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X17" t="n">
         <v>1.02</v>
       </c>
-      <c r="X17" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y17" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.29</v>
+        <v>2.43</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="M20" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="O20" t="n">
-        <v>3.66</v>
+        <v>4.25</v>
       </c>
       <c r="P20" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="T20" t="n">
         <v>3</v>
       </c>
-      <c r="R20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.4</v>
-      </c>
       <c r="U20" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="V20" t="n">
-        <v>9.9</v>
+        <v>8.5</v>
       </c>
       <c r="W20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X20" t="n">
         <v>1.03</v>
       </c>
-      <c r="X20" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y20" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.55</v>
+        <v>3.84</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE20" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46019.52083333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N21" t="n">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="O21" t="n">
-        <v>4.25</v>
+        <v>3.66</v>
       </c>
       <c r="P21" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V21" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE21" t="n">
         <v>2</v>
       </c>
-      <c r="Q21" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V21" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AF21" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46019.52083333334</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N24" t="n">
-        <v>3.45</v>
+        <v>1.92</v>
       </c>
       <c r="O24" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="P24" t="n">
-        <v>2.05</v>
+        <v>2.54</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>2.45</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="S24" t="n">
-        <v>2.75</v>
+        <v>4.6</v>
       </c>
       <c r="T24" t="n">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4</v>
+        <v>1.89</v>
       </c>
       <c r="V24" t="n">
-        <v>6.75</v>
+        <v>3.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.63</v>
+        <v>8</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.97</v>
+        <v>1.25</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.83</v>
+        <v>3.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.34</v>
+        <v>1.82</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.27</v>
+        <v>1.88</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.74</v>
+        <v>1.24</v>
       </c>
       <c r="AF24" t="n">
-        <v>2</v>
+        <v>3.58</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.66</v>
+        <v>1.36</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46019.5625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="M25" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>1.92</v>
+        <v>3.45</v>
       </c>
       <c r="O25" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="P25" t="n">
-        <v>2.54</v>
+        <v>2.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.45</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>4.6</v>
+        <v>2.75</v>
       </c>
       <c r="T25" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="U25" t="n">
-        <v>1.89</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
-        <v>3.5</v>
+        <v>6.75</v>
       </c>
       <c r="W25" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.02</v>
+        <v>1.33</v>
       </c>
       <c r="Z25" t="n">
-        <v>8</v>
+        <v>3.63</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.25</v>
+        <v>1.97</v>
       </c>
       <c r="AB25" t="n">
-        <v>3.5</v>
+        <v>1.83</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.82</v>
+        <v>3.34</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.88</v>
+        <v>1.27</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.24</v>
+        <v>1.74</v>
       </c>
       <c r="AF25" t="n">
-        <v>3.58</v>
+        <v>2</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.36</v>
+        <v>1.66</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46019.5625</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G30" t="n">

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -659,22 +659,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="M2" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N2" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="O2" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="R2" t="n">
         <v>1.36</v>
@@ -683,7 +683,7 @@
         <v>2.73</v>
       </c>
       <c r="T2" t="n">
-        <v>2.79</v>
+        <v>2.86</v>
       </c>
       <c r="U2" t="n">
         <v>1.35</v>
@@ -695,7 +695,7 @@
         <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
         <v>1.25</v>
@@ -704,13 +704,13 @@
         <v>3.28</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AD2" t="n">
         <v>1.26</v>
@@ -722,7 +722,7 @@
         <v>2.02</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
         <v>1.46</v>
@@ -787,13 +787,13 @@
         <v>6.2</v>
       </c>
       <c r="O3" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="P3" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="R3" t="n">
         <v>1.33</v>
@@ -802,7 +802,7 @@
         <v>3.02</v>
       </c>
       <c r="T3" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="U3" t="n">
         <v>1.42</v>
@@ -829,7 +829,7 @@
         <v>2.25</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.94</v>
+        <v>3.02</v>
       </c>
       <c r="AD3" t="n">
         <v>1.31</v>
@@ -841,7 +841,7 @@
         <v>1.87</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AH3" t="n">
         <v>2.33</v>
@@ -897,37 +897,37 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="N4" t="n">
-        <v>4.1</v>
+        <v>3.77</v>
       </c>
       <c r="O4" t="n">
-        <v>2.29</v>
+        <v>2.47</v>
       </c>
       <c r="P4" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.95</v>
+        <v>4.61</v>
       </c>
       <c r="R4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="T4" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U4" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="W4" t="n">
         <v>1.03</v>
@@ -936,34 +936,34 @@
         <v>1.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z4" t="n">
         <v>3.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AD4" t="n">
         <v>1.31</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46019.22916666666</v>
@@ -1266,37 +1266,37 @@
         <v>2.35</v>
       </c>
       <c r="P7" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.18</v>
+        <v>4.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
         <v>2.73</v>
       </c>
       <c r="T7" t="n">
-        <v>2.81</v>
+        <v>2.89</v>
       </c>
       <c r="U7" t="n">
         <v>1.37</v>
       </c>
       <c r="V7" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="W7" t="n">
         <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.2</v>
+        <v>3.43</v>
       </c>
       <c r="AA7" t="n">
         <v>1.9</v>
@@ -1305,22 +1305,22 @@
         <v>1.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="AD7" t="n">
         <v>1.27</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46019.33333333334</v>
@@ -1391,13 +1391,13 @@
         <v>7.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="U8" t="n">
         <v>1.44</v>
@@ -1427,7 +1427,7 @@
         <v>3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE8" t="n">
         <v>2.1</v>
@@ -1439,7 +1439,7 @@
         <v>1.2</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46019.35416666666</v>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.97</v>
+        <v>2.09</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2</v>
+        <v>3.11</v>
       </c>
       <c r="N9" t="n">
         <v>3.3</v>
@@ -1504,13 +1504,13 @@
         <v>2.75</v>
       </c>
       <c r="P9" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.24</v>
+        <v>3.72</v>
       </c>
       <c r="R9" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
         <v>2.53</v>
@@ -1537,16 +1537,16 @@
         <v>2.97</v>
       </c>
       <c r="AA9" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB9" t="n">
         <v>1.71</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.59</v>
+        <v>3.34</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE9" t="n">
         <v>1.78</v>
@@ -1555,7 +1555,7 @@
         <v>1.89</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
         <v>1.58</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.68</v>
+        <v>2.36</v>
       </c>
       <c r="M13" t="n">
-        <v>3.29</v>
+        <v>3.03</v>
       </c>
       <c r="N13" t="n">
-        <v>4.73</v>
+        <v>2.71</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,37 +2206,37 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O15" t="n">
+        <v>6</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S15" t="n">
         <v>2.65</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O15" t="n">
-        <v>3</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.75</v>
-      </c>
       <c r="T15" t="n">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="V15" t="n">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="W15" t="n">
         <v>1.06</v>
@@ -2245,34 +2245,34 @@
         <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>2.43</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.44</v>
+        <v>1.12</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.05</v>
+        <v>2.65</v>
       </c>
       <c r="M16" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>1.77</v>
+        <v>2.75</v>
       </c>
       <c r="O16" t="n">
-        <v>4.34</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.49</v>
+        <v>3.59</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="T16" t="n">
-        <v>2.98</v>
+        <v>3.28</v>
       </c>
       <c r="U16" t="n">
         <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AB16" t="n">
         <v>1.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.48</v>
+        <v>4.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5.6</v>
+        <v>4.05</v>
       </c>
       <c r="M17" t="n">
-        <v>3.77</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="O17" t="n">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.1</v>
+        <v>2.64</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S17" t="n">
         <v>2.65</v>
       </c>
       <c r="T17" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="U17" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.05</v>
+        <v>3.12</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="AD17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.12</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2584,13 +2584,13 @@
         <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="T18" t="n">
         <v>2.2</v>
       </c>
       <c r="U18" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="V18" t="n">
         <v>4.9</v>
@@ -2602,10 +2602,10 @@
         <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.94</v>
+        <v>4.45</v>
       </c>
       <c r="AA18" t="n">
         <v>1.57</v>
@@ -2825,13 +2825,13 @@
         <v>2.53</v>
       </c>
       <c r="T20" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="V20" t="n">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="W20" t="n">
         <v>1.02</v>
@@ -2941,7 +2941,7 @@
         <v>1.5</v>
       </c>
       <c r="S21" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="T21" t="n">
         <v>3.4</v>
@@ -2962,7 +2962,7 @@
         <v>1.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="AA21" t="n">
         <v>2.35</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="M24" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>1.92</v>
+        <v>3.45</v>
       </c>
       <c r="O24" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="P24" t="n">
-        <v>2.54</v>
+        <v>2.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.45</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>4.6</v>
+        <v>2.77</v>
       </c>
       <c r="T24" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="U24" t="n">
-        <v>1.89</v>
+        <v>1.4</v>
       </c>
       <c r="V24" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.02</v>
+        <v>1.33</v>
       </c>
       <c r="Z24" t="n">
-        <v>8</v>
+        <v>3.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.25</v>
+        <v>1.97</v>
       </c>
       <c r="AB24" t="n">
-        <v>3.5</v>
+        <v>1.83</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.82</v>
+        <v>3.34</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.88</v>
+        <v>1.27</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.24</v>
+        <v>1.67</v>
       </c>
       <c r="AF24" t="n">
-        <v>3.58</v>
+        <v>2.01</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46019.5625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N25" t="n">
-        <v>3.45</v>
+        <v>1.92</v>
       </c>
       <c r="O25" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="P25" t="n">
-        <v>2.05</v>
+        <v>2.54</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>2.45</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="S25" t="n">
-        <v>2.75</v>
+        <v>4.6</v>
       </c>
       <c r="T25" t="n">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>1.89</v>
       </c>
       <c r="V25" t="n">
-        <v>6.75</v>
+        <v>3.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.63</v>
+        <v>8</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.97</v>
+        <v>1.25</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.83</v>
+        <v>3.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.34</v>
+        <v>1.82</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.27</v>
+        <v>1.88</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.74</v>
+        <v>1.24</v>
       </c>
       <c r="AF25" t="n">
-        <v>2</v>
+        <v>3.58</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.66</v>
+        <v>1.36</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46019.5625</v>
@@ -3539,7 +3539,7 @@
         <v>2.75</v>
       </c>
       <c r="T26" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U26" t="n">
         <v>1.39</v>
@@ -3646,13 +3646,13 @@
         <v>4</v>
       </c>
       <c r="P27" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="R27" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
         <v>2.85</v>
@@ -3780,10 +3780,10 @@
         <v>2.45</v>
       </c>
       <c r="U28" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="V28" t="n">
-        <v>6.55</v>
+        <v>6.5</v>
       </c>
       <c r="W28" t="n">
         <v>1.09</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4268,7 +4268,7 @@
         <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z32" t="n">
         <v>5.2</v>

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.3</v>
+        <v>6.5</v>
       </c>
       <c r="M5" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="N5" t="n">
-        <v>8</v>
+        <v>1.41</v>
       </c>
       <c r="O5" t="n">
-        <v>1.81</v>
+        <v>6</v>
       </c>
       <c r="P5" t="n">
-        <v>2.39</v>
+        <v>2.29</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.43</v>
+        <v>1.92</v>
       </c>
       <c r="R5" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S5" t="n">
-        <v>3.18</v>
+        <v>3.02</v>
       </c>
       <c r="T5" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="V5" t="n">
-        <v>5.35</v>
+        <v>5.75</v>
       </c>
       <c r="W5" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
         <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.25</v>
+        <v>4.21</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.42</v>
+        <v>2.59</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.12</v>
+        <v>2.16</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.94</v>
+        <v>1.04</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46019.3125</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>6.4</v>
+        <v>1.32</v>
       </c>
       <c r="M6" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>1.43</v>
+        <v>7.8</v>
       </c>
       <c r="O6" t="n">
-        <v>6.75</v>
+        <v>1.7</v>
       </c>
       <c r="P6" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.92</v>
+        <v>7.1</v>
       </c>
       <c r="R6" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S6" t="n">
-        <v>3.02</v>
+        <v>3.18</v>
       </c>
       <c r="T6" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="U6" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="V6" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="AA6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF6" t="n">
         <v>1.83</v>
       </c>
-      <c r="AB6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AG6" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46019.3125</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2087,34 +2087,34 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O14" t="n">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="P14" t="n">
         <v>2.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="R14" t="n">
         <v>1.4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="T14" t="n">
-        <v>3.06</v>
+        <v>2.96</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="V14" t="n">
         <v>8</v>
@@ -2129,16 +2129,16 @@
         <v>1.29</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.17</v>
+        <v>3.04</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AB14" t="n">
         <v>1.58</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="AD14" t="n">
         <v>1.21</v>
@@ -2150,10 +2150,10 @@
         <v>1.9</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46019.41666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.6</v>
+        <v>2.65</v>
       </c>
       <c r="M15" t="n">
-        <v>3.77</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>1.6</v>
+        <v>2.75</v>
       </c>
       <c r="O15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.1</v>
+        <v>3.59</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="T15" t="n">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="U15" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
         <v>1.06</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.43</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.12</v>
+        <v>1.44</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O16" t="n">
+        <v>6</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S16" t="n">
         <v>2.65</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O16" t="n">
-        <v>3</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.6</v>
-      </c>
       <c r="T16" t="n">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="V16" t="n">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
         <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>2.43</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>1.12</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="O20" t="n">
-        <v>4.25</v>
+        <v>3.66</v>
       </c>
       <c r="P20" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V20" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE20" t="n">
         <v>2</v>
       </c>
-      <c r="Q20" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V20" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AF20" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46019.52083333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="M21" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="O21" t="n">
-        <v>3.66</v>
+        <v>4.25</v>
       </c>
       <c r="P21" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="S21" t="n">
-        <v>2.34</v>
+        <v>2.53</v>
       </c>
       <c r="T21" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U21" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="V21" t="n">
-        <v>9.9</v>
+        <v>8.1</v>
       </c>
       <c r="W21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X21" t="n">
         <v>1.03</v>
       </c>
-      <c r="X21" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y21" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.54</v>
+        <v>2.95</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.55</v>
+        <v>3.84</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE21" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46019.52083333334</v>
@@ -3158,19 +3158,19 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="M23" t="n">
         <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O23" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="P23" t="n">
-        <v>2.32</v>
+        <v>2.13</v>
       </c>
       <c r="Q23" t="n">
         <v>4.2</v>
@@ -3179,7 +3179,7 @@
         <v>1.32</v>
       </c>
       <c r="S23" t="n">
-        <v>2.96</v>
+        <v>2.85</v>
       </c>
       <c r="T23" t="n">
         <v>2.56</v>
@@ -3188,7 +3188,7 @@
         <v>1.42</v>
       </c>
       <c r="V23" t="n">
-        <v>6</v>
+        <v>6.35</v>
       </c>
       <c r="W23" t="n">
         <v>1.06</v>
@@ -3197,19 +3197,19 @@
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="Z23" t="n">
         <v>3.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="AD23" t="n">
         <v>1.34</v>
@@ -3218,7 +3218,7 @@
         <v>1.62</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AG23" t="n">
         <v>1.23</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N24" t="n">
-        <v>3.45</v>
+        <v>1.92</v>
       </c>
       <c r="O24" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>2.05</v>
+        <v>2.54</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>2.45</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>1.13</v>
       </c>
       <c r="S24" t="n">
-        <v>2.77</v>
+        <v>4.6</v>
       </c>
       <c r="T24" t="n">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4</v>
+        <v>1.89</v>
       </c>
       <c r="V24" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.3</v>
+        <v>8</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.97</v>
+        <v>1.25</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.83</v>
+        <v>3.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.34</v>
+        <v>1.82</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.27</v>
+        <v>1.88</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.67</v>
+        <v>1.24</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.01</v>
+        <v>3.58</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46019.5625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="M25" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>1.92</v>
+        <v>3.45</v>
       </c>
       <c r="O25" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="P25" t="n">
-        <v>2.54</v>
+        <v>2.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.45</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>4.6</v>
+        <v>2.77</v>
       </c>
       <c r="T25" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="U25" t="n">
-        <v>1.89</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.02</v>
+        <v>1.33</v>
       </c>
       <c r="Z25" t="n">
-        <v>8</v>
+        <v>3.3</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.25</v>
+        <v>1.97</v>
       </c>
       <c r="AB25" t="n">
-        <v>3.5</v>
+        <v>1.83</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.82</v>
+        <v>3.34</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.88</v>
+        <v>1.27</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.24</v>
+        <v>1.67</v>
       </c>
       <c r="AF25" t="n">
-        <v>3.58</v>
+        <v>2.01</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46019.5625</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G31" t="n">

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.36</v>
+        <v>1.68</v>
       </c>
       <c r="M13" t="n">
-        <v>3.03</v>
+        <v>3.29</v>
       </c>
       <c r="N13" t="n">
-        <v>2.71</v>
+        <v>4.73</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O15" t="n">
+        <v>6</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S15" t="n">
         <v>2.65</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O15" t="n">
-        <v>3</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.6</v>
-      </c>
       <c r="T15" t="n">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="V15" t="n">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
         <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>2.43</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.44</v>
+        <v>1.12</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.6</v>
+        <v>4.05</v>
       </c>
       <c r="M16" t="n">
-        <v>3.77</v>
+        <v>3.35</v>
       </c>
       <c r="N16" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="O16" t="n">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.1</v>
+        <v>2.64</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
         <v>2.65</v>
       </c>
       <c r="T16" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="U16" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="AD16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.12</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.05</v>
+        <v>2.65</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>1.77</v>
+        <v>2.75</v>
       </c>
       <c r="O17" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.64</v>
+        <v>3.59</v>
       </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="T17" t="n">
-        <v>3.15</v>
+        <v>3.28</v>
       </c>
       <c r="U17" t="n">
         <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AB17" t="n">
         <v>1.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.82</v>
+        <v>4.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46019.45833333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G31" t="n">

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -778,19 +778,19 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="M3" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="N3" t="n">
-        <v>6.2</v>
+        <v>4.85</v>
       </c>
       <c r="O3" t="n">
         <v>2.25</v>
       </c>
       <c r="P3" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="Q3" t="n">
         <v>4.8</v>
@@ -799,7 +799,7 @@
         <v>1.33</v>
       </c>
       <c r="S3" t="n">
-        <v>3.02</v>
+        <v>3.18</v>
       </c>
       <c r="T3" t="n">
         <v>2.4</v>
@@ -823,10 +823,10 @@
         <v>3.54</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AC3" t="n">
         <v>3.02</v>
@@ -835,10 +835,10 @@
         <v>1.31</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AG3" t="n">
         <v>1.26</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.6</v>
+        <v>2.65</v>
       </c>
       <c r="M15" t="n">
-        <v>3.77</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>1.6</v>
+        <v>2.75</v>
       </c>
       <c r="O15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.1</v>
+        <v>3.59</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="T15" t="n">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="U15" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
         <v>1.06</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.43</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.12</v>
+        <v>1.44</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.05</v>
+        <v>5.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.35</v>
+        <v>3.77</v>
       </c>
       <c r="N16" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="O16" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="P16" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.64</v>
+        <v>2.1</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
         <v>2.65</v>
       </c>
       <c r="T16" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="U16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V16" t="n">
+        <v>8</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y16" t="n">
         <v>1.33</v>
       </c>
-      <c r="V16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.24</v>
-      </c>
       <c r="Z16" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.82</v>
+        <v>3.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.29</v>
+        <v>2.43</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S17" t="n">
         <v>2.65</v>
       </c>
-      <c r="M17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O17" t="n">
-        <v>3</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.6</v>
-      </c>
       <c r="T17" t="n">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="U17" t="n">
         <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.88</v>
+        <v>3.12</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="AB17" t="n">
         <v>1.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.2</v>
+        <v>3.82</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="M20" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="O20" t="n">
-        <v>3.66</v>
+        <v>4.25</v>
       </c>
       <c r="P20" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="S20" t="n">
-        <v>2.34</v>
+        <v>2.53</v>
       </c>
       <c r="T20" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="V20" t="n">
-        <v>9.9</v>
+        <v>8.1</v>
       </c>
       <c r="W20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X20" t="n">
         <v>1.03</v>
       </c>
-      <c r="X20" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y20" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.54</v>
+        <v>2.95</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.55</v>
+        <v>3.84</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE20" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46019.52083333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N21" t="n">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="O21" t="n">
-        <v>4.25</v>
+        <v>3.66</v>
       </c>
       <c r="P21" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V21" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE21" t="n">
         <v>2</v>
       </c>
-      <c r="Q21" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V21" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AF21" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46019.52083333334</v>

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -787,7 +787,7 @@
         <v>4.85</v>
       </c>
       <c r="O3" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="P3" t="n">
         <v>2.23</v>
@@ -799,7 +799,7 @@
         <v>1.33</v>
       </c>
       <c r="S3" t="n">
-        <v>3.18</v>
+        <v>3.02</v>
       </c>
       <c r="T3" t="n">
         <v>2.4</v>
@@ -814,7 +814,7 @@
         <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y3" t="n">
         <v>1.22</v>
@@ -823,7 +823,7 @@
         <v>3.54</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="AB3" t="n">
         <v>2</v>
@@ -832,7 +832,7 @@
         <v>3.02</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AE3" t="n">
         <v>1.88</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>6.5</v>
+        <v>1.32</v>
       </c>
       <c r="M5" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="N5" t="n">
-        <v>1.41</v>
+        <v>7.8</v>
       </c>
       <c r="O5" t="n">
-        <v>6</v>
+        <v>1.7</v>
       </c>
       <c r="P5" t="n">
-        <v>2.29</v>
+        <v>2.37</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.92</v>
+        <v>7.1</v>
       </c>
       <c r="R5" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S5" t="n">
-        <v>3.02</v>
+        <v>3.18</v>
       </c>
       <c r="T5" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="U5" t="n">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="V5" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X5" t="n">
         <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.21</v>
+        <v>4.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.59</v>
+        <v>2.42</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.16</v>
+        <v>1.12</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46019.3125</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.32</v>
+        <v>6.5</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="N6" t="n">
-        <v>7.8</v>
+        <v>1.41</v>
       </c>
       <c r="O6" t="n">
-        <v>1.7</v>
+        <v>6</v>
       </c>
       <c r="P6" t="n">
-        <v>2.37</v>
+        <v>2.29</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.1</v>
+        <v>1.92</v>
       </c>
       <c r="R6" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S6" t="n">
-        <v>3.18</v>
+        <v>3.02</v>
       </c>
       <c r="T6" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="U6" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="V6" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.5</v>
+        <v>4.21</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.42</v>
+        <v>2.59</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.12</v>
+        <v>2.16</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.94</v>
+        <v>1.04</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46019.3125</v>
@@ -1317,7 +1317,7 @@
         <v>1.94</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH7" t="n">
         <v>2</v>
@@ -1391,7 +1391,7 @@
         <v>7.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1427,7 +1427,7 @@
         <v>3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE8" t="n">
         <v>2.1</v>
@@ -1436,10 +1436,10 @@
         <v>1.67</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AH8" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46019.35416666666</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,16 +1656,16 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1900,10 +1900,10 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O15" t="n">
+        <v>6</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S15" t="n">
         <v>2.65</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O15" t="n">
-        <v>3</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.6</v>
-      </c>
       <c r="T15" t="n">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="V15" t="n">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
         <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>2.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.44</v>
+        <v>1.12</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.6</v>
+        <v>2.65</v>
       </c>
       <c r="M16" t="n">
-        <v>3.77</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>1.6</v>
+        <v>2.75</v>
       </c>
       <c r="O16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.1</v>
+        <v>3.59</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="T16" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="U16" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
         <v>1.06</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.43</v>
-      </c>
       <c r="AH16" t="n">
-        <v>1.12</v>
+        <v>1.44</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2471,7 +2471,7 @@
         <v>3.15</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V17" t="n">
         <v>7.8</v>
@@ -2480,7 +2480,7 @@
         <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
         <v>1.24</v>
@@ -2507,7 +2507,7 @@
         <v>1.9</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AH17" t="n">
         <v>1.25</v>
@@ -2617,13 +2617,13 @@
         <v>2.26</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="AE18" t="n">
         <v>1.51</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="AG18" t="n">
         <v>1.2</v>
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2733,10 +2733,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="O20" t="n">
-        <v>4.25</v>
+        <v>3.66</v>
       </c>
       <c r="P20" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V20" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE20" t="n">
         <v>2</v>
       </c>
-      <c r="Q20" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="V20" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AF20" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46019.52083333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="M21" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="O21" t="n">
-        <v>3.66</v>
+        <v>4.25</v>
       </c>
       <c r="P21" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="S21" t="n">
-        <v>2.34</v>
+        <v>2.71</v>
       </c>
       <c r="T21" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U21" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="V21" t="n">
-        <v>9.9</v>
+        <v>8.1</v>
       </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
         <v>1.08</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.54</v>
+        <v>2.95</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.55</v>
+        <v>3.84</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE21" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46019.52083333334</v>
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3334,10 +3334,10 @@
         <v>1.88</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF24" t="n">
-        <v>3.58</v>
+        <v>3.35</v>
       </c>
       <c r="AG24" t="n">
         <v>1.25</v>
@@ -3417,13 +3417,13 @@
         <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="T25" t="n">
         <v>2.75</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="V25" t="n">
         <v>6.5</v>
@@ -3551,7 +3551,7 @@
         <v>1.06</v>
       </c>
       <c r="X26" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y26" t="n">
         <v>1.34</v>
@@ -3643,19 +3643,19 @@
         <v>2.25</v>
       </c>
       <c r="O27" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="P27" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="R27" t="n">
         <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>2.85</v>
+        <v>2.92</v>
       </c>
       <c r="T27" t="n">
         <v>2.95</v>
@@ -3676,7 +3676,7 @@
         <v>1.29</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="AA27" t="n">
         <v>2.25</v>
@@ -3685,7 +3685,7 @@
         <v>1.55</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.54</v>
+        <v>3.85</v>
       </c>
       <c r="AD27" t="n">
         <v>1.25</v>
@@ -3762,7 +3762,7 @@
         <v>2.12</v>
       </c>
       <c r="O28" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="P28" t="n">
         <v>2.38</v>
@@ -3774,13 +3774,13 @@
         <v>1.37</v>
       </c>
       <c r="S28" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T28" t="n">
         <v>2.45</v>
       </c>
       <c r="U28" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="V28" t="n">
         <v>6.5</v>
@@ -3813,13 +3813,13 @@
         <v>1.62</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.83</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46019.69791666666</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4253,7 +4253,7 @@
         <v>3.85</v>
       </c>
       <c r="T32" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="U32" t="n">
         <v>1.73</v>
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -665,7 +665,7 @@
         <v>3.2</v>
       </c>
       <c r="N2" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
@@ -674,7 +674,7 @@
         <v>2.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="R2" t="n">
         <v>1.36</v>
@@ -683,7 +683,7 @@
         <v>2.73</v>
       </c>
       <c r="T2" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="U2" t="n">
         <v>1.35</v>
@@ -704,7 +704,7 @@
         <v>3.28</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AB2" t="n">
         <v>1.85</v>
@@ -713,7 +713,7 @@
         <v>3.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AE2" t="n">
         <v>1.68</v>
@@ -722,10 +722,10 @@
         <v>2.02</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46019.14583333334</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="M4" t="n">
         <v>3.64</v>
@@ -906,25 +906,25 @@
         <v>3.77</v>
       </c>
       <c r="O4" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="P4" t="n">
         <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.61</v>
+        <v>4.6</v>
       </c>
       <c r="R4" t="n">
         <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>2.73</v>
+        <v>2.99</v>
       </c>
       <c r="T4" t="n">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="V4" t="n">
         <v>7.4</v>
@@ -942,10 +942,10 @@
         <v>3.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AC4" t="n">
         <v>3.28</v>
@@ -954,16 +954,16 @@
         <v>1.31</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AF4" t="n">
         <v>1.91</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46019.22916666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.32</v>
+        <v>5.8</v>
       </c>
       <c r="M5" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="N5" t="n">
-        <v>7.8</v>
+        <v>1.41</v>
       </c>
       <c r="O5" t="n">
-        <v>1.7</v>
+        <v>6</v>
       </c>
       <c r="P5" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.1</v>
+        <v>1.92</v>
       </c>
       <c r="R5" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="S5" t="n">
-        <v>3.18</v>
+        <v>3.02</v>
       </c>
       <c r="T5" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="U5" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="V5" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="W5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
         <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.5</v>
+        <v>4.21</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.42</v>
+        <v>3.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AE5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF5" t="n">
         <v>1.86</v>
       </c>
-      <c r="AF5" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AG5" t="n">
-        <v>1.12</v>
+        <v>2.16</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.94</v>
+        <v>1.04</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46019.3125</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>6.5</v>
+        <v>1.32</v>
       </c>
       <c r="M6" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>1.41</v>
+        <v>8.5</v>
       </c>
       <c r="O6" t="n">
-        <v>6</v>
+        <v>1.7</v>
       </c>
       <c r="P6" t="n">
-        <v>2.29</v>
+        <v>2.37</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.92</v>
+        <v>7.2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>3.02</v>
+        <v>3.18</v>
       </c>
       <c r="T6" t="n">
-        <v>2.44</v>
+        <v>2.33</v>
       </c>
       <c r="U6" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="V6" t="n">
-        <v>5.75</v>
+        <v>5.3</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.21</v>
+        <v>4.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.59</v>
+        <v>2.42</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.16</v>
+        <v>1.12</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46019.3125</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="O7" t="n">
         <v>2.35</v>
@@ -1272,7 +1272,7 @@
         <v>4.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="S7" t="n">
         <v>2.73</v>
@@ -1284,7 +1284,7 @@
         <v>1.37</v>
       </c>
       <c r="V7" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="W7" t="n">
         <v>1.04</v>
@@ -1299,22 +1299,22 @@
         <v>3.43</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AC7" t="n">
         <v>3.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE7" t="n">
         <v>1.8</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AG7" t="n">
         <v>1.27</v>
@@ -1376,10 +1376,10 @@
         <v>1.36</v>
       </c>
       <c r="M8" t="n">
-        <v>4.7</v>
+        <v>4.78</v>
       </c>
       <c r="N8" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="O8" t="n">
         <v>1.85</v>
@@ -1391,13 +1391,13 @@
         <v>7.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="U8" t="n">
         <v>1.44</v>
@@ -1418,7 +1418,7 @@
         <v>3.68</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AB8" t="n">
         <v>1.95</v>
@@ -1436,10 +1436,10 @@
         <v>1.67</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46019.35416666666</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="M9" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O9" t="n">
         <v>2.75</v>
@@ -1534,7 +1534,7 @@
         <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AA9" t="n">
         <v>2.05</v>
@@ -1558,7 +1558,7 @@
         <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46019.375</v>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="M10" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="N10" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>14.4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AC10" t="n">
         <v>1.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46019.38541666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1781,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>9.5</v>
+        <v>1.28</v>
       </c>
       <c r="M12" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="N12" t="n">
-        <v>1.18</v>
+        <v>6.7</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1900,10 +1900,10 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="M14" t="n">
         <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O14" t="n">
         <v>2.8</v>
@@ -2102,22 +2102,22 @@
         <v>2.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.8</v>
+        <v>3.87</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="T14" t="n">
         <v>2.96</v>
       </c>
       <c r="U14" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="V14" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="W14" t="n">
         <v>1.02</v>
@@ -2132,10 +2132,10 @@
         <v>3.04</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
         <v>3.58</v>
@@ -2153,7 +2153,7 @@
         <v>1.27</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46019.41666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.77</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.1</v>
+        <v>2.64</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="T15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z15" t="n">
         <v>3.12</v>
       </c>
-      <c r="U15" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V15" t="n">
-        <v>8</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AA15" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.65</v>
+        <v>7</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>1.57</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.59</v>
+        <v>2.1</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="T16" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="V16" t="n">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
         <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>2.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>1.12</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.05</v>
+        <v>2.67</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>1.77</v>
+        <v>2.75</v>
       </c>
       <c r="O17" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.64</v>
+        <v>3.57</v>
       </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="S17" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="T17" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="U17" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="V17" t="n">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.12</v>
+        <v>2.88</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="M18" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="N18" t="n">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="O18" t="n">
         <v>4</v>
@@ -2605,25 +2605,25 @@
         <v>1.14</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.45</v>
+        <v>4.94</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AC18" t="n">
         <v>2.26</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="AE18" t="n">
         <v>1.51</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="AG18" t="n">
         <v>1.2</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="M20" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
-        <v>3.66</v>
+        <v>4.25</v>
       </c>
       <c r="P20" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="S20" t="n">
-        <v>2.34</v>
+        <v>2.53</v>
       </c>
       <c r="T20" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="V20" t="n">
-        <v>9.9</v>
+        <v>8.1</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
         <v>1.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.54</v>
+        <v>2.99</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.35</v>
+        <v>2.26</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.55</v>
+        <v>3.84</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AE20" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46019.52083333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.95</v>
+        <v>3.32</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="N21" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="O21" t="n">
-        <v>4.25</v>
+        <v>3.66</v>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="S21" t="n">
-        <v>2.71</v>
+        <v>2.34</v>
       </c>
       <c r="T21" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U21" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="V21" t="n">
-        <v>8.1</v>
+        <v>9.9</v>
       </c>
       <c r="W21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X21" t="n">
         <v>1.08</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.95</v>
+        <v>2.54</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.84</v>
+        <v>4.55</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46019.52083333334</v>
@@ -3167,40 +3167,40 @@
         <v>3.3</v>
       </c>
       <c r="O23" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="P23" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="R23" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
         <v>2.85</v>
       </c>
       <c r="T23" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="U23" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="V23" t="n">
-        <v>6.35</v>
+        <v>6.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.8</v>
+        <v>3.72</v>
       </c>
       <c r="AA23" t="n">
         <v>1.75</v>
@@ -3212,19 +3212,19 @@
         <v>3.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AF23" t="n">
         <v>2.07</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46019.54166666666</v>
@@ -3277,16 +3277,16 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="M24" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="N24" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P24" t="n">
         <v>2.54</v>
@@ -3295,22 +3295,22 @@
         <v>2.45</v>
       </c>
       <c r="R24" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S24" t="n">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="T24" t="n">
         <v>1.75</v>
       </c>
       <c r="U24" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V24" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="W24" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
@@ -3319,31 +3319,31 @@
         <v>1.02</v>
       </c>
       <c r="Z24" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AB24" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.82</v>
+        <v>1.66</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF24" t="n">
-        <v>3.35</v>
+        <v>3.58</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46019.5625</v>
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="M25" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N25" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="O25" t="n">
         <v>2.85</v>
@@ -3414,22 +3414,22 @@
         <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="T25" t="n">
         <v>2.75</v>
       </c>
       <c r="U25" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
         <v>6.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X25" t="n">
         <v>1</v>
@@ -3441,10 +3441,10 @@
         <v>3.3</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AC25" t="n">
         <v>3.34</v>
@@ -3453,10 +3453,10 @@
         <v>1.27</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AG25" t="n">
         <v>1.35</v>
@@ -3515,16 +3515,16 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="M26" t="n">
-        <v>3.47</v>
+        <v>3.68</v>
       </c>
       <c r="N26" t="n">
-        <v>4.7</v>
+        <v>4.96</v>
       </c>
       <c r="O26" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="P26" t="n">
         <v>2</v>
@@ -3533,7 +3533,7 @@
         <v>4.6</v>
       </c>
       <c r="R26" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S26" t="n">
         <v>2.75</v>
@@ -3557,22 +3557,22 @@
         <v>1.34</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AF26" t="n">
         <v>1.85</v>
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="M27" t="n">
-        <v>3.15</v>
+        <v>3.32</v>
       </c>
       <c r="N27" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="O27" t="n">
         <v>3.85</v>
@@ -3664,13 +3664,13 @@
         <v>1.33</v>
       </c>
       <c r="V27" t="n">
-        <v>7</v>
+        <v>7.9</v>
       </c>
       <c r="W27" t="n">
         <v>1.07</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y27" t="n">
         <v>1.29</v>
@@ -3679,10 +3679,10 @@
         <v>3.05</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AC27" t="n">
         <v>3.85</v>
@@ -3691,7 +3691,7 @@
         <v>1.25</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AF27" t="n">
         <v>2</v>
@@ -3753,28 +3753,28 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.23</v>
+        <v>3.45</v>
       </c>
       <c r="M28" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="N28" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="O28" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="P28" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="Q28" t="n">
         <v>2.68</v>
       </c>
       <c r="R28" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T28" t="n">
         <v>2.45</v>
@@ -3783,7 +3783,7 @@
         <v>1.47</v>
       </c>
       <c r="V28" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="W28" t="n">
         <v>1.09</v>
@@ -3798,10 +3798,10 @@
         <v>3.9</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AC28" t="n">
         <v>2.8</v>
@@ -3813,10 +3813,10 @@
         <v>1.62</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH28" t="n">
         <v>1.3</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="M32" t="n">
-        <v>7.3</v>
+        <v>7.25</v>
       </c>
       <c r="N32" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="O32" t="n">
         <v>1.48</v>
@@ -4250,13 +4250,13 @@
         <v>1.2</v>
       </c>
       <c r="S32" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="T32" t="n">
         <v>2.05</v>
       </c>
       <c r="U32" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="V32" t="n">
         <v>4.15</v>
@@ -4274,16 +4274,16 @@
         <v>5.2</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.55</v>
+        <v>3.03</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="AE32" t="n">
         <v>2.21</v>
@@ -4295,7 +4295,7 @@
         <v>1.08</v>
       </c>
       <c r="AH32" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46019.72916666666</v>
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="M34" t="n">
         <v>3.75</v>
       </c>
       <c r="N34" t="n">
-        <v>4</v>
+        <v>4.08</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="N3" t="n">
-        <v>4.85</v>
+        <v>6.2</v>
       </c>
       <c r="O3" t="n">
         <v>2.12</v>
@@ -823,10 +823,10 @@
         <v>3.54</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.86</v>
+        <v>1.58</v>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AC3" t="n">
         <v>3.02</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="O7" t="n">
         <v>2.35</v>
@@ -1299,10 +1299,10 @@
         <v>3.43</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
         <v>3.1</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>9.5</v>
+        <v>1.28</v>
       </c>
       <c r="M11" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="N11" t="n">
-        <v>1.18</v>
+        <v>6.7</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1781,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.28</v>
+        <v>9.5</v>
       </c>
       <c r="M12" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="N12" t="n">
-        <v>6.7</v>
+        <v>1.18</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1900,10 +1900,10 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.68</v>
+        <v>2.29</v>
       </c>
       <c r="M13" t="n">
-        <v>3.29</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>4.73</v>
+        <v>3.15</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>2.03</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46019.41666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="N14" t="n">
-        <v>3.15</v>
+        <v>2.71</v>
       </c>
       <c r="O14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.03</v>
+        <v>2.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46019.41666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.4</v>
+        <v>7</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="N15" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="O15" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="P15" t="n">
         <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.64</v>
+        <v>2.1</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="T15" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="U15" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="V15" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.82</v>
+        <v>3.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>7</v>
+        <v>2.67</v>
       </c>
       <c r="M16" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>1.57</v>
+        <v>2.75</v>
       </c>
       <c r="O16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.1</v>
+        <v>3.57</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="S16" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="T16" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="U16" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X16" t="n">
         <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.5</v>
+        <v>3.84</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.12</v>
+        <v>1.44</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.67</v>
+        <v>4.05</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>2.75</v>
+        <v>1.77</v>
       </c>
       <c r="O17" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.57</v>
+        <v>2.64</v>
       </c>
       <c r="R17" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="S17" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="T17" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="U17" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="V17" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.88</v>
+        <v>3.12</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.84</v>
+        <v>3.82</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.5</v>
+        <v>1.26</v>
       </c>
       <c r="M18" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="N18" t="n">
-        <v>1.79</v>
+        <v>6.8</v>
       </c>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.26</v>
+        <v>1.93</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.51</v>
+        <v>1.77</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46019.47916666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.26</v>
+        <v>3.5</v>
       </c>
       <c r="M19" t="n">
-        <v>5.1</v>
+        <v>3.7</v>
       </c>
       <c r="N19" t="n">
-        <v>6.8</v>
+        <v>1.79</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.93</v>
+        <v>2.26</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.77</v>
+        <v>1.51</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46019.47916666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.8</v>
+        <v>3.32</v>
       </c>
       <c r="M20" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T20" t="n">
         <v>3.4</v>
       </c>
-      <c r="N20" t="n">
-        <v>2</v>
-      </c>
-      <c r="O20" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.3</v>
-      </c>
       <c r="U20" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="V20" t="n">
-        <v>8.1</v>
+        <v>9.9</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
         <v>1.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.99</v>
+        <v>2.54</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.84</v>
+        <v>4.55</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46019.52083333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.32</v>
+        <v>3.8</v>
       </c>
       <c r="M21" t="n">
-        <v>3.04</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="O21" t="n">
-        <v>3.66</v>
+        <v>4.25</v>
       </c>
       <c r="P21" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="R21" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="S21" t="n">
-        <v>2.34</v>
+        <v>2.53</v>
       </c>
       <c r="T21" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U21" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="V21" t="n">
-        <v>9.9</v>
+        <v>8.1</v>
       </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
         <v>1.08</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.54</v>
+        <v>2.99</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.55</v>
+        <v>3.84</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AE21" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46019.52083333334</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.9</v>
+        <v>2.31</v>
       </c>
       <c r="M24" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O24" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V24" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA24" t="n">
         <v>2</v>
       </c>
-      <c r="O24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S24" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V24" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AB24" t="n">
-        <v>3.48</v>
+        <v>1.89</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.66</v>
+        <v>3.34</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.1</v>
+        <v>1.27</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.24</v>
+        <v>1.73</v>
       </c>
       <c r="AF24" t="n">
-        <v>3.58</v>
+        <v>2</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46019.5625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.31</v>
+        <v>2.9</v>
       </c>
       <c r="M25" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="N25" t="n">
+        <v>2</v>
+      </c>
+      <c r="O25" t="n">
         <v>3.2</v>
       </c>
-      <c r="O25" t="n">
-        <v>2.85</v>
-      </c>
       <c r="P25" t="n">
-        <v>2.05</v>
+        <v>2.54</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>2.45</v>
       </c>
       <c r="R25" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="S25" t="n">
-        <v>2.77</v>
+        <v>4.65</v>
       </c>
       <c r="T25" t="n">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="V25" t="n">
-        <v>6.5</v>
+        <v>3.42</v>
       </c>
       <c r="W25" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA25" t="n">
-        <v>2</v>
+        <v>1.28</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.89</v>
+        <v>3.48</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.34</v>
+        <v>1.66</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.27</v>
+        <v>2.1</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.73</v>
+        <v>1.24</v>
       </c>
       <c r="AF25" t="n">
-        <v>2</v>
+        <v>3.58</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.65</v>
+        <v>1.38</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46019.5625</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="M34" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="N34" t="n">
-        <v>4.08</v>
+        <v>4.2</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="M3" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="N3" t="n">
-        <v>6.2</v>
+        <v>4.85</v>
       </c>
       <c r="O3" t="n">
         <v>2.12</v>
@@ -802,7 +802,7 @@
         <v>3.02</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="U3" t="n">
         <v>1.42</v>
@@ -823,10 +823,10 @@
         <v>3.54</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.58</v>
+        <v>1.87</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AC3" t="n">
         <v>3.02</v>
@@ -835,10 +835,10 @@
         <v>1.38</v>
       </c>
       <c r="AE3" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AF3" t="n">
         <v>1.88</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.92</v>
       </c>
       <c r="AG3" t="n">
         <v>1.26</v>
@@ -1376,28 +1376,28 @@
         <v>1.36</v>
       </c>
       <c r="M8" t="n">
-        <v>4.78</v>
+        <v>4.7</v>
       </c>
       <c r="N8" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="O8" t="n">
         <v>1.85</v>
       </c>
       <c r="P8" t="n">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="Q8" t="n">
         <v>7.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="U8" t="n">
         <v>1.44</v>
@@ -1418,7 +1418,7 @@
         <v>3.68</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AB8" t="n">
         <v>1.95</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="M10" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="N10" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="O10" t="n">
         <v>1.43</v>
@@ -1629,16 +1629,16 @@
         <v>14.4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S10" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="T10" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U10" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V10" t="n">
         <v>3.3</v>
@@ -1656,16 +1656,16 @@
         <v>6.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="AC10" t="n">
         <v>1.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AE10" t="n">
         <v>2.15</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.28</v>
+        <v>9.5</v>
       </c>
       <c r="M11" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="N11" t="n">
-        <v>6.7</v>
+        <v>1.18</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1781,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>9.5</v>
+        <v>1.28</v>
       </c>
       <c r="M12" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="N12" t="n">
-        <v>1.18</v>
+        <v>6.7</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1900,10 +1900,10 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="N13" t="n">
-        <v>3.15</v>
+        <v>2.71</v>
       </c>
       <c r="O13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.03</v>
+        <v>2.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46019.41666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="M14" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.71</v>
+        <v>3.15</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.4</v>
+        <v>2.03</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46019.41666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>7</v>
+        <v>2.65</v>
       </c>
       <c r="M15" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>1.57</v>
+        <v>2.75</v>
       </c>
       <c r="O15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.1</v>
+        <v>3.53</v>
       </c>
       <c r="R15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V15" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1.44</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V15" t="n">
-        <v>8</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.12</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.67</v>
+        <v>5.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>3.77</v>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>1.6</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.57</v>
+        <v>2.1</v>
       </c>
       <c r="R16" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="S16" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="T16" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="U16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="V16" t="n">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
         <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.84</v>
+        <v>3.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>1.12</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.26</v>
+        <v>3.2</v>
       </c>
       <c r="M18" t="n">
-        <v>5.1</v>
+        <v>3.55</v>
       </c>
       <c r="N18" t="n">
-        <v>6.8</v>
+        <v>1.93</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.93</v>
+        <v>2.26</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46019.47916666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.5</v>
+        <v>1.26</v>
       </c>
       <c r="M19" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="N19" t="n">
-        <v>1.79</v>
+        <v>6.8</v>
       </c>
       <c r="O19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.26</v>
+        <v>1.93</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.51</v>
+        <v>1.77</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46019.47916666666</v>
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.32</v>
+        <v>3.1</v>
       </c>
       <c r="M20" t="n">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O20" t="n">
         <v>3.66</v>
@@ -2846,13 +2846,13 @@
         <v>2.54</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="AD20" t="n">
         <v>1.13</v>
@@ -2861,13 +2861,13 @@
         <v>2</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46019.52083333334</v>
@@ -2920,28 +2920,28 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="O21" t="n">
-        <v>4.25</v>
+        <v>4.35</v>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="R21" t="n">
         <v>1.46</v>
       </c>
       <c r="S21" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="T21" t="n">
         <v>3.3</v>
@@ -2950,7 +2950,7 @@
         <v>1.31</v>
       </c>
       <c r="V21" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W21" t="n">
         <v>1.02</v>
@@ -2959,22 +2959,22 @@
         <v>1.08</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.84</v>
+        <v>3.86</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE21" t="n">
         <v>1.93</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.31</v>
+        <v>3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="N24" t="n">
-        <v>3.2</v>
+        <v>1.92</v>
       </c>
       <c r="O24" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="P24" t="n">
-        <v>2.05</v>
+        <v>2.54</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>2.45</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="S24" t="n">
-        <v>2.77</v>
+        <v>4.6</v>
       </c>
       <c r="T24" t="n">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4</v>
+        <v>1.89</v>
       </c>
       <c r="V24" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.3</v>
+        <v>8</v>
       </c>
       <c r="AA24" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.89</v>
+        <v>3.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.34</v>
+        <v>1.82</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.27</v>
+        <v>1.88</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AF24" t="n">
-        <v>2</v>
+        <v>3.51</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.65</v>
+        <v>1.31</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46019.5625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="M25" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF25" t="n">
         <v>2</v>
       </c>
-      <c r="O25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S25" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V25" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>3.58</v>
-      </c>
       <c r="AG25" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46019.5625</v>
@@ -3515,16 +3515,16 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="M26" t="n">
-        <v>3.68</v>
+        <v>3.47</v>
       </c>
       <c r="N26" t="n">
-        <v>4.96</v>
+        <v>4.7</v>
       </c>
       <c r="O26" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="P26" t="n">
         <v>2</v>
@@ -3533,13 +3533,13 @@
         <v>4.6</v>
       </c>
       <c r="R26" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
         <v>2.75</v>
       </c>
       <c r="T26" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="U26" t="n">
         <v>1.39</v>
@@ -3554,16 +3554,16 @@
         <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z26" t="n">
         <v>3.25</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="AC26" t="n">
         <v>3.65</v>
@@ -3634,28 +3634,28 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="M27" t="n">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="N27" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="O27" t="n">
-        <v>3.85</v>
+        <v>3.74</v>
       </c>
       <c r="P27" t="n">
         <v>1.99</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.78</v>
+        <v>2.59</v>
       </c>
       <c r="R27" t="n">
         <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="T27" t="n">
         <v>2.95</v>
@@ -3664,25 +3664,25 @@
         <v>1.33</v>
       </c>
       <c r="V27" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="W27" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X27" t="n">
         <v>1.06</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AC27" t="n">
         <v>3.85</v>
@@ -3691,7 +3691,7 @@
         <v>1.25</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AF27" t="n">
         <v>2</v>
@@ -3700,7 +3700,7 @@
         <v>1.28</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46019.625</v>
@@ -3753,25 +3753,25 @@
         </is>
       </c>
       <c r="L28" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="M28" t="n">
         <v>3.45</v>
       </c>
-      <c r="M28" t="n">
-        <v>3.65</v>
-      </c>
       <c r="N28" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="O28" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P28" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q28" t="n">
         <v>2.68</v>
       </c>
       <c r="R28" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="S28" t="n">
         <v>3.05</v>
@@ -3780,10 +3780,10 @@
         <v>2.45</v>
       </c>
       <c r="U28" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="V28" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="W28" t="n">
         <v>1.09</v>
@@ -3798,10 +3798,10 @@
         <v>3.9</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AB28" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AC28" t="n">
         <v>2.8</v>
@@ -3816,10 +3816,10 @@
         <v>2.2</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46019.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4229,37 +4229,37 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="M32" t="n">
-        <v>7.25</v>
+        <v>7.3</v>
       </c>
       <c r="N32" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="O32" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="P32" t="n">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="Q32" t="n">
-        <v>10</v>
+        <v>10.7</v>
       </c>
       <c r="R32" t="n">
         <v>1.2</v>
       </c>
       <c r="S32" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T32" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="U32" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="V32" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="W32" t="n">
         <v>1.18</v>
@@ -4268,25 +4268,25 @@
         <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z32" t="n">
         <v>5.2</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AB32" t="n">
-        <v>3.03</v>
+        <v>2.55</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.84</v>
+        <v>1.65</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="AF32" t="n">
         <v>1.63</v>
@@ -4295,7 +4295,7 @@
         <v>1.08</v>
       </c>
       <c r="AH32" t="n">
-        <v>5.95</v>
+        <v>6.1</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46019.72916666666</v>

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5.8</v>
+        <v>1.32</v>
       </c>
       <c r="M5" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="N5" t="n">
-        <v>1.41</v>
+        <v>8.5</v>
       </c>
       <c r="O5" t="n">
-        <v>6</v>
+        <v>1.7</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.92</v>
+        <v>7.2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>3.02</v>
+        <v>3.18</v>
       </c>
       <c r="T5" t="n">
-        <v>2.44</v>
+        <v>2.33</v>
       </c>
       <c r="U5" t="n">
         <v>1.5</v>
       </c>
       <c r="V5" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X5" t="n">
         <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.21</v>
+        <v>4.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.1</v>
+        <v>2.42</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AE5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF5" t="n">
         <v>1.83</v>
       </c>
-      <c r="AF5" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AG5" t="n">
-        <v>2.16</v>
+        <v>1.12</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46019.3125</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.32</v>
+        <v>5.8</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="N6" t="n">
-        <v>8.5</v>
+        <v>1.41</v>
       </c>
       <c r="O6" t="n">
-        <v>1.7</v>
+        <v>6</v>
       </c>
       <c r="P6" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.2</v>
+        <v>1.92</v>
       </c>
       <c r="R6" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="S6" t="n">
-        <v>3.18</v>
+        <v>3.02</v>
       </c>
       <c r="T6" t="n">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="U6" t="n">
         <v>1.5</v>
       </c>
       <c r="V6" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.5</v>
+        <v>4.21</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.42</v>
+        <v>3.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AE6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF6" t="n">
         <v>1.86</v>
       </c>
-      <c r="AF6" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AG6" t="n">
-        <v>1.12</v>
+        <v>2.16</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.94</v>
+        <v>1.04</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46019.3125</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="M13" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>2.71</v>
+        <v>3.15</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>2.03</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46019.41666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="N14" t="n">
-        <v>3.15</v>
+        <v>2.71</v>
       </c>
       <c r="O14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.03</v>
+        <v>2.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46019.41666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.65</v>
+        <v>4.05</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>2.75</v>
+        <v>1.77</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.53</v>
+        <v>2.64</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="T15" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="V15" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="AB15" t="n">
         <v>1.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.95</v>
+        <v>3.82</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.48</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.6</v>
+        <v>2.65</v>
       </c>
       <c r="M16" t="n">
-        <v>3.77</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>1.6</v>
+        <v>2.75</v>
       </c>
       <c r="O16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V16" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA16" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V16" t="n">
-        <v>8</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.3</v>
+        <v>1.48</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.12</v>
+        <v>1.44</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.05</v>
+        <v>5.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>3.77</v>
       </c>
       <c r="N17" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="O17" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="P17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V17" t="n">
+        <v>8</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA17" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q17" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.03</v>
-      </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.82</v>
+        <v>3.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.2</v>
+        <v>1.26</v>
       </c>
       <c r="M18" t="n">
-        <v>3.55</v>
+        <v>5.1</v>
       </c>
       <c r="N18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
         <v>1.93</v>
       </c>
-      <c r="O18" t="n">
-        <v>4</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.26</v>
-      </c>
       <c r="AD18" t="n">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46019.47916666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.26</v>
+        <v>3.2</v>
       </c>
       <c r="M19" t="n">
-        <v>5.1</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>6.8</v>
+        <v>1.93</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.93</v>
+        <v>2.26</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46019.47916666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="M20" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="O20" t="n">
-        <v>3.66</v>
+        <v>4.35</v>
       </c>
       <c r="P20" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>2.59</v>
       </c>
       <c r="R20" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="S20" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="T20" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="V20" t="n">
-        <v>9.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
         <v>1.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.54</v>
+        <v>2.88</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.6</v>
+        <v>3.86</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AE20" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46019.52083333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N21" t="n">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="O21" t="n">
-        <v>4.35</v>
+        <v>3.66</v>
       </c>
       <c r="P21" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.59</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="S21" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="T21" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U21" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="V21" t="n">
-        <v>8.199999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="W21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X21" t="n">
         <v>1.08</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.88</v>
+        <v>2.54</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AB21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.62</v>
       </c>
-      <c r="AC21" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46019.52083333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G30" t="n">

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="M2" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="N2" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
@@ -704,7 +704,7 @@
         <v>3.28</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AB2" t="n">
         <v>1.85</v>
@@ -713,7 +713,7 @@
         <v>3.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AE2" t="n">
         <v>1.68</v>
@@ -722,10 +722,10 @@
         <v>2.02</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46019.14583333334</v>
@@ -778,25 +778,25 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="N3" t="n">
-        <v>4.85</v>
+        <v>6.2</v>
       </c>
       <c r="O3" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="P3" t="n">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="Q3" t="n">
         <v>4.8</v>
       </c>
       <c r="R3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S3" t="n">
         <v>3.02</v>
@@ -817,22 +817,22 @@
         <v>1.05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z3" t="n">
         <v>3.54</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.87</v>
+        <v>1.58</v>
       </c>
       <c r="AB3" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AC3" t="n">
         <v>3.02</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE3" t="n">
         <v>1.82</v>
@@ -841,7 +841,7 @@
         <v>1.88</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AH3" t="n">
         <v>2.33</v>
@@ -897,34 +897,34 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="M4" t="n">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="N4" t="n">
-        <v>3.77</v>
+        <v>3.7</v>
       </c>
       <c r="O4" t="n">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="P4" t="n">
         <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.6</v>
+        <v>4.44</v>
       </c>
       <c r="R4" t="n">
         <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>2.99</v>
+        <v>2.75</v>
       </c>
       <c r="T4" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="U4" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="V4" t="n">
         <v>7.4</v>
@@ -933,13 +933,13 @@
         <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="AA4" t="n">
         <v>1.91</v>
@@ -948,22 +948,22 @@
         <v>1.78</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AF4" t="n">
         <v>1.91</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46019.22916666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="O5" t="n">
+        <v>5</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R5" t="n">
         <v>1.32</v>
       </c>
-      <c r="M5" t="n">
-        <v>5</v>
-      </c>
-      <c r="N5" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.28</v>
-      </c>
       <c r="S5" t="n">
-        <v>3.18</v>
+        <v>2.96</v>
       </c>
       <c r="T5" t="n">
-        <v>2.33</v>
+        <v>2.48</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V5" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.19</v>
+        <v>1.86</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.42</v>
+        <v>3.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.94</v>
+        <v>1.07</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46019.3125</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5.8</v>
+        <v>1.34</v>
       </c>
       <c r="M6" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>1.41</v>
+        <v>8</v>
       </c>
       <c r="O6" t="n">
-        <v>6</v>
+        <v>1.7</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.92</v>
+        <v>7</v>
       </c>
       <c r="R6" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>3.02</v>
+        <v>3.18</v>
       </c>
       <c r="T6" t="n">
-        <v>2.44</v>
+        <v>2.33</v>
       </c>
       <c r="U6" t="n">
         <v>1.5</v>
       </c>
       <c r="V6" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.21</v>
+        <v>4.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.1</v>
+        <v>2.42</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AE6" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF6" t="n">
         <v>1.83</v>
       </c>
-      <c r="AF6" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AG6" t="n">
-        <v>2.16</v>
+        <v>1.12</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46019.3125</v>
@@ -1263,7 +1263,7 @@
         <v>4.3</v>
       </c>
       <c r="O7" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="P7" t="n">
         <v>2.08</v>
@@ -1296,7 +1296,7 @@
         <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.43</v>
+        <v>3.2</v>
       </c>
       <c r="AA7" t="n">
         <v>1.9</v>
@@ -1308,7 +1308,7 @@
         <v>3.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE7" t="n">
         <v>1.8</v>
@@ -1317,10 +1317,10 @@
         <v>1.88</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH7" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46019.33333333334</v>
@@ -1400,7 +1400,7 @@
         <v>2.76</v>
       </c>
       <c r="U8" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="V8" t="n">
         <v>6.25</v>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N9" t="n">
         <v>3.35</v>
@@ -1534,10 +1534,10 @@
         <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB9" t="n">
         <v>1.71</v>
@@ -1549,16 +1549,16 @@
         <v>1.25</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AG9" t="n">
         <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46019.375</v>
@@ -1623,22 +1623,22 @@
         <v>1.43</v>
       </c>
       <c r="P10" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="Q10" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="S10" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="T10" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="U10" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="V10" t="n">
         <v>3.3</v>
@@ -1650,16 +1650,16 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="AA10" t="n">
         <v>1.28</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="AC10" t="n">
         <v>1.7</v>
@@ -1668,16 +1668,16 @@
         <v>2.02</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AG10" t="n">
         <v>1.02</v>
       </c>
       <c r="AH10" t="n">
-        <v>5.6</v>
+        <v>5.65</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46019.38541666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>9.5</v>
+        <v>1.28</v>
       </c>
       <c r="M11" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="N11" t="n">
-        <v>1.18</v>
+        <v>6.7</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1781,10 +1781,10 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.29</v>
+        <v>2.17</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.28</v>
+        <v>9.5</v>
       </c>
       <c r="M12" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="N12" t="n">
-        <v>6.7</v>
+        <v>1.18</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1900,10 +1900,10 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1968,7 +1968,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.29</v>
+        <v>2.09</v>
       </c>
       <c r="M13" t="n">
         <v>3</v>
@@ -1977,7 +1977,7 @@
         <v>3.15</v>
       </c>
       <c r="O13" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="P13" t="n">
         <v>2.15</v>
@@ -1989,13 +1989,13 @@
         <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>2.59</v>
+        <v>2.82</v>
       </c>
       <c r="T13" t="n">
         <v>2.96</v>
       </c>
       <c r="U13" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="V13" t="n">
         <v>8.1</v>
@@ -2007,7 +2007,7 @@
         <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
         <v>3.04</v>
@@ -2230,10 +2230,10 @@
         <v>2.66</v>
       </c>
       <c r="T15" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="U15" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="V15" t="n">
         <v>7.8</v>
@@ -2257,10 +2257,10 @@
         <v>1.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AE15" t="n">
         <v>1.8</v>
@@ -2269,10 +2269,10 @@
         <v>1.9</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2340,13 +2340,13 @@
         <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.53</v>
+        <v>3.54</v>
       </c>
       <c r="R16" t="n">
         <v>1.5</v>
       </c>
       <c r="S16" t="n">
-        <v>2.75</v>
+        <v>2.57</v>
       </c>
       <c r="T16" t="n">
         <v>3.1</v>
@@ -2388,7 +2388,7 @@
         <v>1.91</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
         <v>1.44</v>
@@ -2462,7 +2462,7 @@
         <v>2.1</v>
       </c>
       <c r="R17" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
         <v>2.72</v>
@@ -2474,7 +2474,7 @@
         <v>1.37</v>
       </c>
       <c r="V17" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="W17" t="n">
         <v>1.06</v>
@@ -2486,7 +2486,7 @@
         <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.2</v>
+        <v>3.33</v>
       </c>
       <c r="AA17" t="n">
         <v>2.05</v>
@@ -2724,7 +2724,7 @@
         <v>1.14</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.94</v>
+        <v>4.45</v>
       </c>
       <c r="AA19" t="n">
         <v>1.57</v>
@@ -2736,13 +2736,13 @@
         <v>2.26</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="AG19" t="n">
         <v>1.2</v>
@@ -2813,16 +2813,16 @@
         <v>4.35</v>
       </c>
       <c r="P20" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="R20" t="n">
         <v>1.46</v>
       </c>
       <c r="S20" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="T20" t="n">
         <v>3.3</v>
@@ -2831,7 +2831,7 @@
         <v>1.31</v>
       </c>
       <c r="V20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="W20" t="n">
         <v>1.02</v>
@@ -2840,10 +2840,10 @@
         <v>1.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="AA20" t="n">
         <v>2.15</v>
@@ -2852,7 +2852,7 @@
         <v>1.62</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
       <c r="AD20" t="n">
         <v>1.22</v>
@@ -2867,7 +2867,7 @@
         <v>1.82</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46019.52083333334</v>
@@ -2932,7 +2932,7 @@
         <v>3.66</v>
       </c>
       <c r="P21" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="Q21" t="n">
         <v>3</v>
@@ -2944,7 +2944,7 @@
         <v>2.34</v>
       </c>
       <c r="T21" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="U21" t="n">
         <v>1.26</v>
@@ -2962,7 +2962,7 @@
         <v>1.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="AA21" t="n">
         <v>2.35</v>
@@ -2980,13 +2980,13 @@
         <v>2</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46019.52083333334</v>
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N23" t="n">
         <v>3.3</v>
       </c>
       <c r="O23" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="P23" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S23" t="n">
         <v>2.85</v>
       </c>
       <c r="T23" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="U23" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="V23" t="n">
-        <v>6.5</v>
+        <v>6.35</v>
       </c>
       <c r="W23" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="AA23" t="n">
         <v>1.75</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="AC23" t="n">
         <v>3.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.07</v>
+        <v>2.14</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46019.54166666666</v>
@@ -3292,7 +3292,7 @@
         <v>2.54</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="R24" t="n">
         <v>1.13</v>
@@ -3322,10 +3322,10 @@
         <v>8</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AB24" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="AC24" t="n">
         <v>1.82</v>
@@ -3340,10 +3340,10 @@
         <v>3.51</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46019.5625</v>
@@ -3423,10 +3423,10 @@
         <v>2.75</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="V25" t="n">
-        <v>6.5</v>
+        <v>7.8</v>
       </c>
       <c r="W25" t="n">
         <v>1.08</v>
@@ -3453,10 +3453,10 @@
         <v>1.27</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AF25" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AG25" t="n">
         <v>1.33</v>
@@ -3533,7 +3533,7 @@
         <v>4.6</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S26" t="n">
         <v>2.75</v>
@@ -3542,10 +3542,10 @@
         <v>2.8</v>
       </c>
       <c r="U26" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="V26" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="W26" t="n">
         <v>1.06</v>
@@ -3557,7 +3557,7 @@
         <v>1.35</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="AA26" t="n">
         <v>1.98</v>
@@ -3569,13 +3569,13 @@
         <v>3.65</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE26" t="n">
         <v>1.85</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG26" t="n">
         <v>1.29</v>
@@ -3643,22 +3643,22 @@
         <v>2.25</v>
       </c>
       <c r="O27" t="n">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="P27" t="n">
         <v>1.99</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.59</v>
+        <v>2.79</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="S27" t="n">
         <v>2.62</v>
       </c>
       <c r="T27" t="n">
-        <v>2.95</v>
+        <v>3.04</v>
       </c>
       <c r="U27" t="n">
         <v>1.33</v>
@@ -3670,13 +3670,13 @@
         <v>1.02</v>
       </c>
       <c r="X27" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
         <v>1.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="AA27" t="n">
         <v>2.25</v>
@@ -3774,16 +3774,16 @@
         <v>1.37</v>
       </c>
       <c r="S28" t="n">
-        <v>3.05</v>
+        <v>3.32</v>
       </c>
       <c r="T28" t="n">
         <v>2.45</v>
       </c>
       <c r="U28" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="V28" t="n">
-        <v>6.5</v>
+        <v>6.55</v>
       </c>
       <c r="W28" t="n">
         <v>1.09</v>
@@ -3819,7 +3819,7 @@
         <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46019.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4268,16 +4268,16 @@
         <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z32" t="n">
         <v>5.2</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.55</v>
+        <v>2.94</v>
       </c>
       <c r="AC32" t="n">
         <v>2.08</v>
@@ -4286,7 +4286,7 @@
         <v>1.65</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AF32" t="n">
         <v>1.63</v>
@@ -4295,7 +4295,7 @@
         <v>1.08</v>
       </c>
       <c r="AH32" t="n">
-        <v>6.1</v>
+        <v>6.15</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46019.72916666666</v>
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4476,40 +4476,40 @@
         <v>4.2</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA34" t="n">
         <v>1.9</v>
@@ -4518,22 +4518,22 @@
         <v>1.8</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46019.85416666666</v>

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.9</v>
+        <v>1.34</v>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N5" t="n">
-        <v>1.49</v>
+        <v>8</v>
       </c>
       <c r="O5" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="P5" t="n">
-        <v>2.24</v>
+        <v>2.37</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.05</v>
+        <v>7</v>
       </c>
       <c r="R5" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>2.96</v>
+        <v>3.18</v>
       </c>
       <c r="T5" t="n">
-        <v>2.48</v>
+        <v>2.33</v>
       </c>
       <c r="U5" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V5" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AB5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE5" t="n">
         <v>1.86</v>
       </c>
-      <c r="AC5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.79</v>
-      </c>
       <c r="AF5" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.07</v>
+        <v>2.94</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46019.3125</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.34</v>
+        <v>4.9</v>
       </c>
       <c r="M6" t="n">
+        <v>4</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="O6" t="n">
         <v>5</v>
       </c>
-      <c r="N6" t="n">
-        <v>8</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.7</v>
-      </c>
       <c r="P6" t="n">
-        <v>2.37</v>
+        <v>2.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>7</v>
+        <v>2.05</v>
       </c>
       <c r="R6" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>3.18</v>
+        <v>2.96</v>
       </c>
       <c r="T6" t="n">
-        <v>2.33</v>
+        <v>2.48</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V6" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.19</v>
+        <v>1.86</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.42</v>
+        <v>3.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.94</v>
+        <v>1.07</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46019.3125</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="O20" t="n">
-        <v>4.35</v>
+        <v>3.66</v>
       </c>
       <c r="P20" t="n">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="S20" t="n">
-        <v>2.53</v>
+        <v>2.34</v>
       </c>
       <c r="T20" t="n">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="U20" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="V20" t="n">
-        <v>8.1</v>
+        <v>9.9</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
         <v>1.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.99</v>
+        <v>2.55</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.84</v>
+        <v>4.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.82</v>
+        <v>1.39</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46019.52083333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="M21" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="O21" t="n">
-        <v>3.66</v>
+        <v>4.35</v>
       </c>
       <c r="P21" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>2.58</v>
       </c>
       <c r="R21" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="S21" t="n">
-        <v>2.34</v>
+        <v>2.53</v>
       </c>
       <c r="T21" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="U21" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="V21" t="n">
-        <v>9.9</v>
+        <v>8.1</v>
       </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
         <v>1.08</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.55</v>
+        <v>2.99</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.6</v>
+        <v>3.84</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AE21" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.39</v>
+        <v>1.82</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46019.52083333334</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="M24" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>1.92</v>
+        <v>3.45</v>
       </c>
       <c r="O24" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="P24" t="n">
-        <v>2.54</v>
+        <v>2.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="R24" t="n">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>4.6</v>
+        <v>2.77</v>
       </c>
       <c r="T24" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="U24" t="n">
-        <v>1.89</v>
+        <v>1.39</v>
       </c>
       <c r="V24" t="n">
-        <v>3.5</v>
+        <v>7.8</v>
       </c>
       <c r="W24" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.02</v>
+        <v>1.33</v>
       </c>
       <c r="Z24" t="n">
-        <v>8</v>
+        <v>3.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.26</v>
+        <v>1.97</v>
       </c>
       <c r="AB24" t="n">
-        <v>3.48</v>
+        <v>1.83</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.82</v>
+        <v>3.34</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.88</v>
+        <v>1.27</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AF24" t="n">
-        <v>3.51</v>
+        <v>2.01</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46019.5625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N25" t="n">
-        <v>3.45</v>
+        <v>1.92</v>
       </c>
       <c r="O25" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="P25" t="n">
-        <v>2.05</v>
+        <v>2.54</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="R25" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="S25" t="n">
-        <v>2.77</v>
+        <v>4.6</v>
       </c>
       <c r="T25" t="n">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="U25" t="n">
-        <v>1.39</v>
+        <v>1.89</v>
       </c>
       <c r="V25" t="n">
-        <v>7.8</v>
+        <v>3.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.3</v>
+        <v>8</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.97</v>
+        <v>1.26</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.83</v>
+        <v>3.48</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.34</v>
+        <v>1.82</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.27</v>
+        <v>1.88</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.01</v>
+        <v>3.51</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46019.5625</v>

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -662,19 +662,19 @@
         <v>2.28</v>
       </c>
       <c r="M2" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="N2" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="O2" t="n">
         <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="R2" t="n">
         <v>1.36</v>
@@ -704,16 +704,16 @@
         <v>3.28</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AC2" t="n">
         <v>3.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AE2" t="n">
         <v>1.68</v>
@@ -722,10 +722,10 @@
         <v>2.02</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46019.14583333334</v>
@@ -897,16 +897,16 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="M4" t="n">
         <v>3.4</v>
       </c>
       <c r="N4" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="O4" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="P4" t="n">
         <v>2.2</v>
@@ -924,7 +924,7 @@
         <v>2.9</v>
       </c>
       <c r="U4" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="V4" t="n">
         <v>7.4</v>
@@ -936,19 +936,19 @@
         <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.38</v>
+        <v>3.28</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AB4" t="n">
         <v>1.78</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="AD4" t="n">
         <v>1.3</v>
@@ -963,7 +963,7 @@
         <v>1.23</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46019.22916666666</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="M9" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="O9" t="n">
         <v>2.75</v>
@@ -1510,10 +1510,10 @@
         <v>3.72</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S9" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="T9" t="n">
         <v>2.88</v>
@@ -1537,10 +1537,10 @@
         <v>2.97</v>
       </c>
       <c r="AA9" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AC9" t="n">
         <v>3.34</v>
@@ -1549,10 +1549,10 @@
         <v>1.25</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AG9" t="n">
         <v>1.25</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.09</v>
+        <v>2.36</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="N13" t="n">
-        <v>3.15</v>
+        <v>2.71</v>
       </c>
       <c r="O13" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.03</v>
+        <v>2.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46019.41666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.36</v>
+        <v>2.09</v>
       </c>
       <c r="M14" t="n">
-        <v>3.03</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.71</v>
+        <v>3.15</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.4</v>
+        <v>2.03</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46019.41666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.05</v>
+        <v>2.65</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>1.77</v>
+        <v>2.75</v>
       </c>
       <c r="O15" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.64</v>
+        <v>3.54</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="S15" t="n">
-        <v>2.66</v>
+        <v>2.57</v>
       </c>
       <c r="T15" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="U15" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="V15" t="n">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.12</v>
+        <v>2.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AB15" t="n">
         <v>1.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.81</v>
+        <v>3.95</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.65</v>
+        <v>5.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>3.77</v>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>1.6</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.54</v>
+        <v>2.1</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.57</v>
+        <v>2.72</v>
       </c>
       <c r="T16" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="U16" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="V16" t="n">
-        <v>8.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.8</v>
+        <v>3.33</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>2.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>1.12</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5.6</v>
+        <v>4.05</v>
       </c>
       <c r="M17" t="n">
-        <v>3.77</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="O17" t="n">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.1</v>
+        <v>2.64</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S17" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="T17" t="n">
-        <v>2.85</v>
+        <v>3.14</v>
       </c>
       <c r="U17" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="V17" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.33</v>
+        <v>3.12</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.5</v>
+        <v>3.81</v>
       </c>
       <c r="AD17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.12</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.26</v>
+        <v>3.2</v>
       </c>
       <c r="M18" t="n">
-        <v>5.1</v>
+        <v>3.55</v>
       </c>
       <c r="N18" t="n">
-        <v>6.8</v>
+        <v>1.93</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.93</v>
+        <v>2.26</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.77</v>
+        <v>1.51</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46019.47916666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.2</v>
+        <v>1.26</v>
       </c>
       <c r="M19" t="n">
-        <v>3.55</v>
+        <v>5.1</v>
       </c>
       <c r="N19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
         <v>1.93</v>
       </c>
-      <c r="O19" t="n">
-        <v>4</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.26</v>
-      </c>
       <c r="AD19" t="n">
-        <v>1.51</v>
+        <v>1.77</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46019.47916666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="M20" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="O20" t="n">
-        <v>3.66</v>
+        <v>4.35</v>
       </c>
       <c r="P20" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>2.58</v>
       </c>
       <c r="R20" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="S20" t="n">
-        <v>2.34</v>
+        <v>2.53</v>
       </c>
       <c r="T20" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="V20" t="n">
-        <v>9.9</v>
+        <v>8.1</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
         <v>1.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.55</v>
+        <v>2.99</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.6</v>
+        <v>3.84</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AE20" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.39</v>
+        <v>1.82</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46019.52083333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N21" t="n">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="O21" t="n">
-        <v>4.35</v>
+        <v>3.66</v>
       </c>
       <c r="P21" t="n">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="S21" t="n">
-        <v>2.53</v>
+        <v>2.34</v>
       </c>
       <c r="T21" t="n">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="U21" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="V21" t="n">
-        <v>8.1</v>
+        <v>9.9</v>
       </c>
       <c r="W21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X21" t="n">
         <v>1.08</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.99</v>
+        <v>2.55</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.84</v>
+        <v>4.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.82</v>
+        <v>1.39</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46019.52083333334</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G31" t="n">

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -778,40 +778,40 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="M3" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="N3" t="n">
-        <v>6.2</v>
+        <v>4.95</v>
       </c>
       <c r="O3" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="P3" t="n">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="Q3" t="n">
         <v>4.8</v>
       </c>
       <c r="R3" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S3" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="T3" t="n">
-        <v>2.45</v>
+        <v>2.74</v>
       </c>
       <c r="U3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="V3" t="n">
         <v>6.5</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X3" t="n">
         <v>1.05</v>
@@ -820,28 +820,28 @@
         <v>1.21</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.58</v>
+        <v>1.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="AD3" t="n">
         <v>1.39</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AH3" t="n">
         <v>2.33</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.34</v>
+        <v>4.61</v>
       </c>
       <c r="M5" t="n">
+        <v>4</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="O5" t="n">
         <v>5</v>
       </c>
-      <c r="N5" t="n">
-        <v>8</v>
-      </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V5" t="n">
+        <v>6</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AA5" t="n">
         <v>1.7</v>
       </c>
-      <c r="P5" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>7</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W5" t="n">
+      <c r="AB5" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH5" t="n">
         <v>1.09</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>2.94</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46019.3125</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.9</v>
+        <v>1.37</v>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>4.55</v>
       </c>
       <c r="N6" t="n">
+        <v>8</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U6" t="n">
         <v>1.49</v>
       </c>
-      <c r="O6" t="n">
-        <v>5</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S6" t="n">
+      <c r="V6" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH6" t="n">
         <v>2.96</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V6" t="n">
-        <v>6</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.07</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46019.3125</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.28</v>
+        <v>4.7</v>
       </c>
       <c r="M11" t="n">
-        <v>4.9</v>
+        <v>3.95</v>
       </c>
       <c r="N11" t="n">
-        <v>6.7</v>
+        <v>1.63</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>9.5</v>
+        <v>1.28</v>
       </c>
       <c r="M12" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="N12" t="n">
-        <v>1.18</v>
+        <v>6.7</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1900,10 +1900,10 @@
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.29</v>
+        <v>2.17</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.36</v>
+        <v>1.68</v>
       </c>
       <c r="M13" t="n">
-        <v>3.03</v>
+        <v>3.29</v>
       </c>
       <c r="N13" t="n">
-        <v>2.71</v>
+        <v>4.73</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2087,28 +2087,28 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
-        <v>2.69</v>
+        <v>2.85</v>
       </c>
       <c r="P14" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.87</v>
+        <v>3.89</v>
       </c>
       <c r="R14" t="n">
         <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>2.82</v>
+        <v>2.59</v>
       </c>
       <c r="T14" t="n">
         <v>2.96</v>
@@ -2117,7 +2117,7 @@
         <v>1.32</v>
       </c>
       <c r="V14" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="W14" t="n">
         <v>1.02</v>
@@ -2126,7 +2126,7 @@
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z14" t="n">
         <v>3.04</v>
@@ -2141,7 +2141,7 @@
         <v>3.58</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AE14" t="n">
         <v>1.79</v>
@@ -2150,7 +2150,7 @@
         <v>1.9</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
         <v>1.53</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.65</v>
+        <v>5.6</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>3.77</v>
       </c>
       <c r="N15" t="n">
-        <v>2.75</v>
+        <v>1.6</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.54</v>
+        <v>2.1</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.57</v>
+        <v>2.72</v>
       </c>
       <c r="T15" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="V15" t="n">
-        <v>8.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.8</v>
+        <v>3.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>2.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.44</v>
+        <v>1.12</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.6</v>
+        <v>2.65</v>
       </c>
       <c r="M16" t="n">
-        <v>3.77</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>1.6</v>
+        <v>2.75</v>
       </c>
       <c r="O16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V16" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA16" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V16" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y16" t="n">
+      <c r="AB16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z16" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AH16" t="n">
-        <v>1.12</v>
+        <v>1.44</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46019.45833333334</v>
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="N22" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3158,40 +3158,40 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="M23" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="P23" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.2</v>
+        <v>4.26</v>
       </c>
       <c r="R23" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
         <v>2.85</v>
       </c>
       <c r="T23" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="U23" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="V23" t="n">
-        <v>6.35</v>
+        <v>6.45</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X23" t="n">
         <v>1.01</v>
@@ -3200,31 +3200,31 @@
         <v>1.19</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="AA23" t="n">
         <v>1.75</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC23" t="n">
         <v>3.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AG23" t="n">
         <v>1.23</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46019.54166666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N24" t="n">
-        <v>3.45</v>
+        <v>1.92</v>
       </c>
       <c r="O24" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="P24" t="n">
-        <v>2.05</v>
+        <v>2.54</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="S24" t="n">
-        <v>2.77</v>
+        <v>4.6</v>
       </c>
       <c r="T24" t="n">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="U24" t="n">
-        <v>1.39</v>
+        <v>1.89</v>
       </c>
       <c r="V24" t="n">
-        <v>7.8</v>
+        <v>3.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.33</v>
+        <v>1.02</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.3</v>
+        <v>8</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.97</v>
+        <v>1.26</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.83</v>
+        <v>3.48</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.34</v>
+        <v>1.82</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.27</v>
+        <v>1.88</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.01</v>
+        <v>3.51</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46019.5625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="M25" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>1.92</v>
+        <v>3.45</v>
       </c>
       <c r="O25" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="P25" t="n">
-        <v>2.54</v>
+        <v>2.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="R25" t="n">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>4.6</v>
+        <v>2.77</v>
       </c>
       <c r="T25" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="U25" t="n">
-        <v>1.89</v>
+        <v>1.39</v>
       </c>
       <c r="V25" t="n">
-        <v>3.5</v>
+        <v>7.8</v>
       </c>
       <c r="W25" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.02</v>
+        <v>1.33</v>
       </c>
       <c r="Z25" t="n">
-        <v>8</v>
+        <v>3.3</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.26</v>
+        <v>1.97</v>
       </c>
       <c r="AB25" t="n">
-        <v>3.48</v>
+        <v>1.83</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.82</v>
+        <v>3.34</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.88</v>
+        <v>1.27</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AF25" t="n">
-        <v>3.51</v>
+        <v>2.01</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46019.5625</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G30" t="n">

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="N3" t="n">
-        <v>4.95</v>
+        <v>6.2</v>
       </c>
       <c r="O3" t="n">
         <v>2.12</v>
@@ -823,10 +823,10 @@
         <v>3.62</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.9</v>
+        <v>1.58</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="AC3" t="n">
         <v>3.04</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>4.61</v>
+        <v>1.37</v>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="N5" t="n">
-        <v>1.47</v>
+        <v>6.4</v>
       </c>
       <c r="O5" t="n">
-        <v>5</v>
+        <v>1.89</v>
       </c>
       <c r="P5" t="n">
-        <v>2.23</v>
+        <v>2.59</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.1</v>
+        <v>6.86</v>
       </c>
       <c r="R5" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="T5" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="U5" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="V5" t="n">
-        <v>6</v>
+        <v>5.55</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.84</v>
+        <v>4.02</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.1</v>
+        <v>2.52</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.09</v>
+        <v>2.68</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46019.3125</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.37</v>
+        <v>5.8</v>
       </c>
       <c r="M6" t="n">
-        <v>4.55</v>
+        <v>4.53</v>
       </c>
       <c r="N6" t="n">
-        <v>8</v>
+        <v>1.41</v>
       </c>
       <c r="O6" t="n">
-        <v>1.75</v>
+        <v>6.21</v>
       </c>
       <c r="P6" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.75</v>
+        <v>1.97</v>
       </c>
       <c r="R6" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S6" t="n">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.36</v>
+        <v>2.58</v>
       </c>
       <c r="U6" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="V6" t="n">
-        <v>5.45</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.5</v>
+        <v>3.88</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.46</v>
+        <v>3.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.96</v>
+        <v>1.06</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46019.3125</v>
@@ -1263,28 +1263,28 @@
         <v>4.3</v>
       </c>
       <c r="O7" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="P7" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="Q7" t="n">
         <v>4.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="T7" t="n">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="U7" t="n">
         <v>1.37</v>
       </c>
       <c r="V7" t="n">
-        <v>6.9</v>
+        <v>6.95</v>
       </c>
       <c r="W7" t="n">
         <v>1.04</v>
@@ -1293,7 +1293,7 @@
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z7" t="n">
         <v>3.2</v>
@@ -1308,19 +1308,19 @@
         <v>3.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46019.33333333334</v>
@@ -1391,22 +1391,22 @@
         <v>7.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="U8" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="V8" t="n">
         <v>6.25</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X8" t="n">
         <v>1</v>
@@ -1430,7 +1430,7 @@
         <v>1.35</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AF8" t="n">
         <v>1.67</v>
@@ -1632,13 +1632,13 @@
         <v>1.17</v>
       </c>
       <c r="S10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T10" t="n">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="U10" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="V10" t="n">
         <v>3.3</v>
@@ -1650,10 +1650,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="AA10" t="n">
         <v>1.28</v>
@@ -1671,7 +1671,7 @@
         <v>2.19</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="AG10" t="n">
         <v>1.02</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.7</v>
+        <v>1.28</v>
       </c>
       <c r="M11" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="N11" t="n">
-        <v>1.63</v>
+        <v>6.7</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.29</v>
+        <v>2.17</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.28</v>
+        <v>4.7</v>
       </c>
       <c r="M12" t="n">
-        <v>4.9</v>
+        <v>3.95</v>
       </c>
       <c r="N12" t="n">
-        <v>6.7</v>
+        <v>1.63</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,16 +1894,16 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O14" t="n">
         <v>2.85</v>
@@ -2102,7 +2102,7 @@
         <v>1.98</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="R14" t="n">
         <v>1.41</v>
@@ -2111,10 +2111,10 @@
         <v>2.59</v>
       </c>
       <c r="T14" t="n">
-        <v>2.96</v>
+        <v>3.07</v>
       </c>
       <c r="U14" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
         <v>8</v>
@@ -2126,7 +2126,7 @@
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="Z14" t="n">
         <v>3.04</v>
@@ -2138,7 +2138,7 @@
         <v>1.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.58</v>
+        <v>3.63</v>
       </c>
       <c r="AD14" t="n">
         <v>1.27</v>
@@ -2224,10 +2224,10 @@
         <v>2.1</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.72</v>
+        <v>2.81</v>
       </c>
       <c r="T15" t="n">
         <v>2.85</v>
@@ -2239,7 +2239,7 @@
         <v>7.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
         <v>1.06</v>
@@ -2260,7 +2260,7 @@
         <v>3.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE15" t="n">
         <v>1.95</v>
@@ -2337,25 +2337,25 @@
         <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.54</v>
+        <v>3.57</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S16" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="T16" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W16" t="n">
         <v>1.04</v>
@@ -2376,19 +2376,19 @@
         <v>1.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AD16" t="n">
         <v>1.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AF16" t="n">
         <v>1.91</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="AH16" t="n">
         <v>1.44</v>
@@ -2459,7 +2459,7 @@
         <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="R17" t="n">
         <v>1.41</v>
@@ -2468,7 +2468,7 @@
         <v>2.66</v>
       </c>
       <c r="T17" t="n">
-        <v>3.14</v>
+        <v>2.45</v>
       </c>
       <c r="U17" t="n">
         <v>1.34</v>
@@ -2507,10 +2507,10 @@
         <v>1.9</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.2</v>
+        <v>1.26</v>
       </c>
       <c r="M18" t="n">
-        <v>3.55</v>
+        <v>5.1</v>
       </c>
       <c r="N18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
         <v>1.93</v>
       </c>
-      <c r="O18" t="n">
-        <v>4</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.26</v>
-      </c>
       <c r="AD18" t="n">
-        <v>1.51</v>
+        <v>1.77</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46019.47916666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.26</v>
+        <v>3.2</v>
       </c>
       <c r="M19" t="n">
-        <v>5.1</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>6.8</v>
+        <v>1.93</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.93</v>
+        <v>2.26</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.77</v>
+        <v>1.51</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46019.47916666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="O20" t="n">
-        <v>4.35</v>
+        <v>3.66</v>
       </c>
       <c r="P20" t="n">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.58</v>
+        <v>3.06</v>
       </c>
       <c r="R20" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="S20" t="n">
-        <v>2.53</v>
+        <v>2.34</v>
       </c>
       <c r="T20" t="n">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="U20" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="V20" t="n">
-        <v>8.1</v>
+        <v>9.9</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
         <v>1.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.99</v>
+        <v>2.54</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.84</v>
+        <v>4.55</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.82</v>
+        <v>1.39</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46019.52083333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="M21" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="O21" t="n">
-        <v>3.66</v>
+        <v>4.7</v>
       </c>
       <c r="P21" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>2.57</v>
       </c>
       <c r="R21" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="S21" t="n">
-        <v>2.34</v>
+        <v>2.53</v>
       </c>
       <c r="T21" t="n">
-        <v>3.48</v>
+        <v>3.33</v>
       </c>
       <c r="U21" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="V21" t="n">
-        <v>9.9</v>
+        <v>8.1</v>
       </c>
       <c r="W21" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
         <v>1.08</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.55</v>
+        <v>3.01</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.6</v>
+        <v>3.84</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AE21" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.39</v>
+        <v>1.82</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46019.52083333334</v>
@@ -3295,22 +3295,22 @@
         <v>2.3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S24" t="n">
-        <v>4.6</v>
+        <v>4.65</v>
       </c>
       <c r="T24" t="n">
         <v>1.75</v>
       </c>
       <c r="U24" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="V24" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="W24" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
@@ -3319,7 +3319,7 @@
         <v>1.02</v>
       </c>
       <c r="Z24" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA24" t="n">
         <v>1.26</v>
@@ -3334,13 +3334,13 @@
         <v>1.88</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF24" t="n">
-        <v>3.51</v>
+        <v>3.58</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AH24" t="n">
         <v>1.3</v>
@@ -3408,28 +3408,28 @@
         <v>2.8</v>
       </c>
       <c r="P25" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q25" t="n">
         <v>3.7</v>
       </c>
       <c r="R25" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S25" t="n">
         <v>2.77</v>
       </c>
       <c r="T25" t="n">
-        <v>2.75</v>
+        <v>2.98</v>
       </c>
       <c r="U25" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="W25" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X25" t="n">
         <v>1</v>
@@ -3447,7 +3447,7 @@
         <v>1.83</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.34</v>
+        <v>3.55</v>
       </c>
       <c r="AD25" t="n">
         <v>1.27</v>
@@ -3456,10 +3456,10 @@
         <v>1.67</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH25" t="n">
         <v>1.65</v>
@@ -3527,7 +3527,7 @@
         <v>2.25</v>
       </c>
       <c r="P26" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q26" t="n">
         <v>4.6</v>
@@ -3542,7 +3542,7 @@
         <v>2.8</v>
       </c>
       <c r="U26" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="V26" t="n">
         <v>7</v>
@@ -3575,7 +3575,7 @@
         <v>1.85</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AG26" t="n">
         <v>1.29</v>
@@ -3658,7 +3658,7 @@
         <v>2.62</v>
       </c>
       <c r="T27" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="U27" t="n">
         <v>1.33</v>
@@ -3673,7 +3673,7 @@
         <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z27" t="n">
         <v>3</v>
@@ -3688,16 +3688,16 @@
         <v>3.85</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AF27" t="n">
         <v>2</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AH27" t="n">
         <v>1.33</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4238,31 +4238,31 @@
         <v>19</v>
       </c>
       <c r="O32" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="P32" t="n">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="Q32" t="n">
-        <v>10.7</v>
+        <v>11</v>
       </c>
       <c r="R32" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S32" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="T32" t="n">
         <v>1.95</v>
       </c>
       <c r="U32" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V32" t="n">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="W32" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X32" t="n">
         <v>1.01</v>
@@ -4286,7 +4286,7 @@
         <v>1.65</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="AF32" t="n">
         <v>1.63</v>
@@ -4295,7 +4295,7 @@
         <v>1.08</v>
       </c>
       <c r="AH32" t="n">
-        <v>6.15</v>
+        <v>6.1</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46019.72916666666</v>
@@ -4357,40 +4357,40 @@
         <v>1.35</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>6.83</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA33" t="n">
         <v>1.55</v>
@@ -4405,16 +4405,16 @@
         <v>1.57</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46019.75</v>

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -659,43 +659,43 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="M2" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="N2" t="n">
-        <v>2.78</v>
+        <v>3.25</v>
       </c>
       <c r="O2" t="n">
-        <v>3</v>
+        <v>2.51</v>
       </c>
       <c r="P2" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.4</v>
+        <v>3.87</v>
       </c>
       <c r="R2" t="n">
         <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="T2" t="n">
-        <v>2.87</v>
+        <v>2.79</v>
       </c>
       <c r="U2" t="n">
         <v>1.35</v>
       </c>
       <c r="V2" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="W2" t="n">
         <v>1.03</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
         <v>1.25</v>
@@ -707,25 +707,25 @@
         <v>1.95</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AC2" t="n">
         <v>3.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46019.14583333334</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="M3" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="N3" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="O3" t="n">
         <v>2.12</v>
@@ -793,7 +793,7 @@
         <v>2.23</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="R3" t="n">
         <v>1.35</v>
@@ -808,7 +808,7 @@
         <v>1.43</v>
       </c>
       <c r="V3" t="n">
-        <v>6.5</v>
+        <v>6.45</v>
       </c>
       <c r="W3" t="n">
         <v>1.1</v>
@@ -817,22 +817,22 @@
         <v>1.05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="Z3" t="n">
         <v>3.62</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="AC3" t="n">
         <v>3.04</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE3" t="n">
         <v>1.81</v>
@@ -897,37 +897,37 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="M4" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N4" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="O4" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.44</v>
+        <v>4.55</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S4" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="T4" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="U4" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V4" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="W4" t="n">
         <v>1.03</v>
@@ -942,28 +942,28 @@
         <v>3.28</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="AD4" t="n">
         <v>1.3</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AG4" t="n">
         <v>1.23</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46019.22916666666</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.37</v>
+        <v>5.8</v>
       </c>
       <c r="M5" t="n">
-        <v>4.3</v>
+        <v>4.53</v>
       </c>
       <c r="N5" t="n">
-        <v>6.4</v>
+        <v>1.41</v>
       </c>
       <c r="O5" t="n">
-        <v>1.89</v>
+        <v>6.21</v>
       </c>
       <c r="P5" t="n">
-        <v>2.59</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.86</v>
+        <v>1.97</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S5" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="T5" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="U5" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="V5" t="n">
-        <v>5.55</v>
+        <v>6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
         <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.02</v>
+        <v>3.88</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.52</v>
+        <v>3.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.68</v>
+        <v>1.06</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46019.3125</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5.8</v>
+        <v>1.37</v>
       </c>
       <c r="M6" t="n">
-        <v>4.53</v>
+        <v>4.3</v>
       </c>
       <c r="N6" t="n">
-        <v>1.41</v>
+        <v>6.4</v>
       </c>
       <c r="O6" t="n">
-        <v>6.21</v>
+        <v>1.89</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3</v>
+        <v>2.59</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.97</v>
+        <v>6.86</v>
       </c>
       <c r="R6" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="T6" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="V6" t="n">
-        <v>6</v>
+        <v>5.55</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X6" t="n">
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.88</v>
+        <v>4.02</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.1</v>
+        <v>2.52</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.06</v>
+        <v>2.68</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46019.3125</v>
@@ -1254,37 +1254,37 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="N7" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="O7" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="P7" t="n">
         <v>2.07</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.2</v>
+        <v>4.97</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>2.69</v>
+        <v>2.95</v>
       </c>
       <c r="T7" t="n">
-        <v>2.81</v>
+        <v>2.55</v>
       </c>
       <c r="U7" t="n">
         <v>1.37</v>
       </c>
       <c r="V7" t="n">
-        <v>6.95</v>
+        <v>6.9</v>
       </c>
       <c r="W7" t="n">
         <v>1.04</v>
@@ -1293,34 +1293,34 @@
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AD7" t="n">
         <v>1.28</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AF7" t="n">
         <v>1.9</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46019.33333333334</v>
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="M8" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="N8" t="n">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="O8" t="n">
         <v>1.85</v>
@@ -1391,37 +1391,37 @@
         <v>7.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="T8" t="n">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="U8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="V8" t="n">
         <v>6.25</v>
       </c>
       <c r="W8" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
         <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z8" t="n">
         <v>3.68</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="n">
         <v>3</v>
@@ -1430,7 +1430,7 @@
         <v>1.35</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AF8" t="n">
         <v>1.67</v>
@@ -1492,28 +1492,28 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="M9" t="n">
         <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="O9" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="P9" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.72</v>
+        <v>4.45</v>
       </c>
       <c r="R9" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S9" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="T9" t="n">
         <v>2.88</v>
@@ -1537,7 +1537,7 @@
         <v>2.97</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB9" t="n">
         <v>1.7</v>
@@ -1546,19 +1546,19 @@
         <v>3.34</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46019.375</v>
@@ -1611,28 +1611,28 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="M10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N10" t="n">
-        <v>26</v>
+        <v>15.5</v>
       </c>
       <c r="O10" t="n">
         <v>1.43</v>
       </c>
       <c r="P10" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="Q10" t="n">
-        <v>14.6</v>
+        <v>15</v>
       </c>
       <c r="R10" t="n">
         <v>1.17</v>
       </c>
       <c r="S10" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T10" t="n">
         <v>1.91</v>
@@ -1653,31 +1653,31 @@
         <v>1.06</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
       <c r="AA10" t="n">
         <v>1.28</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.34</v>
+        <v>3.55</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AG10" t="n">
         <v>1.02</v>
       </c>
       <c r="AH10" t="n">
-        <v>5.65</v>
+        <v>5.7</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46019.38541666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.28</v>
+        <v>6.2</v>
       </c>
       <c r="M11" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="N11" t="n">
-        <v>6.7</v>
+        <v>1.44</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>6.37</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.17</v>
+        <v>2.56</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46019.40972222222</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.7</v>
+        <v>1.36</v>
       </c>
       <c r="M12" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="N12" t="n">
-        <v>1.63</v>
+        <v>6</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>6.24</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.08</v>
+        <v>2.36</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46019.40972222222</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.6</v>
+        <v>2.73</v>
       </c>
       <c r="M15" t="n">
-        <v>3.77</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>1.6</v>
+        <v>2.76</v>
       </c>
       <c r="O15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.1</v>
+        <v>3.57</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="S15" t="n">
-        <v>2.81</v>
+        <v>2.54</v>
       </c>
       <c r="T15" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="U15" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>7.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W15" t="n">
         <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.33</v>
+        <v>2.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.3</v>
+        <v>1.41</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.12</v>
+        <v>1.46</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.65</v>
+        <v>3.4</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>1.95</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="P16" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.57</v>
+        <v>2.66</v>
       </c>
       <c r="R16" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="T16" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V16" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.2</v>
+        <v>3.84</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.05</v>
+        <v>6.25</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="N17" t="n">
-        <v>1.77</v>
+        <v>1.43</v>
       </c>
       <c r="O17" t="n">
-        <v>3.7</v>
+        <v>6</v>
       </c>
       <c r="P17" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.66</v>
+        <v>2.1</v>
       </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>2.66</v>
+        <v>2.85</v>
       </c>
       <c r="T17" t="n">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="U17" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="V17" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.81</v>
+        <v>3.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R18" t="n">
         <v>1.26</v>
       </c>
-      <c r="M18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.93</v>
+        <v>2.35</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46019.47916666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.2</v>
+        <v>1.26</v>
       </c>
       <c r="M19" t="n">
-        <v>3.55</v>
+        <v>5.1</v>
       </c>
       <c r="N19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
         <v>1.93</v>
       </c>
-      <c r="O19" t="n">
-        <v>4</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.26</v>
-      </c>
       <c r="AD19" t="n">
-        <v>1.51</v>
+        <v>1.77</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46019.47916666666</v>
@@ -2801,16 +2801,16 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="M20" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N20" t="n">
         <v>2.35</v>
       </c>
       <c r="O20" t="n">
-        <v>3.66</v>
+        <v>4.1</v>
       </c>
       <c r="P20" t="n">
         <v>1.87</v>
@@ -2819,7 +2819,7 @@
         <v>3.06</v>
       </c>
       <c r="R20" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S20" t="n">
         <v>2.34</v>
@@ -2834,7 +2834,7 @@
         <v>9.9</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X20" t="n">
         <v>1.08</v>
@@ -2846,10 +2846,10 @@
         <v>2.54</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AC20" t="n">
         <v>4.55</v>
@@ -2858,10 +2858,10 @@
         <v>1.13</v>
       </c>
       <c r="AE20" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG20" t="n">
         <v>1.39</v>
@@ -2920,22 +2920,22 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>3.36</v>
       </c>
       <c r="N21" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="O21" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="P21" t="n">
-        <v>1.99</v>
+        <v>2.18</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.57</v>
+        <v>2.43</v>
       </c>
       <c r="R21" t="n">
         <v>1.46</v>
@@ -2962,19 +2962,19 @@
         <v>1.34</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.01</v>
+        <v>2.95</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC21" t="n">
         <v>3.84</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE21" t="n">
         <v>1.93</v>
@@ -2983,10 +2983,10 @@
         <v>1.78</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.82</v>
+        <v>1.34</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46019.52083333334</v>
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O22" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V22" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z22" t="n">
         <v>3.95</v>
       </c>
-      <c r="M22" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
       <c r="AA22" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46019.53125</v>
@@ -3158,37 +3158,37 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N23" t="n">
         <v>3.5</v>
       </c>
       <c r="O23" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="P23" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.26</v>
+        <v>3.52</v>
       </c>
       <c r="R23" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S23" t="n">
-        <v>2.85</v>
+        <v>2.96</v>
       </c>
       <c r="T23" t="n">
-        <v>2.59</v>
+        <v>2.64</v>
       </c>
       <c r="U23" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="V23" t="n">
-        <v>6.45</v>
+        <v>6.4</v>
       </c>
       <c r="W23" t="n">
         <v>1.05</v>
@@ -3200,22 +3200,22 @@
         <v>1.19</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="AA23" t="n">
         <v>1.75</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AD23" t="n">
         <v>1.33</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AF23" t="n">
         <v>2.1</v>
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="M24" t="n">
-        <v>3.85</v>
+        <v>4.15</v>
       </c>
       <c r="N24" t="n">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="O24" t="n">
-        <v>3.25</v>
+        <v>3.74</v>
       </c>
       <c r="P24" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="R24" t="n">
         <v>1.12</v>
       </c>
       <c r="S24" t="n">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="T24" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="U24" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="V24" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="W24" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Z24" t="n">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AB24" t="n">
-        <v>3.48</v>
+        <v>3.75</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.82</v>
+        <v>1.66</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AF24" t="n">
-        <v>3.58</v>
+        <v>3.51</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46019.5625</v>
@@ -3396,40 +3396,40 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="M25" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N25" t="n">
-        <v>3.45</v>
+        <v>3.32</v>
       </c>
       <c r="O25" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P25" t="n">
         <v>2.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
       <c r="T25" t="n">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="V25" t="n">
         <v>7</v>
       </c>
       <c r="W25" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X25" t="n">
         <v>1</v>
@@ -3441,25 +3441,25 @@
         <v>3.3</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.55</v>
+        <v>3.33</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AE25" t="n">
         <v>1.67</v>
       </c>
       <c r="AF25" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AH25" t="n">
         <v>1.65</v>
@@ -3518,16 +3518,16 @@
         <v>1.76</v>
       </c>
       <c r="M26" t="n">
-        <v>3.47</v>
+        <v>3.6</v>
       </c>
       <c r="N26" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O26" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="P26" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="Q26" t="n">
         <v>4.6</v>
@@ -3542,7 +3542,7 @@
         <v>2.8</v>
       </c>
       <c r="U26" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="V26" t="n">
         <v>7</v>
@@ -3560,13 +3560,13 @@
         <v>3.36</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="AD26" t="n">
         <v>1.29</v>
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="M27" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="N27" t="n">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="O27" t="n">
         <v>4.1</v>
@@ -3670,7 +3670,7 @@
         <v>1.02</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y27" t="n">
         <v>1.29</v>
@@ -3679,10 +3679,10 @@
         <v>3</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AC27" t="n">
         <v>3.85</v>
@@ -3694,7 +3694,7 @@
         <v>1.86</v>
       </c>
       <c r="AF27" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AG27" t="n">
         <v>1.35</v>
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.23</v>
+        <v>3.75</v>
       </c>
       <c r="M28" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>2.12</v>
+        <v>2.01</v>
       </c>
       <c r="O28" t="n">
         <v>3.75</v>
@@ -3768,28 +3768,28 @@
         <v>2.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.68</v>
+        <v>2.45</v>
       </c>
       <c r="R28" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="S28" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="T28" t="n">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="U28" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="V28" t="n">
-        <v>6.55</v>
+        <v>6.35</v>
       </c>
       <c r="W28" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X28" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y28" t="n">
         <v>1.22</v>
@@ -3798,13 +3798,13 @@
         <v>3.9</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="AD28" t="n">
         <v>1.4</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4229,31 +4229,31 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="M32" t="n">
-        <v>7.3</v>
+        <v>8.1</v>
       </c>
       <c r="N32" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="O32" t="n">
         <v>1.47</v>
       </c>
       <c r="P32" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="Q32" t="n">
-        <v>11</v>
+        <v>10.7</v>
       </c>
       <c r="R32" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S32" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T32" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="U32" t="n">
         <v>1.72</v>
@@ -4262,31 +4262,31 @@
         <v>4.15</v>
       </c>
       <c r="W32" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X32" t="n">
         <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.2</v>
+        <v>5.55</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.94</v>
+        <v>3.04</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AF32" t="n">
         <v>1.63</v>
@@ -4295,7 +4295,7 @@
         <v>1.08</v>
       </c>
       <c r="AH32" t="n">
-        <v>6.1</v>
+        <v>6.15</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46019.72916666666</v>
@@ -4348,28 +4348,28 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>6.9</v>
+        <v>6.3</v>
       </c>
       <c r="M33" t="n">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="N33" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="O33" t="n">
-        <v>6.83</v>
+        <v>6.62</v>
       </c>
       <c r="P33" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="R33" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S33" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="T33" t="n">
         <v>2.24</v>
@@ -4387,34 +4387,34 @@
         <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AB33" t="n">
         <v>2.3</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AD33" t="n">
         <v>1.57</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46019.75</v>
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="M34" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="N34" t="n">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="O34" t="n">
         <v>2.21</v>
@@ -4494,7 +4494,7 @@
         <v>2.79</v>
       </c>
       <c r="U34" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="V34" t="n">
         <v>6.8</v>
@@ -4512,7 +4512,7 @@
         <v>3.28</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AB34" t="n">
         <v>1.8</v>

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="N3" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="O3" t="n">
         <v>2.12</v>
@@ -823,10 +823,10 @@
         <v>3.62</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="AC3" t="n">
         <v>3.04</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="M7" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="O7" t="n">
         <v>2.41</v>
@@ -1299,10 +1299,10 @@
         <v>3.45</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
         <v>3.14</v>
@@ -1730,37 +1730,37 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="M11" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="N11" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="O11" t="n">
-        <v>6.37</v>
+        <v>6.58</v>
       </c>
       <c r="P11" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S11" t="n">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="T11" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="U11" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="V11" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="W11" t="n">
         <v>1.08</v>
@@ -1769,34 +1769,34 @@
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.56</v>
+        <v>2.29</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46019.40972222222</v>
@@ -1849,37 +1849,37 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="M12" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="N12" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="P12" t="n">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>6.24</v>
+        <v>5.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="T12" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U12" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="V12" t="n">
-        <v>5.15</v>
+        <v>5.2</v>
       </c>
       <c r="W12" t="n">
         <v>1.1</v>
@@ -1891,31 +1891,31 @@
         <v>1.12</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="AG12" t="n">
         <v>1.13</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46019.40972222222</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.68</v>
+        <v>2.15</v>
       </c>
       <c r="M13" t="n">
-        <v>3.29</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>4.73</v>
+        <v>3.2</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.4</v>
+        <v>2.03</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46019.41666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.15</v>
+        <v>1.68</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>3.29</v>
       </c>
       <c r="N14" t="n">
-        <v>3.2</v>
+        <v>4.73</v>
       </c>
       <c r="O14" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.03</v>
+        <v>2.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46019.41666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.73</v>
+        <v>6.25</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="N15" t="n">
-        <v>2.76</v>
+        <v>1.43</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P15" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.57</v>
+        <v>2.1</v>
       </c>
       <c r="R15" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.54</v>
+        <v>2.85</v>
       </c>
       <c r="T15" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="V15" t="n">
-        <v>8.800000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="W15" t="n">
         <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="AA15" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG15" t="n">
         <v>2.3</v>
       </c>
-      <c r="AB15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.46</v>
+        <v>1.13</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N16" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="O16" t="n">
         <v>3.7</v>
@@ -2370,10 +2370,10 @@
         <v>3.08</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AC16" t="n">
         <v>3.84</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6.25</v>
+        <v>2.73</v>
       </c>
       <c r="M17" t="n">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>1.43</v>
+        <v>2.76</v>
       </c>
       <c r="O17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.1</v>
+        <v>3.57</v>
       </c>
       <c r="R17" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="S17" t="n">
-        <v>2.85</v>
+        <v>2.54</v>
       </c>
       <c r="T17" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="U17" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>7.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="W17" t="n">
         <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.3</v>
+        <v>1.41</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.13</v>
+        <v>1.46</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46019.45833333334</v>
@@ -3039,28 +3039,28 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.74</v>
+        <v>3.95</v>
       </c>
       <c r="M22" t="n">
-        <v>3.62</v>
+        <v>3.75</v>
       </c>
       <c r="N22" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="O22" t="n">
-        <v>4.36</v>
+        <v>4.57</v>
       </c>
       <c r="P22" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="T22" t="n">
         <v>2.44</v>
@@ -3075,37 +3075,37 @@
         <v>1.07</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
         <v>1.17</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AG22" t="n">
         <v>1.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46019.53125</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>6.3</v>
+        <v>6.9</v>
       </c>
       <c r="M33" t="n">
-        <v>4.35</v>
+        <v>4.4</v>
       </c>
       <c r="N33" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="O33" t="n">
         <v>6.62</v>
@@ -4393,13 +4393,13 @@
         <v>5</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AB33" t="n">
         <v>2.3</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD33" t="n">
         <v>1.57</v>
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="M34" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="N34" t="n">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="O34" t="n">
         <v>2.21</v>
@@ -4512,7 +4512,7 @@
         <v>3.28</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB34" t="n">
         <v>1.8</v>

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -1373,22 +1373,22 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="M8" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="N8" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="P8" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
       <c r="R8" t="n">
         <v>1.36</v>
@@ -1397,37 +1397,37 @@
         <v>2.97</v>
       </c>
       <c r="T8" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="U8" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="V8" t="n">
-        <v>6.25</v>
+        <v>6.8</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AB8" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC8" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE8" t="n">
         <v>2.1</v>
@@ -1611,22 +1611,22 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="M10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N10" t="n">
-        <v>15.5</v>
+        <v>26</v>
       </c>
       <c r="O10" t="n">
         <v>1.43</v>
       </c>
       <c r="P10" t="n">
-        <v>2.94</v>
+        <v>2.97</v>
       </c>
       <c r="Q10" t="n">
-        <v>15</v>
+        <v>14.4</v>
       </c>
       <c r="R10" t="n">
         <v>1.17</v>
@@ -1635,10 +1635,10 @@
         <v>4.7</v>
       </c>
       <c r="T10" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="U10" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V10" t="n">
         <v>3.3</v>
@@ -1653,25 +1653,25 @@
         <v>1.06</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.15</v>
+        <v>6.25</v>
       </c>
       <c r="AA10" t="n">
         <v>1.28</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AG10" t="n">
         <v>1.02</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="M14" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>4.73</v>
+        <v>4.5</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="AB14" t="n">
         <v>1.5</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>6.25</v>
+        <v>2.65</v>
       </c>
       <c r="M15" t="n">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>1.43</v>
+        <v>2.75</v>
       </c>
       <c r="O15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="S15" t="n">
-        <v>2.85</v>
+        <v>2.58</v>
       </c>
       <c r="T15" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="U15" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="V15" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="W15" t="n">
         <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AB15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1.78</v>
       </c>
-      <c r="AC15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AG15" t="n">
-        <v>2.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.13</v>
+        <v>1.44</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.05</v>
+        <v>5.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.35</v>
+        <v>3.77</v>
       </c>
       <c r="N16" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="O16" t="n">
-        <v>3.7</v>
+        <v>4.94</v>
       </c>
       <c r="P16" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.66</v>
+        <v>2.1</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S16" t="n">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="T16" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="U16" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="V16" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.08</v>
+        <v>3.32</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.84</v>
+        <v>3.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.73</v>
+        <v>4.05</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>2.76</v>
+        <v>1.77</v>
       </c>
       <c r="O17" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="P17" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.57</v>
+        <v>2.66</v>
       </c>
       <c r="R17" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="S17" t="n">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="T17" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V17" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X17" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.2</v>
+        <v>3.84</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.46</v>
+        <v>1.26</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.6</v>
+        <v>1.26</v>
       </c>
       <c r="M18" t="n">
-        <v>3.85</v>
+        <v>5.1</v>
       </c>
       <c r="N18" t="n">
-        <v>1.83</v>
+        <v>6.8</v>
       </c>
       <c r="O18" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.35</v>
+        <v>1.93</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.55</v>
+        <v>1.77</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46019.47916666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.26</v>
       </c>
-      <c r="M19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.93</v>
+        <v>2.26</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.77</v>
+        <v>1.59</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46019.47916666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="M20" t="n">
         <v>3.25</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.05</v>
-      </c>
       <c r="N20" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="O20" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="P20" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.06</v>
+        <v>2.57</v>
       </c>
       <c r="R20" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="S20" t="n">
-        <v>2.34</v>
+        <v>2.53</v>
       </c>
       <c r="T20" t="n">
-        <v>3.48</v>
+        <v>2.9</v>
       </c>
       <c r="U20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V20" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.26</v>
-      </c>
-      <c r="V20" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.35</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46019.52083333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="M21" t="n">
-        <v>3.36</v>
+        <v>3.15</v>
       </c>
       <c r="N21" t="n">
-        <v>1.96</v>
+        <v>2.35</v>
       </c>
       <c r="O21" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="P21" t="n">
-        <v>2.18</v>
+        <v>1.87</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.43</v>
+        <v>3.06</v>
       </c>
       <c r="R21" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="S21" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="T21" t="n">
-        <v>3.33</v>
+        <v>3.48</v>
       </c>
       <c r="U21" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="V21" t="n">
-        <v>8.1</v>
+        <v>9.9</v>
       </c>
       <c r="W21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X21" t="n">
         <v>1.08</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.95</v>
+        <v>2.54</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.84</v>
+        <v>4.55</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46019.52083333334</v>
@@ -3277,40 +3277,40 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="M24" t="n">
-        <v>4.15</v>
+        <v>3.85</v>
       </c>
       <c r="N24" t="n">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="O24" t="n">
-        <v>3.74</v>
+        <v>3.55</v>
       </c>
       <c r="P24" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="R24" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="S24" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T24" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U24" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V24" t="n">
         <v>3.3</v>
       </c>
       <c r="W24" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="X24" t="n">
         <v>1.01</v>
@@ -3322,16 +3322,16 @@
         <v>7.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AB24" t="n">
-        <v>3.75</v>
+        <v>3.48</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="AE24" t="n">
         <v>1.25</v>
@@ -3340,7 +3340,7 @@
         <v>3.51</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AH24" t="n">
         <v>1.25</v>
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="M25" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>3.32</v>
+        <v>3.45</v>
       </c>
       <c r="O25" t="n">
         <v>2.75</v>
@@ -3414,7 +3414,7 @@
         <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="S25" t="n">
         <v>2.72</v>
@@ -3423,43 +3423,43 @@
         <v>2.88</v>
       </c>
       <c r="U25" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="V25" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W25" t="n">
         <v>1.04</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z25" t="n">
         <v>3.3</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AF25" t="n">
         <v>2.1</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
         <v>1.65</v>
@@ -3518,10 +3518,10 @@
         <v>1.76</v>
       </c>
       <c r="M26" t="n">
-        <v>3.6</v>
+        <v>3.47</v>
       </c>
       <c r="N26" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O26" t="n">
         <v>2.3</v>
@@ -3533,43 +3533,43 @@
         <v>4.6</v>
       </c>
       <c r="R26" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S26" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="T26" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="U26" t="n">
         <v>1.38</v>
       </c>
       <c r="V26" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W26" t="n">
         <v>1.06</v>
       </c>
       <c r="X26" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="AA26" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE26" t="n">
         <v>1.85</v>
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="M27" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="N27" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="O27" t="n">
         <v>4.1</v>
@@ -3652,46 +3652,46 @@
         <v>2.79</v>
       </c>
       <c r="R27" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S27" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="T27" t="n">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="U27" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V27" t="n">
         <v>8</v>
       </c>
       <c r="W27" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X27" t="n">
         <v>1.07</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="Z27" t="n">
         <v>3</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.85</v>
+        <v>3.54</v>
       </c>
       <c r="AD27" t="n">
         <v>1.22</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AF27" t="n">
         <v>1.9</v>
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.75</v>
+        <v>3.23</v>
       </c>
       <c r="M28" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N28" t="n">
-        <v>2.01</v>
+        <v>2.12</v>
       </c>
       <c r="O28" t="n">
         <v>3.75</v>
@@ -3771,10 +3771,10 @@
         <v>2.45</v>
       </c>
       <c r="R28" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S28" t="n">
-        <v>3.31</v>
+        <v>3.02</v>
       </c>
       <c r="T28" t="n">
         <v>2.59</v>
@@ -3783,28 +3783,28 @@
         <v>1.46</v>
       </c>
       <c r="V28" t="n">
-        <v>6.35</v>
+        <v>6.4</v>
       </c>
       <c r="W28" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X28" t="n">
         <v>1.04</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z28" t="n">
         <v>3.9</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AB28" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.77</v>
+        <v>2.93</v>
       </c>
       <c r="AD28" t="n">
         <v>1.4</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="M32" t="n">
-        <v>8.1</v>
+        <v>7.3</v>
       </c>
       <c r="N32" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="O32" t="n">
         <v>1.47</v>
@@ -4247,19 +4247,19 @@
         <v>10.7</v>
       </c>
       <c r="R32" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S32" t="n">
         <v>3.85</v>
       </c>
       <c r="T32" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="U32" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V32" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="W32" t="n">
         <v>1.18</v>
@@ -4268,22 +4268,22 @@
         <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.55</v>
+        <v>5.6</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AB32" t="n">
-        <v>3.04</v>
+        <v>2.94</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.84</v>
+        <v>1.65</v>
       </c>
       <c r="AE32" t="n">
         <v>2.15</v>

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.7</v>
+        <v>1.42</v>
       </c>
       <c r="M11" t="n">
-        <v>3.95</v>
+        <v>4.45</v>
       </c>
       <c r="N11" t="n">
-        <v>1.63</v>
+        <v>5.2</v>
       </c>
       <c r="O11" t="n">
-        <v>6.58</v>
+        <v>1.8</v>
       </c>
       <c r="P11" t="n">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.88</v>
+        <v>5.75</v>
       </c>
       <c r="R11" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="T11" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="U11" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="V11" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.05</v>
+        <v>4.75</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.08</v>
+        <v>2.34</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.86</v>
+        <v>2.03</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46019.40972222222</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.42</v>
+        <v>4.7</v>
       </c>
       <c r="M12" t="n">
-        <v>4.45</v>
+        <v>3.95</v>
       </c>
       <c r="N12" t="n">
-        <v>5.2</v>
+        <v>1.63</v>
       </c>
       <c r="O12" t="n">
-        <v>1.8</v>
+        <v>6.58</v>
       </c>
       <c r="P12" t="n">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.75</v>
+        <v>1.88</v>
       </c>
       <c r="R12" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S12" t="n">
-        <v>3.28</v>
+        <v>3.12</v>
       </c>
       <c r="T12" t="n">
-        <v>2.28</v>
+        <v>2.41</v>
       </c>
       <c r="U12" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="V12" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
         <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.75</v>
+        <v>4.05</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.34</v>
+        <v>2.08</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.03</v>
+        <v>1.86</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.6</v>
+        <v>1.04</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46019.40972222222</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N13" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="O13" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.03</v>
+        <v>2.41</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46019.41666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.77</v>
+        <v>2.15</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.41</v>
+        <v>2.03</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46019.41666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.65</v>
+        <v>4.05</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>2.75</v>
+        <v>1.77</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="P15" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>2.66</v>
       </c>
       <c r="R15" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="T15" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U15" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="V15" t="n">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.7</v>
+        <v>3.08</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="AB15" t="n">
         <v>1.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.4</v>
+        <v>3.84</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.6</v>
+        <v>2.65</v>
       </c>
       <c r="M16" t="n">
-        <v>3.77</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>1.6</v>
+        <v>2.75</v>
       </c>
       <c r="O16" t="n">
-        <v>4.94</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V16" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA16" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V16" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.13</v>
+        <v>1.44</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.05</v>
+        <v>5.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>3.77</v>
       </c>
       <c r="N17" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="O17" t="n">
-        <v>3.7</v>
+        <v>4.94</v>
       </c>
       <c r="P17" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.66</v>
+        <v>2.1</v>
       </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S17" t="n">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="T17" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="U17" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="V17" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.08</v>
+        <v>3.32</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.84</v>
+        <v>3.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="O18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R18" t="n">
         <v>1.26</v>
       </c>
-      <c r="M18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.93</v>
+        <v>2.26</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.77</v>
+        <v>1.59</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46019.47916666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.2</v>
+        <v>1.26</v>
       </c>
       <c r="M19" t="n">
-        <v>3.55</v>
+        <v>5.1</v>
       </c>
       <c r="N19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
         <v>1.93</v>
       </c>
-      <c r="O19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V19" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>5.04</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.26</v>
-      </c>
       <c r="AD19" t="n">
-        <v>1.59</v>
+        <v>1.77</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46019.47916666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="O20" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="P20" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.57</v>
+        <v>3.06</v>
       </c>
       <c r="R20" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="S20" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="T20" t="n">
-        <v>2.9</v>
+        <v>3.48</v>
       </c>
       <c r="U20" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="V20" t="n">
-        <v>8.1</v>
+        <v>9.9</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.03</v>
+        <v>2.54</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.2</v>
+        <v>4.55</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46019.52083333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="M21" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="O21" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="P21" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.06</v>
+        <v>2.57</v>
       </c>
       <c r="R21" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="S21" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="T21" t="n">
-        <v>3.48</v>
+        <v>2.9</v>
       </c>
       <c r="U21" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="V21" t="n">
-        <v>9.9</v>
+        <v>8.1</v>
       </c>
       <c r="W21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X21" t="n">
         <v>1.03</v>
       </c>
-      <c r="X21" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y21" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.54</v>
+        <v>3.03</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.55</v>
+        <v>4.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46019.52083333334</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="M24" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>1.92</v>
+        <v>3.45</v>
       </c>
       <c r="O24" t="n">
-        <v>3.55</v>
+        <v>2.75</v>
       </c>
       <c r="P24" t="n">
-        <v>2.66</v>
+        <v>2.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.23</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>1.15</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>2.72</v>
       </c>
       <c r="T24" t="n">
-        <v>1.78</v>
+        <v>2.88</v>
       </c>
       <c r="U24" t="n">
-        <v>1.94</v>
+        <v>1.38</v>
       </c>
       <c r="V24" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z24" t="n">
         <v>3.3</v>
       </c>
-      <c r="W24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>7.5</v>
-      </c>
       <c r="AA24" t="n">
-        <v>1.26</v>
+        <v>1.97</v>
       </c>
       <c r="AB24" t="n">
-        <v>3.48</v>
+        <v>1.83</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.82</v>
+        <v>3.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.88</v>
+        <v>1.28</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="AF24" t="n">
-        <v>3.51</v>
+        <v>2.1</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46019.5625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="N25" t="n">
-        <v>3.45</v>
+        <v>1.92</v>
       </c>
       <c r="O25" t="n">
-        <v>2.75</v>
+        <v>3.55</v>
       </c>
       <c r="P25" t="n">
-        <v>2.15</v>
+        <v>2.66</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>2.23</v>
       </c>
       <c r="R25" t="n">
-        <v>1.42</v>
+        <v>1.15</v>
       </c>
       <c r="S25" t="n">
-        <v>2.72</v>
+        <v>5</v>
       </c>
       <c r="T25" t="n">
-        <v>2.88</v>
+        <v>1.78</v>
       </c>
       <c r="U25" t="n">
-        <v>1.38</v>
+        <v>1.94</v>
       </c>
       <c r="V25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z25" t="n">
         <v>7.5</v>
       </c>
-      <c r="W25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AA25" t="n">
-        <v>1.97</v>
+        <v>1.26</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.83</v>
+        <v>3.48</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.3</v>
+        <v>1.82</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.28</v>
+        <v>1.88</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.1</v>
+        <v>3.51</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46019.5625</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G31" t="n">

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -659,34 +659,34 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="M2" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N2" t="n">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="O2" t="n">
-        <v>2.51</v>
+        <v>2.8</v>
       </c>
       <c r="P2" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.87</v>
+        <v>3.92</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
         <v>2.75</v>
       </c>
       <c r="T2" t="n">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="U2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V2" t="n">
         <v>7.2</v>
@@ -698,34 +698,34 @@
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AA2" t="n">
         <v>1.95</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC2" t="n">
         <v>3.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46019.14583333334</v>
@@ -787,40 +787,40 @@
         <v>6.2</v>
       </c>
       <c r="O3" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="P3" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S3" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="T3" t="n">
-        <v>2.74</v>
+        <v>2.45</v>
       </c>
       <c r="U3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="V3" t="n">
-        <v>6.45</v>
+        <v>6.25</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X3" t="n">
         <v>1.05</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.62</v>
+        <v>3.75</v>
       </c>
       <c r="AA3" t="n">
         <v>1.58</v>
@@ -829,10 +829,10 @@
         <v>2.25</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE3" t="n">
         <v>1.81</v>
@@ -841,10 +841,10 @@
         <v>1.9</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46019.20833333334</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N4" t="n">
-        <v>4.2</v>
+        <v>4.55</v>
       </c>
       <c r="O4" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="P4" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.55</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="T4" t="n">
-        <v>2.87</v>
+        <v>2.67</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V4" t="n">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG4" t="n">
         <v>1.25</v>
       </c>
-      <c r="Z4" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AH4" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46019.22916666666</v>
@@ -1016,34 +1016,34 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="O5" t="n">
         <v>5.8</v>
-      </c>
-      <c r="M5" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="O5" t="n">
-        <v>6.21</v>
       </c>
       <c r="P5" t="n">
         <v>2.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="T5" t="n">
-        <v>2.58</v>
+        <v>2.47</v>
       </c>
       <c r="U5" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="V5" t="n">
         <v>6</v>
@@ -1055,31 +1055,31 @@
         <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.15</v>
+        <v>2.65</v>
       </c>
       <c r="AH5" t="n">
         <v>1.06</v>
@@ -1135,22 +1135,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="M6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="N6" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="O6" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="P6" t="n">
-        <v>2.59</v>
+        <v>2.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.86</v>
+        <v>7.5</v>
       </c>
       <c r="R6" t="n">
         <v>1.3</v>
@@ -1159,13 +1159,13 @@
         <v>3.08</v>
       </c>
       <c r="T6" t="n">
-        <v>2.57</v>
+        <v>2.41</v>
       </c>
       <c r="U6" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="V6" t="n">
-        <v>5.55</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
         <v>1.08</v>
@@ -1177,10 +1177,10 @@
         <v>1.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.02</v>
+        <v>4.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AB6" t="n">
         <v>2.15</v>
@@ -1189,16 +1189,16 @@
         <v>2.52</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AE6" t="n">
         <v>1.84</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AH6" t="n">
         <v>2.68</v>
@@ -1263,7 +1263,7 @@
         <v>4.3</v>
       </c>
       <c r="O7" t="n">
-        <v>2.41</v>
+        <v>2.33</v>
       </c>
       <c r="P7" t="n">
         <v>2.07</v>
@@ -1272,19 +1272,19 @@
         <v>4.97</v>
       </c>
       <c r="R7" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S7" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>2.55</v>
+        <v>2.94</v>
       </c>
       <c r="U7" t="n">
         <v>1.37</v>
       </c>
       <c r="V7" t="n">
-        <v>6.9</v>
+        <v>6.95</v>
       </c>
       <c r="W7" t="n">
         <v>1.04</v>
@@ -1293,10 +1293,10 @@
         <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AA7" t="n">
         <v>1.9</v>
@@ -1305,7 +1305,7 @@
         <v>1.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="AD7" t="n">
         <v>1.28</v>
@@ -1320,7 +1320,7 @@
         <v>1.27</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46019.33333333334</v>
@@ -1382,40 +1382,40 @@
         <v>8.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="P8" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="T8" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="U8" t="n">
         <v>1.42</v>
       </c>
       <c r="V8" t="n">
-        <v>6.8</v>
+        <v>6.75</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AA8" t="n">
         <v>1.79</v>
@@ -1427,7 +1427,7 @@
         <v>3.15</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE8" t="n">
         <v>2.1</v>
@@ -1439,7 +1439,7 @@
         <v>1.2</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.9</v>
+        <v>3.21</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46019.35416666666</v>
@@ -1492,7 +1492,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="M9" t="n">
         <v>3.2</v>
@@ -1501,16 +1501,16 @@
         <v>3.4</v>
       </c>
       <c r="O9" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="P9" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.45</v>
+        <v>4.54</v>
       </c>
       <c r="R9" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
         <v>2.53</v>
@@ -1522,7 +1522,7 @@
         <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="W9" t="n">
         <v>1.04</v>
@@ -1537,28 +1537,28 @@
         <v>2.97</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC9" t="n">
         <v>3.34</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46019.375</v>
@@ -1620,40 +1620,40 @@
         <v>26</v>
       </c>
       <c r="O10" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="P10" t="n">
-        <v>2.97</v>
+        <v>3.35</v>
       </c>
       <c r="Q10" t="n">
-        <v>14.4</v>
+        <v>10.5</v>
       </c>
       <c r="R10" t="n">
         <v>1.17</v>
       </c>
       <c r="S10" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="T10" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U10" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="V10" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="W10" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.25</v>
+        <v>6.55</v>
       </c>
       <c r="AA10" t="n">
         <v>1.28</v>
@@ -1668,16 +1668,16 @@
         <v>2.02</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.17</v>
+        <v>1.92</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AH10" t="n">
-        <v>5.7</v>
+        <v>4.95</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46019.38541666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,22 +1730,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.42</v>
+        <v>4.7</v>
       </c>
       <c r="M11" t="n">
-        <v>4.45</v>
+        <v>3.95</v>
       </c>
       <c r="N11" t="n">
-        <v>5.2</v>
+        <v>1.63</v>
       </c>
       <c r="O11" t="n">
-        <v>1.8</v>
+        <v>6.6</v>
       </c>
       <c r="P11" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.75</v>
+        <v>1.81</v>
       </c>
       <c r="R11" t="n">
         <v>1.25</v>
@@ -1754,49 +1754,49 @@
         <v>3.28</v>
       </c>
       <c r="T11" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="U11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.55</v>
       </c>
-      <c r="V11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X11" t="n">
+      <c r="AE11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>2.6</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46019.40972222222</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.7</v>
+        <v>1.43</v>
       </c>
       <c r="M12" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>1.63</v>
+        <v>5.25</v>
       </c>
       <c r="O12" t="n">
-        <v>6.58</v>
+        <v>1.96</v>
       </c>
       <c r="P12" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.88</v>
+        <v>5.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>3.12</v>
+        <v>3.34</v>
       </c>
       <c r="T12" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="U12" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="V12" t="n">
-        <v>5.6</v>
+        <v>5.15</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
         <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.05</v>
+        <v>4.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.08</v>
+        <v>2.37</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.04</v>
+        <v>2.47</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46019.40972222222</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.77</v>
+        <v>2.11</v>
       </c>
       <c r="M13" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>4.5</v>
+        <v>3.15</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.41</v>
+        <v>2.03</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46019.41666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="N14" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="O14" t="n">
-        <v>2.85</v>
+        <v>2.57</v>
       </c>
       <c r="P14" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.9</v>
+        <v>5.91</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="S14" t="n">
-        <v>2.59</v>
+        <v>2.21</v>
       </c>
       <c r="T14" t="n">
-        <v>3.07</v>
+        <v>3.8</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="V14" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.37</v>
+        <v>1.72</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.04</v>
+        <v>2</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.03</v>
+        <v>2.41</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.63</v>
+        <v>4.9</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.79</v>
+        <v>2.37</v>
       </c>
       <c r="AF14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH14" t="n">
         <v>1.9</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46019.41666666666</v>
@@ -2215,22 +2215,22 @@
         <v>1.77</v>
       </c>
       <c r="O15" t="n">
-        <v>3.7</v>
+        <v>4.35</v>
       </c>
       <c r="P15" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
         <v>2.66</v>
       </c>
       <c r="T15" t="n">
-        <v>2.88</v>
+        <v>3.23</v>
       </c>
       <c r="U15" t="n">
         <v>1.34</v>
@@ -2242,7 +2242,7 @@
         <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="Y15" t="n">
         <v>1.36</v>
@@ -2257,10 +2257,10 @@
         <v>1.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.84</v>
+        <v>4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AE15" t="n">
         <v>1.8</v>
@@ -2269,10 +2269,10 @@
         <v>1.9</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2334,31 +2334,31 @@
         <v>2.75</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>3.46</v>
       </c>
       <c r="P16" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.4</v>
+        <v>3.21</v>
       </c>
       <c r="R16" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="T16" t="n">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="U16" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
         <v>1.08</v>
@@ -2376,22 +2376,22 @@
         <v>1.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="AD16" t="n">
         <v>1.18</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2453,40 +2453,40 @@
         <v>1.6</v>
       </c>
       <c r="O17" t="n">
-        <v>4.94</v>
+        <v>6.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="R17" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>2.84</v>
+        <v>2.68</v>
       </c>
       <c r="T17" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="U17" t="n">
         <v>1.37</v>
       </c>
       <c r="V17" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W17" t="n">
         <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="AA17" t="n">
         <v>2.05</v>
@@ -2495,19 +2495,19 @@
         <v>1.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="AD17" t="n">
         <v>1.28</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH17" t="n">
         <v>1.13</v>
@@ -2572,28 +2572,28 @@
         <v>1.93</v>
       </c>
       <c r="O18" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="T18" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="U18" t="n">
         <v>1.56</v>
       </c>
       <c r="V18" t="n">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="W18" t="n">
         <v>1.11</v>
@@ -2605,7 +2605,7 @@
         <v>1.13</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.04</v>
+        <v>4.5</v>
       </c>
       <c r="AA18" t="n">
         <v>1.57</v>
@@ -2617,19 +2617,19 @@
         <v>2.26</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AF18" t="n">
         <v>2.38</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46019.47916666666</v>
@@ -2810,37 +2810,37 @@
         <v>2.35</v>
       </c>
       <c r="O20" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="P20" t="n">
-        <v>1.87</v>
+        <v>2.03</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.06</v>
+        <v>3.32</v>
       </c>
       <c r="R20" t="n">
         <v>1.55</v>
       </c>
       <c r="S20" t="n">
-        <v>2.52</v>
+        <v>2.34</v>
       </c>
       <c r="T20" t="n">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="V20" t="n">
-        <v>9.9</v>
+        <v>8</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X20" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="Z20" t="n">
         <v>2.54</v>
@@ -2855,19 +2855,19 @@
         <v>4.55</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46019.52083333334</v>
@@ -2929,28 +2929,28 @@
         <v>1.97</v>
       </c>
       <c r="O21" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="P21" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
         <v>2.53</v>
       </c>
       <c r="T21" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="U21" t="n">
         <v>1.31</v>
       </c>
       <c r="V21" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="W21" t="n">
         <v>1.02</v>
@@ -2959,10 +2959,10 @@
         <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.03</v>
+        <v>2.95</v>
       </c>
       <c r="AA21" t="n">
         <v>2.15</v>
@@ -2977,7 +2977,7 @@
         <v>1.22</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="AF21" t="n">
         <v>1.78</v>
@@ -2986,7 +2986,7 @@
         <v>1.34</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46019.52083333334</v>
@@ -3048,10 +3048,10 @@
         <v>1.77</v>
       </c>
       <c r="O22" t="n">
-        <v>4.57</v>
+        <v>4</v>
       </c>
       <c r="P22" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="Q22" t="n">
         <v>2.3</v>
@@ -3069,10 +3069,10 @@
         <v>1.46</v>
       </c>
       <c r="V22" t="n">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="W22" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
         <v>1.03</v>
@@ -3090,16 +3090,16 @@
         <v>2.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="AD22" t="n">
         <v>1.39</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AG22" t="n">
         <v>1.2</v>
@@ -3158,22 +3158,22 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="M23" t="n">
-        <v>3.55</v>
+        <v>3.62</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="O23" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="P23" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.52</v>
+        <v>4.31</v>
       </c>
       <c r="R23" t="n">
         <v>1.32</v>
@@ -3182,49 +3182,49 @@
         <v>2.96</v>
       </c>
       <c r="T23" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="U23" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="V23" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="W23" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AC23" t="n">
         <v>3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46019.54166666666</v>
@@ -3286,28 +3286,28 @@
         <v>3.45</v>
       </c>
       <c r="O24" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="P24" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="R24" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S24" t="n">
-        <v>2.72</v>
+        <v>3.05</v>
       </c>
       <c r="T24" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U24" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V24" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="W24" t="n">
         <v>1.04</v>
@@ -3319,7 +3319,7 @@
         <v>1.28</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AA24" t="n">
         <v>1.97</v>
@@ -3328,19 +3328,19 @@
         <v>1.83</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="AD24" t="n">
         <v>1.28</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AF24" t="n">
         <v>2.1</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH24" t="n">
         <v>1.65</v>
@@ -3405,40 +3405,40 @@
         <v>1.92</v>
       </c>
       <c r="O25" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="P25" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="R25" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>4.85</v>
       </c>
       <c r="T25" t="n">
         <v>1.78</v>
       </c>
       <c r="U25" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="V25" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="W25" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
         <v>1.01</v>
       </c>
       <c r="Z25" t="n">
-        <v>7.5</v>
+        <v>8.4</v>
       </c>
       <c r="AA25" t="n">
         <v>1.26</v>
@@ -3459,7 +3459,7 @@
         <v>3.51</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AH25" t="n">
         <v>1.25</v>
@@ -3524,40 +3524,40 @@
         <v>4.7</v>
       </c>
       <c r="O26" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="P26" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S26" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="T26" t="n">
-        <v>2.96</v>
+        <v>3.08</v>
       </c>
       <c r="U26" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="V26" t="n">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="W26" t="n">
         <v>1.06</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y26" t="n">
         <v>1.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="AA26" t="n">
         <v>1.98</v>
@@ -3578,10 +3578,10 @@
         <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46019.58333333334</v>
@@ -3643,37 +3643,37 @@
         <v>2.25</v>
       </c>
       <c r="O27" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="P27" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="R27" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="T27" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="U27" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V27" t="n">
         <v>8</v>
       </c>
       <c r="W27" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X27" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z27" t="n">
         <v>3</v>
@@ -3685,22 +3685,22 @@
         <v>1.55</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.54</v>
+        <v>3.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46019.625</v>
@@ -3762,40 +3762,40 @@
         <v>2.12</v>
       </c>
       <c r="O28" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P28" t="n">
         <v>2.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="R28" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="S28" t="n">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
       <c r="T28" t="n">
         <v>2.59</v>
       </c>
       <c r="U28" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="V28" t="n">
-        <v>6.4</v>
+        <v>6.35</v>
       </c>
       <c r="W28" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X28" t="n">
         <v>1.04</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.9</v>
+        <v>4.35</v>
       </c>
       <c r="AA28" t="n">
         <v>1.78</v>
@@ -3804,10 +3804,10 @@
         <v>2.03</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE28" t="n">
         <v>1.62</v>
@@ -3816,10 +3816,10 @@
         <v>2.2</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46019.69791666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,22 +3872,22 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>8.01</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,22 +3991,22 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,22 +4110,22 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -4149,16 +4149,16 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -4238,19 +4238,19 @@
         <v>19</v>
       </c>
       <c r="O32" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="P32" t="n">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="Q32" t="n">
-        <v>10.7</v>
+        <v>13.2</v>
       </c>
       <c r="R32" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S32" t="n">
-        <v>3.85</v>
+        <v>3.88</v>
       </c>
       <c r="T32" t="n">
         <v>2.04</v>
@@ -4292,10 +4292,10 @@
         <v>1.63</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AH32" t="n">
-        <v>6.15</v>
+        <v>6.2</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46019.72916666666</v>
@@ -4357,40 +4357,40 @@
         <v>1.35</v>
       </c>
       <c r="O33" t="n">
-        <v>6.62</v>
+        <v>4.5</v>
       </c>
       <c r="P33" t="n">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="R33" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="S33" t="n">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="T33" t="n">
-        <v>2.24</v>
+        <v>2.5</v>
       </c>
       <c r="U33" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="V33" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="W33" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="X33" t="n">
         <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="Z33" t="n">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="AA33" t="n">
         <v>1.55</v>
@@ -4405,16 +4405,16 @@
         <v>1.57</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="AG33" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH33" t="n">
         <v>1.12</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.04</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46019.75</v>
@@ -4476,34 +4476,34 @@
         <v>4.2</v>
       </c>
       <c r="O34" t="n">
-        <v>2.21</v>
+        <v>2</v>
       </c>
       <c r="P34" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="Q34" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="R34" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="S34" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="T34" t="n">
         <v>2.79</v>
       </c>
       <c r="U34" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="V34" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="W34" t="n">
         <v>1.07</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y34" t="n">
         <v>1.25</v>
@@ -4518,22 +4518,22 @@
         <v>1.8</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.83</v>
+        <v>2.03</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.03</v>
+        <v>2.49</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46019.85416666666</v>

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>6.18</v>
+        <v>1.39</v>
       </c>
       <c r="M5" t="n">
-        <v>4.05</v>
+        <v>4.4</v>
       </c>
       <c r="N5" t="n">
-        <v>1.49</v>
+        <v>7</v>
       </c>
       <c r="O5" t="n">
-        <v>5.8</v>
+        <v>1.85</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>7.5</v>
       </c>
       <c r="R5" t="n">
         <v>1.3</v>
@@ -1040,49 +1040,49 @@
         <v>3.08</v>
       </c>
       <c r="T5" t="n">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="U5" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="V5" t="n">
         <v>6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
         <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.65</v>
+        <v>1.14</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.06</v>
+        <v>2.68</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46019.3125</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,22 +1135,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.39</v>
+        <v>6.18</v>
       </c>
       <c r="M6" t="n">
-        <v>4.4</v>
+        <v>4.05</v>
       </c>
       <c r="N6" t="n">
-        <v>7</v>
+        <v>1.49</v>
       </c>
       <c r="O6" t="n">
-        <v>1.85</v>
+        <v>5.8</v>
       </c>
       <c r="P6" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.5</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
         <v>1.3</v>
@@ -1159,49 +1159,49 @@
         <v>3.08</v>
       </c>
       <c r="T6" t="n">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="U6" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="V6" t="n">
         <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="Z6" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.14</v>
+        <v>2.65</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.68</v>
+        <v>1.06</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46019.3125</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.7</v>
+        <v>1.43</v>
       </c>
       <c r="M11" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="N11" t="n">
-        <v>1.63</v>
+        <v>5.25</v>
       </c>
       <c r="O11" t="n">
-        <v>6.6</v>
+        <v>1.96</v>
       </c>
       <c r="P11" t="n">
-        <v>2.65</v>
+        <v>2.36</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.81</v>
+        <v>5.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="T11" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="U11" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="V11" t="n">
-        <v>5</v>
+        <v>5.15</v>
       </c>
       <c r="W11" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z11" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.08</v>
+        <v>2.37</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.02</v>
+        <v>2.47</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46019.40972222222</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.43</v>
+        <v>4.7</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="N12" t="n">
-        <v>5.25</v>
+        <v>1.63</v>
       </c>
       <c r="O12" t="n">
-        <v>1.96</v>
+        <v>6.6</v>
       </c>
       <c r="P12" t="n">
-        <v>2.36</v>
+        <v>2.65</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.5</v>
+        <v>1.81</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="T12" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="U12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V12" t="n">
+        <v>5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.55</v>
       </c>
-      <c r="V12" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X12" t="n">
+      <c r="AE12" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.02</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>2.47</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46019.40972222222</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="N13" t="n">
-        <v>3.15</v>
+        <v>4.8</v>
       </c>
       <c r="O13" t="n">
-        <v>2.95</v>
+        <v>2.57</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.6</v>
+        <v>5.91</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="S13" t="n">
-        <v>2.59</v>
+        <v>2.21</v>
       </c>
       <c r="T13" t="n">
-        <v>2.96</v>
+        <v>3.8</v>
       </c>
       <c r="U13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V13" t="n">
+        <v>12</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.32</v>
       </c>
-      <c r="V13" t="n">
-        <v>8</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF13" t="n">
+      <c r="AH13" t="n">
         <v>1.9</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.53</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46019.41666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V14" t="n">
+        <v>8</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AF14" t="n">
         <v>1.9</v>
       </c>
-      <c r="M14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N14" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>5.91</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V14" t="n">
-        <v>12</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AF14" t="n">
+      <c r="AG14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH14" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.9</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46019.41666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.05</v>
+        <v>5.6</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>3.77</v>
       </c>
       <c r="N15" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="O15" t="n">
-        <v>4.35</v>
+        <v>6.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.6</v>
+        <v>2.16</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T15" t="n">
-        <v>3.23</v>
+        <v>2.8</v>
       </c>
       <c r="U15" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="V15" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.08</v>
+        <v>3.31</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="AG15" t="n">
         <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5.6</v>
+        <v>4.05</v>
       </c>
       <c r="M17" t="n">
-        <v>3.77</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="O17" t="n">
-        <v>6.2</v>
+        <v>4.35</v>
       </c>
       <c r="P17" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.16</v>
+        <v>2.6</v>
       </c>
       <c r="R17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="n">
         <v>1.36</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V17" t="n">
-        <v>7</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.32</v>
-      </c>
       <c r="Z17" t="n">
-        <v>3.31</v>
+        <v>3.08</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.69</v>
+        <v>1.9</v>
       </c>
       <c r="AG17" t="n">
         <v>1.28</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.2</v>
+        <v>1.26</v>
       </c>
       <c r="M18" t="n">
-        <v>3.55</v>
+        <v>5.1</v>
       </c>
       <c r="N18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
         <v>1.93</v>
       </c>
-      <c r="O18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V18" t="n">
-        <v>5</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.26</v>
-      </c>
       <c r="AD18" t="n">
-        <v>1.51</v>
+        <v>1.77</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46019.47916666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.26</v>
+        <v>3.2</v>
       </c>
       <c r="M19" t="n">
-        <v>5.1</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>6.8</v>
+        <v>1.93</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.93</v>
+        <v>2.26</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.77</v>
+        <v>1.51</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46019.47916666666</v>

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -642,20 +642,20 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -761,20 +761,20 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -880,20 +880,20 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M5" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="N5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="O5" t="n">
         <v>1.85</v>
@@ -1031,7 +1031,7 @@
         <v>2.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="R5" t="n">
         <v>1.3</v>
@@ -1040,34 +1040,34 @@
         <v>3.08</v>
       </c>
       <c r="T5" t="n">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="U5" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="V5" t="n">
         <v>6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z5" t="n">
         <v>4.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="AD5" t="n">
         <v>1.43</v>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>6.18</v>
+        <v>6.5</v>
       </c>
       <c r="M6" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="O6" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="T6" t="n">
-        <v>2.47</v>
+        <v>2.59</v>
       </c>
       <c r="U6" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="V6" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z6" t="n">
         <v>3.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AF6" t="n">
         <v>1.91</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46019.3125</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O9" t="n">
         <v>2.5</v>
@@ -1507,58 +1507,58 @@
         <v>2.02</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.54</v>
+        <v>4.62</v>
       </c>
       <c r="R9" t="n">
         <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="T9" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="U9" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="W9" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
         <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AB9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.71</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.75</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46019.375</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.43</v>
+        <v>4.7</v>
       </c>
       <c r="M11" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="N11" t="n">
-        <v>5.25</v>
+        <v>1.63</v>
       </c>
       <c r="O11" t="n">
-        <v>1.96</v>
+        <v>6.6</v>
       </c>
       <c r="P11" t="n">
-        <v>2.36</v>
+        <v>2.65</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.5</v>
+        <v>1.81</v>
       </c>
       <c r="R11" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="T11" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="U11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.55</v>
       </c>
-      <c r="V11" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X11" t="n">
+      <c r="AE11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>2.47</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46019.40972222222</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>4.7</v>
+        <v>1.43</v>
       </c>
       <c r="M12" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>1.63</v>
+        <v>5.25</v>
       </c>
       <c r="O12" t="n">
-        <v>6.6</v>
+        <v>1.96</v>
       </c>
       <c r="P12" t="n">
-        <v>2.65</v>
+        <v>2.36</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.81</v>
+        <v>5.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="T12" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="V12" t="n">
-        <v>5</v>
+        <v>5.15</v>
       </c>
       <c r="W12" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="Z12" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.08</v>
+        <v>2.37</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.02</v>
+        <v>2.47</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46019.40972222222</v>
@@ -2087,19 +2087,19 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="M14" t="n">
         <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3.15</v>
+        <v>3.08</v>
       </c>
       <c r="O14" t="n">
         <v>2.95</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
         <v>3.6</v>
@@ -2138,13 +2138,13 @@
         <v>1.75</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="AD14" t="n">
         <v>1.21</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AF14" t="n">
         <v>1.9</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.6</v>
+        <v>4.05</v>
       </c>
       <c r="M15" t="n">
-        <v>3.77</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="O15" t="n">
-        <v>6.2</v>
+        <v>4.35</v>
       </c>
       <c r="P15" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.16</v>
+        <v>2.6</v>
       </c>
       <c r="R15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="n">
         <v>1.36</v>
       </c>
-      <c r="S15" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V15" t="n">
-        <v>7</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.32</v>
-      </c>
       <c r="Z15" t="n">
-        <v>3.31</v>
+        <v>3.08</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.69</v>
+        <v>1.9</v>
       </c>
       <c r="AG15" t="n">
         <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.65</v>
+        <v>5.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>3.77</v>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>1.6</v>
       </c>
       <c r="O16" t="n">
-        <v>3.46</v>
+        <v>6.2</v>
       </c>
       <c r="P16" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.21</v>
+        <v>2.16</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="T16" t="n">
-        <v>3.42</v>
+        <v>2.8</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="V16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.7</v>
+        <v>3.31</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.49</v>
+        <v>1.13</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>4.05</v>
+        <v>2.65</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N17" t="n">
-        <v>1.77</v>
+        <v>2.75</v>
       </c>
       <c r="O17" t="n">
-        <v>4.35</v>
+        <v>3.46</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.6</v>
+        <v>3.21</v>
       </c>
       <c r="R17" t="n">
         <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.66</v>
+        <v>2.55</v>
       </c>
       <c r="T17" t="n">
-        <v>3.23</v>
+        <v>3.42</v>
       </c>
       <c r="U17" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="V17" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.08</v>
+        <v>2.7</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AB17" t="n">
         <v>1.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AE17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF17" t="n">
         <v>1.8</v>
       </c>
-      <c r="AF17" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AG17" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.26</v>
+        <v>3.2</v>
       </c>
       <c r="M18" t="n">
-        <v>5.1</v>
+        <v>3.55</v>
       </c>
       <c r="N18" t="n">
-        <v>6.8</v>
+        <v>1.93</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.93</v>
+        <v>2.26</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.77</v>
+        <v>1.51</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46019.47916666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.2</v>
+        <v>1.26</v>
       </c>
       <c r="M19" t="n">
-        <v>3.55</v>
+        <v>5.1</v>
       </c>
       <c r="N19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
         <v>1.93</v>
       </c>
-      <c r="O19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V19" t="n">
-        <v>5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.26</v>
-      </c>
       <c r="AD19" t="n">
-        <v>1.51</v>
+        <v>1.77</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46019.47916666666</v>
@@ -3161,7 +3161,7 @@
         <v>1.85</v>
       </c>
       <c r="M23" t="n">
-        <v>3.62</v>
+        <v>3.87</v>
       </c>
       <c r="N23" t="n">
         <v>3.62</v>
@@ -3170,37 +3170,37 @@
         <v>2.5</v>
       </c>
       <c r="P23" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="Q23" t="n">
         <v>4.31</v>
       </c>
       <c r="R23" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S23" t="n">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="T23" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="U23" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="V23" t="n">
-        <v>6.3</v>
+        <v>6.25</v>
       </c>
       <c r="W23" t="n">
         <v>1.06</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
         <v>1.24</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.82</v>
+        <v>3.85</v>
       </c>
       <c r="AA23" t="n">
         <v>1.78</v>
@@ -3212,19 +3212,19 @@
         <v>3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AE23" t="n">
         <v>1.62</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46019.54166666666</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,22 +3872,22 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>8.800000000000001</v>
+        <v>1.57</v>
       </c>
       <c r="M29" t="n">
-        <v>8.01</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>1.14</v>
+        <v>5.8</v>
       </c>
       <c r="O29" t="n">
-        <v>4.5</v>
+        <v>2.25</v>
       </c>
       <c r="P29" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -3911,16 +3911,16 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,22 +4110,22 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.57</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M31" t="n">
-        <v>3.3</v>
+        <v>8.01</v>
       </c>
       <c r="N31" t="n">
-        <v>5.8</v>
+        <v>1.14</v>
       </c>
       <c r="O31" t="n">
-        <v>2.25</v>
+        <v>4.5</v>
       </c>
       <c r="P31" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q31" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -4149,16 +4149,16 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -990,99 +990,99 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.4</v>
+        <v>6.5</v>
       </c>
       <c r="M5" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>7.2</v>
+        <v>1.48</v>
       </c>
       <c r="O5" t="n">
-        <v>1.85</v>
+        <v>5</v>
       </c>
       <c r="P5" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V5" t="n">
         <v>6.5</v>
       </c>
-      <c r="R5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V5" t="n">
-        <v>6</v>
-      </c>
       <c r="W5" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.59</v>
+        <v>3</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.14</v>
+        <v>2.55</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.68</v>
+        <v>1.08</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46019.3125</v>
@@ -1109,99 +1109,99 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="N6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q6" t="n">
         <v>6.5</v>
       </c>
-      <c r="M6" t="n">
-        <v>4</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="O6" t="n">
-        <v>5</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.03</v>
-      </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>2.96</v>
+        <v>3.08</v>
       </c>
       <c r="T6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V6" t="n">
+        <v>6</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC6" t="n">
         <v>2.59</v>
       </c>
-      <c r="U6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3</v>
-      </c>
       <c r="AD6" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.55</v>
+        <v>1.14</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.08</v>
+        <v>2.68</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46019.3125</v>
@@ -1237,72 +1237,72 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O7" t="n">
         <v>2.33</v>
       </c>
       <c r="P7" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.97</v>
+        <v>5.02</v>
       </c>
       <c r="R7" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="T7" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="U7" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="V7" t="n">
-        <v>6.95</v>
+        <v>6.75</v>
       </c>
       <c r="W7" t="n">
         <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AC7" t="n">
         <v>3.1</v>
@@ -1311,10 +1311,10 @@
         <v>1.28</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AG7" t="n">
         <v>1.27</v>
@@ -1356,90 +1356,90 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="M8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="N8" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="O8" t="n">
         <v>1.85</v>
       </c>
       <c r="P8" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="Q8" t="n">
         <v>7.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="T8" t="n">
-        <v>2.81</v>
+        <v>2.87</v>
       </c>
       <c r="U8" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="V8" t="n">
-        <v>6.75</v>
+        <v>7.2</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AE8" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46019.35416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.7</v>
+        <v>1.37</v>
       </c>
       <c r="M11" t="n">
-        <v>3.95</v>
+        <v>4.55</v>
       </c>
       <c r="N11" t="n">
-        <v>1.63</v>
+        <v>5.4</v>
       </c>
       <c r="O11" t="n">
-        <v>6.6</v>
+        <v>2.04</v>
       </c>
       <c r="P11" t="n">
-        <v>2.65</v>
+        <v>2.34</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.81</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S11" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="T11" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="U11" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="V11" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z11" t="n">
-        <v>5</v>
+        <v>4.85</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.08</v>
+        <v>2.33</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="AD11" t="n">
         <v>1.55</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.78</v>
+        <v>1.59</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.91</v>
+        <v>2.19</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.02</v>
+        <v>2.31</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46019.40972222222</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,22 +1849,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.43</v>
+        <v>5.4</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="N12" t="n">
-        <v>5.25</v>
+        <v>1.38</v>
       </c>
       <c r="O12" t="n">
-        <v>1.96</v>
+        <v>5.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.5</v>
+        <v>2.01</v>
       </c>
       <c r="R12" t="n">
         <v>1.24</v>
@@ -1879,22 +1879,22 @@
         <v>1.55</v>
       </c>
       <c r="V12" t="n">
-        <v>5.15</v>
+        <v>5.05</v>
       </c>
       <c r="W12" t="n">
         <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="Z12" t="n">
         <v>4.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AB12" t="n">
         <v>2.37</v>
@@ -1903,19 +1903,19 @@
         <v>2.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.47</v>
+        <v>1.09</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46019.40972222222</v>
@@ -1968,43 +1968,43 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="N13" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="O13" t="n">
-        <v>2.57</v>
+        <v>2.99</v>
       </c>
       <c r="P13" t="n">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.91</v>
+        <v>5.59</v>
       </c>
       <c r="R13" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="S13" t="n">
-        <v>2.21</v>
+        <v>1.99</v>
       </c>
       <c r="T13" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="U13" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="V13" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Y13" t="n">
         <v>1.72</v>
@@ -2019,22 +2019,22 @@
         <v>1.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.9</v>
+        <v>6.65</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.37</v>
+        <v>2.54</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.9</v>
+        <v>1.59</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46019.41666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>4.05</v>
+        <v>5.6</v>
       </c>
       <c r="M15" t="n">
-        <v>3.35</v>
+        <v>3.77</v>
       </c>
       <c r="N15" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="O15" t="n">
-        <v>4.35</v>
+        <v>6.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="R15" t="n">
         <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T15" t="n">
-        <v>3.23</v>
+        <v>2.9</v>
       </c>
       <c r="U15" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="V15" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="AG15" t="n">
         <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.6</v>
+        <v>4.05</v>
       </c>
       <c r="M16" t="n">
-        <v>3.77</v>
+        <v>3.35</v>
       </c>
       <c r="N16" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="O16" t="n">
-        <v>6.2</v>
+        <v>4.34</v>
       </c>
       <c r="P16" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.16</v>
+        <v>2.62</v>
       </c>
       <c r="R16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V16" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y16" t="n">
         <v>1.36</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V16" t="n">
-        <v>7</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.32</v>
-      </c>
       <c r="Z16" t="n">
-        <v>3.31</v>
+        <v>3.04</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.65</v>
+        <v>4.03</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.07</v>
+        <v>1.82</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.69</v>
+        <v>1.88</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.2</v>
+        <v>1.32</v>
       </c>
       <c r="M18" t="n">
-        <v>3.55</v>
+        <v>4.9</v>
       </c>
       <c r="N18" t="n">
-        <v>1.93</v>
+        <v>6.8</v>
       </c>
       <c r="O18" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.26</v>
+        <v>1.98</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46019.47916666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.26</v>
+        <v>3.2</v>
       </c>
       <c r="M19" t="n">
-        <v>5.1</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>6.8</v>
+        <v>1.93</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.93</v>
+        <v>2.26</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.77</v>
+        <v>1.51</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46019.47916666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="M20" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="O20" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="P20" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.32</v>
+        <v>2.58</v>
       </c>
       <c r="R20" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="T20" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="U20" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="V20" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.54</v>
+        <v>2.95</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.55</v>
+        <v>4.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE20" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46019.52083333334</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N21" t="n">
-        <v>1.97</v>
+        <v>2.35</v>
       </c>
       <c r="O21" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.5</v>
+        <v>3.43</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="S21" t="n">
-        <v>2.53</v>
+        <v>2.39</v>
       </c>
       <c r="T21" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="U21" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="V21" t="n">
         <v>8</v>
       </c>
       <c r="W21" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46019.52083333334</v>
@@ -3048,10 +3048,10 @@
         <v>1.77</v>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P22" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="Q22" t="n">
         <v>2.3</v>
@@ -3063,13 +3063,13 @@
         <v>3.08</v>
       </c>
       <c r="T22" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="U22" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="V22" t="n">
-        <v>5.7</v>
+        <v>5.65</v>
       </c>
       <c r="W22" t="n">
         <v>1.08</v>
@@ -3081,7 +3081,7 @@
         <v>1.17</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.96</v>
+        <v>4.05</v>
       </c>
       <c r="AA22" t="n">
         <v>1.68</v>
@@ -3090,16 +3090,16 @@
         <v>2.05</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AG22" t="n">
         <v>1.2</v>
@@ -3408,37 +3408,37 @@
         <v>3.58</v>
       </c>
       <c r="P25" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="Q25" t="n">
         <v>2.22</v>
       </c>
       <c r="R25" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="S25" t="n">
-        <v>4.85</v>
+        <v>4.75</v>
       </c>
       <c r="T25" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U25" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V25" t="n">
-        <v>3.42</v>
+        <v>3.48</v>
       </c>
       <c r="W25" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Z25" t="n">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="AA25" t="n">
         <v>1.26</v>
@@ -3453,10 +3453,10 @@
         <v>1.88</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF25" t="n">
-        <v>3.51</v>
+        <v>3.55</v>
       </c>
       <c r="AG25" t="n">
         <v>1.15</v>
@@ -3524,28 +3524,28 @@
         <v>4.7</v>
       </c>
       <c r="O26" t="n">
-        <v>2.35</v>
+        <v>2.53</v>
       </c>
       <c r="P26" t="n">
         <v>2.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="T26" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="U26" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="V26" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="W26" t="n">
         <v>1.06</v>
@@ -3557,7 +3557,7 @@
         <v>1.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="AA26" t="n">
         <v>1.98</v>
@@ -3575,13 +3575,13 @@
         <v>1.85</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46019.58333333334</v>
@@ -3646,37 +3646,37 @@
         <v>3.85</v>
       </c>
       <c r="P27" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="R27" t="n">
         <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="T27" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="U27" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V27" t="n">
         <v>8</v>
       </c>
       <c r="W27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X27" t="n">
         <v>1.02</v>
       </c>
-      <c r="X27" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y27" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AA27" t="n">
         <v>2.25</v>
@@ -3685,22 +3685,22 @@
         <v>1.55</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AD27" t="n">
         <v>1.25</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AF27" t="n">
         <v>1.91</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46019.625</v>
@@ -3762,7 +3762,7 @@
         <v>2.12</v>
       </c>
       <c r="O28" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="P28" t="n">
         <v>2.3</v>
@@ -3795,7 +3795,7 @@
         <v>1.22</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.35</v>
+        <v>3.9</v>
       </c>
       <c r="AA28" t="n">
         <v>1.78</v>
@@ -3881,34 +3881,34 @@
         <v>5.8</v>
       </c>
       <c r="O29" t="n">
-        <v>2.25</v>
+        <v>2.52</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="Q29" t="n">
-        <v>6</v>
+        <v>7.08</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y29" t="n">
         <v>1.5</v>
@@ -3923,22 +3923,22 @@
         <v>1.52</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46019.70833333334</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="M30" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="N30" t="n">
+        <v>2</v>
+      </c>
+      <c r="O30" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V30" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AF30" t="n">
         <v>1.68</v>
       </c>
-      <c r="O30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46019.70833333334</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>8.800000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="M31" t="n">
-        <v>8.01</v>
+        <v>3.45</v>
       </c>
       <c r="N31" t="n">
-        <v>1.14</v>
+        <v>1.68</v>
       </c>
       <c r="O31" t="n">
-        <v>4.5</v>
+        <v>4.54</v>
       </c>
       <c r="P31" t="n">
         <v>2.05</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46019.70833333334</v>
@@ -4241,37 +4241,37 @@
         <v>1.49</v>
       </c>
       <c r="P32" t="n">
-        <v>3.08</v>
+        <v>3.26</v>
       </c>
       <c r="Q32" t="n">
-        <v>13.2</v>
+        <v>14.93</v>
       </c>
       <c r="R32" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S32" t="n">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="T32" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U32" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="V32" t="n">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="W32" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X32" t="n">
         <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AA32" t="n">
         <v>1.37</v>
@@ -4286,16 +4286,16 @@
         <v>1.65</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AG32" t="n">
         <v>1.03</v>
       </c>
       <c r="AH32" t="n">
-        <v>6.2</v>
+        <v>6.85</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46019.72916666666</v>
@@ -4357,37 +4357,37 @@
         <v>1.35</v>
       </c>
       <c r="O33" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="P33" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R33" t="n">
         <v>1.33</v>
       </c>
       <c r="S33" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="T33" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="U33" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="V33" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="W33" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z33" t="n">
         <v>3.65</v>
@@ -4405,16 +4405,16 @@
         <v>1.57</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46019.75</v>
@@ -4476,13 +4476,13 @@
         <v>4.2</v>
       </c>
       <c r="O34" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="P34" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="Q34" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="R34" t="n">
         <v>1.37</v>
@@ -4518,19 +4518,19 @@
         <v>1.8</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AH34" t="n">
         <v>2.49</v>

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -990,25 +990,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
         <v>1</v>
       </c>
-      <c r="H5" t="n">
-        <v>4</v>
-      </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="N5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q5" t="n">
         <v>6.5</v>
       </c>
-      <c r="M5" t="n">
-        <v>4</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="O5" t="n">
-        <v>5</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.03</v>
-      </c>
       <c r="R5" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>2.96</v>
+        <v>3.08</v>
       </c>
       <c r="T5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V5" t="n">
+        <v>6</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC5" t="n">
         <v>2.59</v>
       </c>
-      <c r="U5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>3</v>
-      </c>
       <c r="AD5" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.55</v>
+        <v>1.14</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.08</v>
+        <v>2.68</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46019.3125</v>
@@ -1109,99 +1109,99 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC6" t="n">
         <v>3</v>
       </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M6" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="N6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V6" t="n">
-        <v>6</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.59</v>
-      </c>
       <c r="AD6" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.14</v>
+        <v>2.55</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.68</v>
+        <v>1.08</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46019.3125</v>
@@ -1475,20 +1475,20 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1594,57 +1594,57 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="M10" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="N10" t="n">
-        <v>26</v>
+        <v>15.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P10" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.5</v>
+        <v>10.75</v>
       </c>
       <c r="R10" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="T10" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="U10" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="V10" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="X10" t="n">
         <v>1.01</v>
@@ -1653,25 +1653,25 @@
         <v>1.07</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.55</v>
+        <v>6.4</v>
       </c>
       <c r="AA10" t="n">
         <v>1.28</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG10" t="n">
         <v>1.03</v>
@@ -1704,48 +1704,48 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.37</v>
+        <v>5.4</v>
       </c>
       <c r="M11" t="n">
-        <v>4.55</v>
+        <v>4.4</v>
       </c>
       <c r="N11" t="n">
-        <v>5.4</v>
+        <v>1.38</v>
       </c>
       <c r="O11" t="n">
-        <v>2.04</v>
+        <v>5.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>2.01</v>
       </c>
       <c r="R11" t="n">
         <v>1.24</v>
@@ -1754,49 +1754,49 @@
         <v>3.34</v>
       </c>
       <c r="T11" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="U11" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="V11" t="n">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="W11" t="n">
         <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.85</v>
+        <v>4.75</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="AC11" t="n">
         <v>2.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.31</v>
+        <v>1.09</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46019.40972222222</v>
@@ -1823,48 +1823,48 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M12" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="N12" t="n">
         <v>5.4</v>
       </c>
-      <c r="M12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1.38</v>
-      </c>
       <c r="O12" t="n">
-        <v>5.2</v>
+        <v>2.04</v>
       </c>
       <c r="P12" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.01</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
         <v>1.24</v>
@@ -1873,49 +1873,49 @@
         <v>3.34</v>
       </c>
       <c r="T12" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="U12" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="V12" t="n">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="W12" t="n">
         <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="AC12" t="n">
         <v>2.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.09</v>
+        <v>2.31</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46019.40972222222</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,16 +1942,16 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1964,77 +1964,77 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="M13" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="N13" t="n">
-        <v>4.5</v>
+        <v>3.08</v>
       </c>
       <c r="O13" t="n">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="P13" t="n">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.59</v>
+        <v>3.6</v>
       </c>
       <c r="R13" t="n">
-        <v>1.73</v>
+        <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>1.99</v>
+        <v>2.59</v>
       </c>
       <c r="T13" t="n">
-        <v>4.3</v>
+        <v>2.96</v>
       </c>
       <c r="U13" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="V13" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="W13" t="n">
         <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.72</v>
+        <v>1.29</v>
       </c>
       <c r="Z13" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.41</v>
+        <v>2.03</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.65</v>
+        <v>3.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.54</v>
+        <v>1.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.45</v>
+        <v>1.9</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46019.41666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,99 +2061,99 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="M14" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="N14" t="n">
-        <v>3.08</v>
+        <v>4.5</v>
       </c>
       <c r="O14" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.6</v>
+        <v>5.59</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>1.73</v>
       </c>
       <c r="S14" t="n">
-        <v>2.59</v>
+        <v>1.99</v>
       </c>
       <c r="T14" t="n">
-        <v>2.96</v>
+        <v>4.3</v>
       </c>
       <c r="U14" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="V14" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="W14" t="n">
         <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.29</v>
+        <v>1.72</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.03</v>
+        <v>2.41</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.7</v>
+        <v>6.65</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.8</v>
+        <v>2.54</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.9</v>
+        <v>1.45</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46019.41666666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.6</v>
+        <v>2.65</v>
       </c>
       <c r="M15" t="n">
-        <v>3.77</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>1.6</v>
+        <v>2.75</v>
       </c>
       <c r="O15" t="n">
-        <v>6.2</v>
+        <v>3.48</v>
       </c>
       <c r="P15" t="n">
-        <v>2.14</v>
+        <v>1.93</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.2</v>
+        <v>3.28</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="U15" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="V15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.28</v>
+        <v>2.63</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.14</v>
+        <v>1.49</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.65</v>
+        <v>5.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.25</v>
+        <v>3.77</v>
       </c>
       <c r="N17" t="n">
-        <v>2.75</v>
+        <v>1.6</v>
       </c>
       <c r="O17" t="n">
-        <v>3.46</v>
+        <v>6.2</v>
       </c>
       <c r="P17" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.21</v>
+        <v>2.2</v>
       </c>
       <c r="R17" t="n">
         <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="T17" t="n">
-        <v>3.42</v>
+        <v>2.9</v>
       </c>
       <c r="U17" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="V17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W17" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.7</v>
+        <v>3.28</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.49</v>
+        <v>1.14</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46019.45833333334</v>
@@ -3042,19 +3042,19 @@
         <v>3.95</v>
       </c>
       <c r="M22" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="O22" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="P22" t="n">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="R22" t="n">
         <v>1.3</v>
@@ -3063,13 +3063,13 @@
         <v>3.08</v>
       </c>
       <c r="T22" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="U22" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="V22" t="n">
-        <v>5.65</v>
+        <v>5.5</v>
       </c>
       <c r="W22" t="n">
         <v>1.08</v>
@@ -3078,22 +3078,22 @@
         <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z22" t="n">
-        <v>4.05</v>
+        <v>4.15</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE22" t="n">
         <v>1.6</v>
@@ -3105,7 +3105,7 @@
         <v>1.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46019.53125</v>
@@ -3158,22 +3158,22 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="M23" t="n">
-        <v>3.87</v>
+        <v>3.8</v>
       </c>
       <c r="N23" t="n">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
         <v>2.5</v>
       </c>
       <c r="P23" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.31</v>
+        <v>4.41</v>
       </c>
       <c r="R23" t="n">
         <v>1.31</v>
@@ -3182,13 +3182,13 @@
         <v>3.02</v>
       </c>
       <c r="T23" t="n">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="U23" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="V23" t="n">
-        <v>6.25</v>
+        <v>6.15</v>
       </c>
       <c r="W23" t="n">
         <v>1.06</v>
@@ -3200,7 +3200,7 @@
         <v>1.24</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.85</v>
+        <v>3.94</v>
       </c>
       <c r="AA23" t="n">
         <v>1.78</v>
@@ -3209,22 +3209,22 @@
         <v>2</v>
       </c>
       <c r="AC23" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46019.54166666666</v>
@@ -3277,61 +3277,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N24" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="O24" t="n">
         <v>2.88</v>
       </c>
       <c r="P24" t="n">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="R24" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="T24" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V24" t="n">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
       <c r="W24" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X24" t="n">
         <v>1.04</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.26</v>
+        <v>3</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AE24" t="n">
         <v>1.67</v>
@@ -3340,7 +3340,7 @@
         <v>2.1</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
         <v>1.65</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.57</v>
+        <v>3.8</v>
       </c>
       <c r="M29" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N29" t="n">
-        <v>5.8</v>
+        <v>2</v>
       </c>
       <c r="O29" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z29" t="n">
         <v>2.52</v>
       </c>
-      <c r="P29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>7.08</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="S29" t="n">
+      <c r="AA29" t="n">
         <v>2.1</v>
       </c>
-      <c r="T29" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="V29" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AB29" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.33</v>
+        <v>3.85</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.24</v>
+        <v>2.01</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.87</v>
+        <v>1.21</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46019.70833333334</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.8</v>
+        <v>1.57</v>
       </c>
       <c r="M30" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>2</v>
+        <v>5.8</v>
       </c>
       <c r="O30" t="n">
-        <v>4.62</v>
+        <v>2.52</v>
       </c>
       <c r="P30" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.7</v>
+        <v>7.08</v>
       </c>
       <c r="R30" t="n">
-        <v>1.49</v>
+        <v>1.64</v>
       </c>
       <c r="S30" t="n">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="T30" t="n">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="U30" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="V30" t="n">
-        <v>9.199999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W30" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X30" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.85</v>
+        <v>4.33</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.01</v>
+        <v>2.24</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.21</v>
+        <v>1.87</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46019.70833333334</v>

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -990,99 +990,99 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O5" t="n">
+        <v>5</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V5" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC5" t="n">
         <v>3</v>
       </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M5" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="N5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V5" t="n">
-        <v>6</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.59</v>
-      </c>
       <c r="AD5" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.14</v>
+        <v>2.55</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.68</v>
+        <v>1.08</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46019.3125</v>
@@ -1109,25 +1109,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" t="n">
         <v>1</v>
       </c>
-      <c r="H6" t="n">
-        <v>4</v>
-      </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="N6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q6" t="n">
         <v>6.5</v>
       </c>
-      <c r="M6" t="n">
-        <v>4</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="O6" t="n">
-        <v>5</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.03</v>
-      </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S6" t="n">
-        <v>2.96</v>
+        <v>3.08</v>
       </c>
       <c r="T6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V6" t="n">
+        <v>6</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC6" t="n">
         <v>2.59</v>
       </c>
-      <c r="U6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3</v>
-      </c>
       <c r="AD6" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.55</v>
+        <v>1.14</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.08</v>
+        <v>2.68</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46019.3125</v>
@@ -1704,25 +1704,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1730,22 +1730,22 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M11" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="N11" t="n">
         <v>5.4</v>
       </c>
-      <c r="M11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1.38</v>
-      </c>
       <c r="O11" t="n">
-        <v>5.2</v>
+        <v>2.04</v>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.01</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
         <v>1.24</v>
@@ -1754,49 +1754,49 @@
         <v>3.34</v>
       </c>
       <c r="T11" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="U11" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="V11" t="n">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="W11" t="n">
         <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="AC11" t="n">
         <v>2.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.09</v>
+        <v>2.31</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46019.40972222222</v>
@@ -1823,25 +1823,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1849,22 +1849,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.37</v>
+        <v>5.4</v>
       </c>
       <c r="M12" t="n">
-        <v>4.55</v>
+        <v>4.4</v>
       </c>
       <c r="N12" t="n">
-        <v>5.4</v>
+        <v>1.38</v>
       </c>
       <c r="O12" t="n">
-        <v>2.04</v>
+        <v>5.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>2.01</v>
       </c>
       <c r="R12" t="n">
         <v>1.24</v>
@@ -1873,49 +1873,49 @@
         <v>3.34</v>
       </c>
       <c r="T12" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="U12" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="V12" t="n">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="W12" t="n">
         <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.85</v>
+        <v>4.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="AC12" t="n">
         <v>2.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.31</v>
+        <v>1.09</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46019.40972222222</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,25 +1942,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
         <v>1</v>
       </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="N13" t="n">
-        <v>3.08</v>
+        <v>4.5</v>
       </c>
       <c r="O13" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.6</v>
+        <v>5.59</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>1.73</v>
       </c>
       <c r="S13" t="n">
-        <v>2.59</v>
+        <v>1.99</v>
       </c>
       <c r="T13" t="n">
-        <v>2.96</v>
+        <v>4.3</v>
       </c>
       <c r="U13" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="V13" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="W13" t="n">
         <v>1.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.29</v>
+        <v>1.72</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.03</v>
+        <v>2.41</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.7</v>
+        <v>6.65</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.8</v>
+        <v>2.54</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.9</v>
+        <v>1.45</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46019.41666666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,25 +2061,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="M14" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="N14" t="n">
-        <v>4.5</v>
+        <v>3.08</v>
       </c>
       <c r="O14" t="n">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="P14" t="n">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.59</v>
+        <v>3.6</v>
       </c>
       <c r="R14" t="n">
-        <v>1.73</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>1.99</v>
+        <v>2.59</v>
       </c>
       <c r="T14" t="n">
-        <v>4.3</v>
+        <v>2.96</v>
       </c>
       <c r="U14" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="V14" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="W14" t="n">
         <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.72</v>
+        <v>1.29</v>
       </c>
       <c r="Z14" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.41</v>
+        <v>2.03</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.65</v>
+        <v>3.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.54</v>
+        <v>1.8</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.45</v>
+        <v>1.9</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46019.41666666666</v>
@@ -2189,20 +2189,20 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -2430,17 +2430,17 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -2572,40 +2572,40 @@
         <v>6.8</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>6.91</v>
       </c>
       <c r="AA18" t="n">
         <v>1.4</v>
@@ -2620,16 +2620,16 @@
         <v>1.72</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46019.47916666666</v>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2797,77 +2797,77 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.95</v>
+        <v>3.05</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>1.97</v>
+        <v>2.5</v>
       </c>
       <c r="O20" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.58</v>
+        <v>3.46</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="S20" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="T20" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="V20" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.15</v>
+        <v>2.65</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.2</v>
+        <v>4.85</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46019.52083333334</v>
@@ -2894,99 +2894,99 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="M21" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="O21" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.43</v>
+        <v>2.53</v>
       </c>
       <c r="R21" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
       <c r="T21" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="U21" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="V21" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W21" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AF21" t="n">
         <v>1.76</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46019.52083333334</v>
@@ -3022,20 +3022,20 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -3141,20 +3141,20 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,99 +3251,99 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Al Rayyan</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.31</v>
+        <v>3.2</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>4.25</v>
       </c>
       <c r="N24" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="O24" t="n">
-        <v>2.88</v>
+        <v>3.58</v>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>2.65</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.5</v>
+        <v>2.21</v>
       </c>
       <c r="R24" t="n">
-        <v>1.38</v>
+        <v>1.11</v>
       </c>
       <c r="S24" t="n">
-        <v>2.95</v>
+        <v>4.9</v>
       </c>
       <c r="T24" t="n">
-        <v>2.62</v>
+        <v>1.77</v>
       </c>
       <c r="U24" t="n">
-        <v>1.44</v>
+        <v>1.93</v>
       </c>
       <c r="V24" t="n">
-        <v>6.9</v>
+        <v>3.34</v>
       </c>
       <c r="W24" t="n">
-        <v>1.05</v>
+        <v>1.24</v>
       </c>
       <c r="X24" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.9</v>
+        <v>8.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.87</v>
+        <v>1.25</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.01</v>
+        <v>3.7</v>
       </c>
       <c r="AC24" t="n">
-        <v>3</v>
+        <v>1.65</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.33</v>
+        <v>2.12</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.1</v>
+        <v>3.51</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46019.5625</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,99 +3370,99 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Rayyan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L25" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V25" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AC25" t="n">
         <v>3</v>
       </c>
-      <c r="M25" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="O25" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S25" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V25" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AD25" t="n">
-        <v>1.88</v>
+        <v>1.33</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.26</v>
+        <v>1.67</v>
       </c>
       <c r="AF25" t="n">
-        <v>3.55</v>
+        <v>2.1</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46019.5625</v>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -3511,44 +3511,44 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.76</v>
+        <v>1.97</v>
       </c>
       <c r="M26" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
       <c r="N26" t="n">
-        <v>4.7</v>
+        <v>3.85</v>
       </c>
       <c r="O26" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="P26" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="R26" t="n">
         <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="T26" t="n">
         <v>3.04</v>
       </c>
       <c r="U26" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="V26" t="n">
         <v>7.3</v>
       </c>
       <c r="W26" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X26" t="n">
         <v>1.04</v>
@@ -3560,16 +3560,16 @@
         <v>3.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AC26" t="n">
         <v>3.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE26" t="n">
         <v>1.85</v>
@@ -3578,10 +3578,10 @@
         <v>1.9</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46019.58333333334</v>
@@ -3637,10 +3637,10 @@
         <v>3.25</v>
       </c>
       <c r="M27" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O27" t="n">
         <v>3.85</v>
@@ -3649,25 +3649,25 @@
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="R27" t="n">
         <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="T27" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="U27" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V27" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X27" t="n">
         <v>1.02</v>
@@ -3679,13 +3679,13 @@
         <v>2.95</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.55</v>
+        <v>1.81</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AD27" t="n">
         <v>1.25</v>
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.23</v>
+        <v>3.55</v>
       </c>
       <c r="M28" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N28" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="O28" t="n">
         <v>3.85</v>
@@ -3768,22 +3768,22 @@
         <v>2.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="R28" t="n">
         <v>1.27</v>
       </c>
       <c r="S28" t="n">
-        <v>3.25</v>
+        <v>3.02</v>
       </c>
       <c r="T28" t="n">
-        <v>2.59</v>
+        <v>2.45</v>
       </c>
       <c r="U28" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="V28" t="n">
-        <v>6.35</v>
+        <v>6.2</v>
       </c>
       <c r="W28" t="n">
         <v>1.07</v>
@@ -3795,22 +3795,22 @@
         <v>1.22</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.03</v>
+        <v>2.17</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AF28" t="n">
         <v>2.2</v>
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="M29" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N29" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="O29" t="n">
-        <v>4.62</v>
+        <v>5.81</v>
       </c>
       <c r="P29" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.7</v>
+        <v>2.32</v>
       </c>
       <c r="R29" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="S29" t="n">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="T29" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="U29" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="V29" t="n">
-        <v>9.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W29" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X29" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.85</v>
+        <v>4.05</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46019.70833333334</v>
@@ -3991,22 +3991,22 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="M30" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="N30" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="O30" t="n">
         <v>2.52</v>
       </c>
       <c r="P30" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q30" t="n">
-        <v>7.08</v>
+        <v>6.86</v>
       </c>
       <c r="R30" t="n">
         <v>1.64</v>
@@ -4030,19 +4030,19 @@
         <v>1.1</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Z30" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AA30" t="n">
         <v>2.45</v>
       </c>
-      <c r="AA30" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AB30" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AD30" t="n">
         <v>1.14</v>
@@ -4054,10 +4054,10 @@
         <v>1.55</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46019.70833333334</v>
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4.4</v>
+        <v>3.68</v>
       </c>
       <c r="M31" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="N31" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="O31" t="n">
-        <v>4.54</v>
+        <v>4.66</v>
       </c>
       <c r="P31" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="R31" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S31" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="T31" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="U31" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V31" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="W31" t="n">
         <v>1.06</v>
       </c>
       <c r="X31" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AC31" t="n">
         <v>3.25</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AG31" t="n">
         <v>1.24</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46019.70833333334</v>
@@ -4229,40 +4229,40 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="M32" t="n">
-        <v>7.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N32" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="O32" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="P32" t="n">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="Q32" t="n">
-        <v>14.93</v>
+        <v>15.65</v>
       </c>
       <c r="R32" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S32" t="n">
-        <v>3.75</v>
+        <v>3.66</v>
       </c>
       <c r="T32" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="U32" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="V32" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="W32" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X32" t="n">
         <v>1.01</v>
@@ -4271,31 +4271,31 @@
         <v>1.09</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.4</v>
+        <v>5.25</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AG32" t="n">
         <v>1.03</v>
       </c>
       <c r="AH32" t="n">
-        <v>6.85</v>
+        <v>6.9</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46019.72916666666</v>
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>6.9</v>
+        <v>6.3</v>
       </c>
       <c r="M33" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="N33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="O33" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R33" t="n">
         <v>1.35</v>
       </c>
-      <c r="O33" t="n">
-        <v>5</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.33</v>
-      </c>
       <c r="S33" t="n">
-        <v>2.86</v>
+        <v>2.79</v>
       </c>
       <c r="T33" t="n">
-        <v>2.39</v>
+        <v>2.47</v>
       </c>
       <c r="U33" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V33" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="W33" t="n">
         <v>1.09</v>
       </c>
       <c r="X33" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.65</v>
+        <v>3.42</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.25</v>
+        <v>2.83</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46019.75</v>
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="M34" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="N34" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="O34" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="P34" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="Q34" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="R34" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S34" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="T34" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="U34" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V34" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="W34" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X34" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC34" t="n">
         <v>3.14</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.49</v>
+        <v>2.59</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46019.85416666666</v>

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -990,25 +990,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
         <v>1</v>
       </c>
-      <c r="H5" t="n">
-        <v>4</v>
-      </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="N5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q5" t="n">
         <v>6.5</v>
       </c>
-      <c r="M5" t="n">
-        <v>4</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="O5" t="n">
-        <v>5</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.03</v>
-      </c>
       <c r="R5" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
-        <v>2.96</v>
+        <v>3.08</v>
       </c>
       <c r="T5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V5" t="n">
+        <v>6</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC5" t="n">
         <v>2.59</v>
       </c>
-      <c r="U5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>3</v>
-      </c>
       <c r="AD5" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.55</v>
+        <v>1.14</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.08</v>
+        <v>2.68</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46019.3125</v>
@@ -1109,99 +1109,99 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O6" t="n">
+        <v>5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AC6" t="n">
         <v>3</v>
       </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M6" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="N6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V6" t="n">
-        <v>6</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.59</v>
-      </c>
       <c r="AD6" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.14</v>
+        <v>2.55</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.68</v>
+        <v>1.08</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46019.3125</v>
@@ -1704,25 +1704,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1730,22 +1730,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.37</v>
+        <v>5.4</v>
       </c>
       <c r="M11" t="n">
-        <v>4.55</v>
+        <v>4.4</v>
       </c>
       <c r="N11" t="n">
-        <v>5.4</v>
+        <v>1.38</v>
       </c>
       <c r="O11" t="n">
-        <v>2.04</v>
+        <v>5.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>2.01</v>
       </c>
       <c r="R11" t="n">
         <v>1.24</v>
@@ -1754,49 +1754,49 @@
         <v>3.34</v>
       </c>
       <c r="T11" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="U11" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="V11" t="n">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="W11" t="n">
         <v>1.1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.85</v>
+        <v>4.75</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="AC11" t="n">
         <v>2.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.31</v>
+        <v>1.09</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46019.40972222222</v>
@@ -1823,25 +1823,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1849,22 +1849,22 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M12" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="N12" t="n">
         <v>5.4</v>
       </c>
-      <c r="M12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1.38</v>
-      </c>
       <c r="O12" t="n">
-        <v>5.2</v>
+        <v>2.04</v>
       </c>
       <c r="P12" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.01</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
         <v>1.24</v>
@@ -1873,49 +1873,49 @@
         <v>3.34</v>
       </c>
       <c r="T12" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="U12" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="V12" t="n">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="W12" t="n">
         <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="AC12" t="n">
         <v>2.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.09</v>
+        <v>2.31</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46019.40972222222</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,22 +2180,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.65</v>
+        <v>4.05</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N15" t="n">
-        <v>2.75</v>
+        <v>1.77</v>
       </c>
       <c r="O15" t="n">
-        <v>3.48</v>
+        <v>4.34</v>
       </c>
       <c r="P15" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.28</v>
+        <v>2.62</v>
       </c>
       <c r="R15" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="T15" t="n">
-        <v>3.5</v>
+        <v>3.24</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.63</v>
+        <v>3.04</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="AB15" t="n">
         <v>1.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.3</v>
+        <v>4.03</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,22 +2299,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>4.05</v>
+        <v>2.65</v>
       </c>
       <c r="M16" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>1.77</v>
+        <v>2.75</v>
       </c>
       <c r="O16" t="n">
-        <v>4.34</v>
+        <v>3.48</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.62</v>
+        <v>3.28</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="T16" t="n">
-        <v>3.24</v>
+        <v>3.5</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.04</v>
+        <v>2.63</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AB16" t="n">
         <v>1.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.03</v>
+        <v>4.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46019.45833333334</v>
@@ -2537,16 +2537,16 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.32</v>
+        <v>3.2</v>
       </c>
       <c r="M18" t="n">
-        <v>4.9</v>
+        <v>3.55</v>
       </c>
       <c r="N18" t="n">
-        <v>6.8</v>
+        <v>1.93</v>
       </c>
       <c r="O18" t="n">
-        <v>1.83</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="Q18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V18" t="n">
         <v>5</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V18" t="n">
-        <v>4</v>
-      </c>
       <c r="W18" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.91</v>
+        <v>4.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.98</v>
+        <v>2.26</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.72</v>
+        <v>1.51</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.38</v>
+        <v>1.23</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46019.47916666666</v>
@@ -2656,16 +2656,16 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.2</v>
+        <v>1.32</v>
       </c>
       <c r="M19" t="n">
-        <v>3.55</v>
+        <v>4.9</v>
       </c>
       <c r="N19" t="n">
-        <v>1.93</v>
+        <v>6.8</v>
       </c>
       <c r="O19" t="n">
-        <v>3.6</v>
+        <v>1.83</v>
       </c>
       <c r="P19" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S19" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="T19" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="U19" t="n">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="V19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.5</v>
+        <v>6.91</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.26</v>
+        <v>1.98</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AF19" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AH19" t="n">
         <v>2.38</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.23</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46019.47916666666</v>
@@ -2775,25 +2775,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.05</v>
+        <v>4.33</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="O20" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="P20" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.46</v>
+        <v>2.53</v>
       </c>
       <c r="R20" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>2.31</v>
+        <v>2.47</v>
       </c>
       <c r="T20" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="U20" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="V20" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X20" t="n">
         <v>1.03</v>
       </c>
-      <c r="X20" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y20" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.65</v>
+        <v>2.28</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.85</v>
+        <v>4.2</v>
       </c>
       <c r="AD20" t="n">
         <v>1.18</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46019.52083333334</v>
@@ -2894,25 +2894,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>4.33</v>
+        <v>3.05</v>
       </c>
       <c r="M21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T21" t="n">
         <v>3.3</v>
       </c>
-      <c r="N21" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="O21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.22</v>
-      </c>
       <c r="U21" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="V21" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="W21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X21" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.28</v>
+        <v>2.65</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.2</v>
+        <v>4.85</v>
       </c>
       <c r="AD21" t="n">
         <v>1.18</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46019.52083333334</v>
@@ -3617,20 +3617,20 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -3739,7 +3739,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3868,77 +3868,77 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.75</v>
+        <v>1.57</v>
       </c>
       <c r="M29" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>1.7</v>
+        <v>5.8</v>
       </c>
       <c r="O29" t="n">
-        <v>5.81</v>
+        <v>2.52</v>
       </c>
       <c r="P29" t="n">
-        <v>1.97</v>
+        <v>1.76</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.32</v>
+        <v>6.86</v>
       </c>
       <c r="R29" t="n">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="S29" t="n">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="T29" t="n">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="U29" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="V29" t="n">
-        <v>8.699999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W29" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X29" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.59</v>
+        <v>2.45</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.05</v>
+        <v>4.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.09</v>
+        <v>2.24</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.11</v>
+        <v>1.85</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46019.70833333334</v>
@@ -3965,19 +3965,19 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -3987,77 +3987,77 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L30" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="O30" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V30" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB30" t="n">
         <v>1.8</v>
       </c>
-      <c r="M30" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O30" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="V30" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AC30" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.24</v>
+        <v>1.77</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.85</v>
+        <v>1.18</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46019.70833333334</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.68</v>
+        <v>4.5</v>
       </c>
       <c r="M31" t="n">
         <v>3.3</v>
       </c>
       <c r="N31" t="n">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="O31" t="n">
-        <v>4.66</v>
+        <v>5.81</v>
       </c>
       <c r="P31" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.47</v>
+        <v>2.32</v>
       </c>
       <c r="R31" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="S31" t="n">
-        <v>2.67</v>
+        <v>2.39</v>
       </c>
       <c r="T31" t="n">
-        <v>2.79</v>
+        <v>3.2</v>
       </c>
       <c r="U31" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="V31" t="n">
-        <v>7.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="W31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X31" t="n">
         <v>1.06</v>
       </c>
-      <c r="X31" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y31" t="n">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.14</v>
+        <v>2.59</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.25</v>
+        <v>4.05</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.77</v>
+        <v>2.09</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.9</v>
+        <v>1.63</v>
       </c>
       <c r="AG31" t="n">
         <v>1.24</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46019.70833333334</v>
@@ -4348,49 +4348,49 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>6.3</v>
+        <v>4.97</v>
       </c>
       <c r="M33" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="N33" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="O33" t="n">
         <v>4.75</v>
       </c>
       <c r="P33" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="R33" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S33" t="n">
-        <v>2.79</v>
+        <v>2.92</v>
       </c>
       <c r="T33" t="n">
-        <v>2.47</v>
+        <v>2.65</v>
       </c>
       <c r="U33" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="V33" t="n">
-        <v>6.3</v>
+        <v>5</v>
       </c>
       <c r="W33" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X33" t="n">
         <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.42</v>
+        <v>4</v>
       </c>
       <c r="AA33" t="n">
         <v>1.85</v>
@@ -4399,22 +4399,22 @@
         <v>1.93</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.83</v>
+        <v>2.52</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46019.75</v>
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="M34" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="N34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O34" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="P34" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="Q34" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="R34" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S34" t="n">
         <v>2.75</v>
       </c>
       <c r="T34" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="U34" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V34" t="n">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="W34" t="n">
         <v>1.08</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AC34" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AD34" t="n">
         <v>1.3</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AH34" t="n">
-        <v>2.59</v>
+        <v>2.3</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46019.85416666666</v>

--- a/jogos_2025-12-28.xlsx
+++ b/jogos_2025-12-28.xlsx
@@ -2537,16 +2537,16 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.2</v>
+        <v>1.32</v>
       </c>
       <c r="M18" t="n">
-        <v>3.55</v>
+        <v>4.9</v>
       </c>
       <c r="N18" t="n">
-        <v>1.93</v>
+        <v>6.8</v>
       </c>
       <c r="O18" t="n">
-        <v>3.6</v>
+        <v>1.83</v>
       </c>
       <c r="P18" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S18" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="T18" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="U18" t="n">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="V18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.5</v>
+        <v>6.91</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.26</v>
+        <v>1.98</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AF18" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AH18" t="n">
         <v>2.38</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.23</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46019.47916666666</v>
@@ -2656,16 +2656,16 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.32</v>
+        <v>3.2</v>
       </c>
       <c r="M19" t="n">
-        <v>4.9</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>6.8</v>
+        <v>1.93</v>
       </c>
       <c r="O19" t="n">
-        <v>1.83</v>
+        <v>3.6</v>
       </c>
       <c r="P19" t="n">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="Q19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V19" t="n">
         <v>5</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V19" t="n">
-        <v>4</v>
-      </c>
       <c r="W19" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.91</v>
+        <v>4.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.98</v>
+        <v>2.26</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.72</v>
+        <v>1.51</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.38</v>
+        <v>1.23</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46019.47916666666</v>
@@ -2775,25 +2775,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FC Arouca</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.33</v>
+        <v>3.05</v>
       </c>
       <c r="M20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T20" t="n">
         <v>3.3</v>
       </c>
-      <c r="N20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="O20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.22</v>
-      </c>
       <c r="U20" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="V20" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.28</v>
+        <v>2.65</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.2</v>
+        <v>4.85</v>
       </c>
       <c r="AD20" t="n">
         <v>1.18</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46019.52083333334</v>
@@ -2894,25 +2894,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>FC Arouca</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.05</v>
+        <v>4.33</v>
       </c>
       <c r="M21" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="N21" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="O21" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="P21" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.46</v>
+        <v>2.53</v>
       </c>
       <c r="R21" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>2.31</v>
+        <v>2.47</v>
       </c>
       <c r="T21" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="U21" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="V21" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X21" t="n">
         <v>1.03</v>
       </c>
-      <c r="X21" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y21" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.65</v>
+        <v>2.28</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.85</v>
+        <v>4.2</v>
       </c>
       <c r="AD21" t="n">
         <v>1.18</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46019.52083333334</v>
@@ -3846,19 +3846,19 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.57</v>
+        <v>4.4</v>
       </c>
       <c r="M29" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N29" t="n">
-        <v>5.8</v>
+        <v>1.68</v>
       </c>
       <c r="O29" t="n">
-        <v>2.52</v>
+        <v>4.66</v>
       </c>
       <c r="P29" t="n">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="Q29" t="n">
-        <v>6.86</v>
+        <v>2.47</v>
       </c>
       <c r="R29" t="n">
-        <v>1.64</v>
+        <v>1.38</v>
       </c>
       <c r="S29" t="n">
-        <v>2.1</v>
+        <v>2.67</v>
       </c>
       <c r="T29" t="n">
-        <v>3.42</v>
+        <v>2.79</v>
       </c>
       <c r="U29" t="n">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="V29" t="n">
-        <v>9.699999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X29" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.45</v>
+        <v>3.14</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.24</v>
+        <v>1.77</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.85</v>
+        <v>1.18</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46019.70833333334</v>
@@ -3965,19 +3965,19 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N30" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="V30" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC30" t="n">
         <v>4.4</v>
       </c>
-      <c r="M30" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N30" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="O30" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V30" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AD30" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.77</v>
+        <v>2.24</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.9</v>
+        <v>1.55</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.18</v>
+        <v>1.85</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46019.70833333334</v>
@@ -4096,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -4212,20 +4212,20 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L32" t="n">
@@ -4331,7 +4331,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L33" t="n">
